--- a/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
+++ b/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
@@ -606,8 +606,10 @@
           <t>14942298s1</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>550</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -639,8 +641,10 @@
           <t>14993499s1</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>1122</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>14993499s1-3</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -933,7 +937,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1926,1933,1940,1957,1964/1224</t>
+          <t>AST-0007</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -969,7 +973,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1926,1940,1957,1964/816</t>
+          <t>AST-0006</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1005,7 +1009,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1940,1957,1964/612</t>
+          <t>AST-0005</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1077,7 +1081,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2121,2138,2145,2152/1020</t>
+          <t>AST-0008</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1113,7 +1117,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2367,2459/347,157</t>
+          <t>2367,2459/347,157-a</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1149,7 +1153,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2374,2466/347,157</t>
+          <t>2374,2466/347,157-a</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1185,7 +1189,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2381,2473/347,157</t>
+          <t>2381,2473/347,157-a</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1221,7 +1225,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2398,2480/347,157</t>
+          <t>2398,2480/347,157-a</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1257,7 +1261,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2404,2497/347,157</t>
+          <t>2404,2497/347,157-a</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1293,7 +1297,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2411,2503/347,157</t>
+          <t>2411,2503/347,157-a</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1329,7 +1333,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2428,2510/347,157</t>
+          <t>2428,2510/347,157-a</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1401,7 +1405,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2541,2558,2565,2572,2589,2596</t>
+          <t>AST-0009</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1437,7 +1441,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2718,2725,2732,2749,2756/768</t>
+          <t>2787,2794,2800,2817,2824/2088-a</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1473,7 +1477,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2787,2794,2800,2817,2824/2088</t>
+          <t>2787,2794,2800,2817,2824/2088-a</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1509,7 +1513,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2794,2817,2831/1044</t>
+          <t>2794,2817,2831/1044-a</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1545,7 +1549,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2787,2800,2824/1044</t>
+          <t>2787,2800,2824/1044-a</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1617,7 +1621,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6508,6515,8076,8083,8090/1130</t>
+          <t>AST-0012</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1655,7 +1659,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>6508,6515,8076,8083,8090/1130</t>
+          <t>AST-0012</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1693,7 +1697,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>6508,6515,8076,8083,8090/1130</t>
+          <t>AST-0012</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1731,7 +1735,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6508,6515,8076,8083,8090/1130</t>
+          <t>AST-0012</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1769,7 +1773,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>6508,6515/638</t>
+          <t>AST-0011-a</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -2129,7 +2133,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2129,2167,2136/1815</t>
+          <t>2129,2167/1210</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2273,7 +2277,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>4838/3848</t>
+          <t>4571411204838</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2675,7 +2679,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3737,3432</t>
+          <t>3737/3432</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -3026,8 +3030,10 @@
       <c r="B69" t="n">
         <v>840064400329</v>
       </c>
-      <c r="C69" t="n">
-        <v>329</v>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0329</t>
+        </is>
       </c>
       <c r="D69" t="n">
         <v>840064400329</v>
@@ -3200,7 +3206,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2142/1980</t>
+          <t>2142/1980-a</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3250,7 +3256,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>6936/383</t>
+          <t>6936/383-a</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3398,7 +3404,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>5055/165</t>
+          <t>4987244145055-a</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3448,7 +3454,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>5055/165</t>
+          <t>4987244145055-a</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3498,7 +3504,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>5055/165</t>
+          <t>4987244145055-a</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3548,7 +3554,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>5055/165</t>
+          <t>4987244145055-a</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3788,7 +3794,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2330/1220</t>
+          <t>2330/1220-a</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3828,7 +3834,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1307/1540</t>
+          <t>4902628241307-2-a</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3878,7 +3884,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>8286/1978</t>
+          <t>8286/1978-a</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3928,7 +3934,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>9912/1538</t>
+          <t>9912/1538-a</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4068,7 +4074,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>8772/550</t>
+          <t>8772/550-a</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4118,7 +4124,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>8734/434</t>
+          <t>8734/434-a</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4256,7 +4262,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>0916/2418</t>
+          <t>0916/2418-a</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4296,7 +4302,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>0923/3246</t>
+          <t>0923/3246-a</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4336,7 +4342,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>0909/2418</t>
+          <t>0909/2418-a</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4386,7 +4392,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>0011,3092/2501</t>
+          <t>0011,3092/2501-a</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4436,7 +4442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>0011,3238/3178</t>
+          <t>0011,3238/3178-a</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4486,7 +4492,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>0011,3214/2457</t>
+          <t>0011,3214/2457-a</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4536,7 +4542,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>0011,2330/2187</t>
+          <t>0011,2330/2187-a</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4586,7 +4592,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>0011,3153/3403</t>
+          <t>0011,3153/3403-a</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4636,7 +4642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2866/4117</t>
+          <t>2866/4117-a</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4686,7 +4692,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>0893/1810</t>
+          <t>0893/1810-a</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4736,7 +4742,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0930/2418</t>
+          <t>0930/2418-a</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4776,7 +4782,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>7439/833</t>
+          <t>7439/833-a</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4826,7 +4832,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0211/2160</t>
+          <t>4901301200211-6-a</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4962,7 +4968,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>8703/1584</t>
+          <t>8703/1584-a</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5002,7 +5008,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>8710/1800</t>
+          <t>4901133618710-a</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5152,7 +5158,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>6365/680</t>
+          <t>4987072036365-3-a</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5202,7 +5208,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2927/2728</t>
+          <t>2927/2728-a</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5242,7 +5248,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>6317/1522</t>
+          <t>4901080186317-2-a</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5292,7 +5298,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>6317/3044</t>
+          <t>4901080186317-4-a</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5342,7 +5348,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>6031/612</t>
+          <t>6031/612-a</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5432,7 +5438,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1420,1437/2191,2208,2208</t>
+          <t>1420,1437/2191,2208,2208-a</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5472,7 +5478,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1420,1437/2191,2208,2208</t>
+          <t>1420,1437/2191,2208,2208-a</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5512,7 +5518,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>1420,1437/2191,2208,2208</t>
+          <t>1420,1437/2191,2208,2208-a</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5692,7 +5698,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>8938/416</t>
+          <t>4905009678938-2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -5742,7 +5748,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>8938/832</t>
+          <t>4905009678938-4</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5842,7 +5848,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>7378/620</t>
+          <t>7378/620-a</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5892,7 +5898,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>7378/1642</t>
+          <t>7378/1642-a</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5942,7 +5948,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>7378/2463</t>
+          <t>7378/2463-a</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6042,7 +6048,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3683/2790</t>
+          <t>4953103473683-a</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6132,7 +6138,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2866/5080</t>
+          <t>2866/5080-a</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6272,7 +6278,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>3092/1848</t>
+          <t>3092/1848-a</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6322,7 +6328,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>1115/704</t>
+          <t>1115/704-a</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6370,8 +6376,10 @@
           <t>b01dlmhmja</t>
         </is>
       </c>
-      <c r="C140" t="n">
-        <v>2528</v>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2492/2528</t>
+        </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -6420,7 +6428,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>8533/918</t>
+          <t>8533/918-a</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6460,7 +6468,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>9380/1584</t>
+          <t>9380/1584-a</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6510,7 +6518,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>3385/3320</t>
+          <t>3385/3320-a</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6610,7 +6618,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>3153/3652</t>
+          <t>3153/3652-a</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -6650,7 +6658,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>9659/1584</t>
+          <t>9659/1584-a</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6750,7 +6758,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>6117/522</t>
+          <t>6117/522-a</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6800,7 +6808,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>4619/2766</t>
+          <t>4901080194619-3-a</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6998,8 +7006,10 @@
           <t>b01navanrx</t>
         </is>
       </c>
-      <c r="C153" t="n">
-        <v>2512184180</v>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2512184180/3990</t>
+        </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -7048,7 +7058,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0380/5404</t>
+          <t>4901792030380-2-a</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7148,7 +7158,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>8986/852</t>
+          <t>4987072048986-2</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7198,7 +7208,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>9051/766</t>
+          <t>4987072049051-3-a</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7334,7 +7344,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>9577/1010</t>
+          <t>9577/1010-a</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7384,7 +7394,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>9502/500</t>
+          <t>9502/500-a</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7434,7 +7444,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>5767,5729/1999</t>
+          <t>5767,5729/1999-a</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7484,7 +7494,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>6804/3680</t>
+          <t>6804/3680-a</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7534,7 +7544,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>5620/2514</t>
+          <t>5620/2514-a</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7584,7 +7594,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>7773/1560</t>
+          <t>7773/1560-a</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -7684,7 +7694,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>6182/825</t>
+          <t>4992440036182</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -7822,8 +7832,10 @@
           <t>b079yplcvj</t>
         </is>
       </c>
-      <c r="C170" t="n">
-        <v>659</v>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>659-a</t>
+        </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -7872,7 +7884,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>M-8984/806</t>
+          <t>4901133718984</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -7912,7 +7924,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>4070/1311</t>
+          <t>4070/1311-a</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -7962,7 +7974,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0752/3026</t>
+          <t>4582300930752-2-a</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8012,7 +8024,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>7309/12730</t>
+          <t>4981254047309-a</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8062,7 +8074,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2803/1089</t>
+          <t>2803/1089-a</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8160,8 +8172,10 @@
           <t>b07gvmh1bb</t>
         </is>
       </c>
-      <c r="C177" t="n">
-        <v>418</v>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>418-a</t>
+        </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -8258,7 +8272,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>3813/4680</t>
+          <t>3813/4680-a</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8298,7 +8312,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2512/1659</t>
+          <t>4901080682512-3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8348,7 +8362,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1075/660</t>
+          <t>6902395691075-a</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8398,7 +8412,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1873/1248</t>
+          <t>4906156801873-3-a</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8448,7 +8462,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>5487/2970</t>
+          <t>5487/2970-a</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8548,7 +8562,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>1764/660</t>
+          <t>1764/660-a</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -8598,7 +8612,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>3214/1760</t>
+          <t>3214/1760-a</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8636,7 +8650,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>8286/3956</t>
+          <t>8286/3956-a</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -8676,7 +8690,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>8414/528</t>
+          <t>8414/528-a</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -8876,7 +8890,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>0204/2154</t>
+          <t>0204/2154-a</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -8976,7 +8990,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>6411/1740</t>
+          <t>6411/1740-a</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -9026,7 +9040,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>6411/1160</t>
+          <t>4901080686411-4-a</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -9076,7 +9090,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>6216/711</t>
+          <t>6216/711-a</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -9126,7 +9140,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>7934/9100</t>
+          <t>4540790177934-a</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -9176,7 +9190,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>7835/8000</t>
+          <t>7835/8000-a</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -9266,7 +9280,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0403/474</t>
+          <t>0403/474-a</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9366,7 +9380,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>5480/1650</t>
+          <t>5480/1650-a</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -9406,7 +9420,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>5510/1650</t>
+          <t>5510/1650-a</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -9456,7 +9470,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>5497/1650</t>
+          <t>5497/1650-a</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -9496,7 +9510,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>3414/730</t>
+          <t>4901080023414-2-a</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -9546,7 +9560,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>3414/2190</t>
+          <t>3414/2190-a</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -9596,7 +9610,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2180,2197/143,99</t>
+          <t>2180,2197/143,99-a</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -9646,7 +9660,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>3615/850</t>
+          <t>3615/850-a</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -9840,7 +9854,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>3238/2216</t>
+          <t>3238/2216-a</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -9880,7 +9894,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>3080/1167</t>
+          <t>3080/1167-a</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -9930,7 +9944,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>3080,4421/690</t>
+          <t>3080,4421/690-a</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -10080,7 +10094,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>1790/598</t>
+          <t>1790/598-a</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -10120,7 +10134,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>1769/638</t>
+          <t>4901133441769-a</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10370,7 +10384,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>0853/584</t>
+          <t>0853/584-a</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10420,7 +10434,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>0860/980</t>
+          <t>0860/980-a</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10460,7 +10474,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>6489/748</t>
+          <t>6489/748-a</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10560,7 +10574,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>1902/657</t>
+          <t>1902/657-a</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10610,7 +10624,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>1902/1314</t>
+          <t>1902/1314-a</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10660,7 +10674,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>1773/1738</t>
+          <t>4571263111773</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10810,7 +10824,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>3591/886</t>
+          <t>3591/886-a</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -10860,7 +10874,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>3591/886</t>
+          <t>3591/886-a</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -10908,8 +10922,10 @@
           <t>b08j1ndtz7</t>
         </is>
       </c>
-      <c r="C234" t="n">
-        <v>995</v>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>0995-a</t>
+        </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -11258,7 +11274,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6692/980</t>
+          <t>6692/980-a</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11306,8 +11322,10 @@
           <t>b08wshptwz</t>
         </is>
       </c>
-      <c r="C242" t="n">
-        <v>2691</v>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>2691-a</t>
+        </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -11356,7 +11374,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>8446/2283</t>
+          <t>8446/2283-a</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11406,7 +11424,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>8453/2600</t>
+          <t>4987241168453-2-a</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11446,7 +11464,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>0674/898</t>
+          <t>4987072060674-2</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11536,7 +11554,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>8902/1900</t>
+          <t>8902/1900-a</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11586,7 +11604,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>8919/1463</t>
+          <t>4901301388919-2</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11636,7 +11654,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>5878/1892</t>
+          <t>4936201105878-4-a</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -13416,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>4914/750</t>
+          <t>4902430644914-3</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13580,7 +13598,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>3322/3900</t>
+          <t>3322/3900-a</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13630,7 +13648,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>1491/1718</t>
+          <t>1491/1718-a</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13680,7 +13698,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>1255,1286/1508</t>
+          <t>1255,1286/1508-a</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13730,7 +13748,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>1255/2262</t>
+          <t>1255/2262-a</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13780,7 +13798,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>1286/2262</t>
+          <t>1286/2262-a</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13820,7 +13838,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>1484,1491/1055,859</t>
+          <t>1484,1491/1914-a</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13870,7 +13888,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>1484/2110</t>
+          <t>1484/2110-a</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13920,7 +13938,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>1323,5774/2061</t>
+          <t>1323,5774/2061-a</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13970,7 +13988,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>1323/2134</t>
+          <t>4987241171323-2-a</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14120,7 +14138,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>7685/9980</t>
+          <t>4961310157685</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14170,7 +14188,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>7698/16700</t>
+          <t>4571390307698</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14260,7 +14278,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0492/4980</t>
+          <t>0492/4980-a</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14310,7 +14328,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>3569/981</t>
+          <t>3569/981-a</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14590,7 +14608,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>6547/435</t>
+          <t>6547/435-a</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14640,7 +14658,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>5600,5709/168</t>
+          <t>5600,5709/168-a</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14690,7 +14708,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>7835/347</t>
+          <t>7835/347-a</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14740,7 +14758,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>4916,5050/1270</t>
+          <t>SET-4916-5050-a</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14790,7 +14808,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>4916/1188</t>
+          <t>4902407024916-2-a</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14888,8 +14906,10 @@
           <t>b09tpstjlv</t>
         </is>
       </c>
-      <c r="C316" t="n">
-        <v>6980</v>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>6980-a</t>
+        </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -14938,7 +14958,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>0439/2300</t>
+          <t>0439/2300-a</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14988,7 +15008,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>5809/13050</t>
+          <t>5809/13050-a</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -15178,7 +15198,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2724/1026</t>
+          <t>2724/1026-a</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15278,7 +15298,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2731,2724/1026</t>
+          <t>2731,2724/1026-a</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15328,7 +15348,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>7308/1010</t>
+          <t>4994527917308-a</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15548,7 +15568,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>3588/844</t>
+          <t>3588/844-a</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -15598,7 +15618,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>4542/3490</t>
+          <t>0194644104542</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -15648,7 +15668,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>3278/18800</t>
+          <t>3278/18800-a</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -15738,7 +15758,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0331/438</t>
+          <t>0331/438-a</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -15788,7 +15808,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0331/438</t>
+          <t>0331/438-a</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -15838,7 +15858,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0324/219</t>
+          <t>4580679800324-a</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -15888,7 +15908,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>0324/438</t>
+          <t>4580679800324-a</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -15938,7 +15958,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>0324,0331/438</t>
+          <t>0324,0331/438-a</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -15988,7 +16008,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>4459/6630</t>
+          <t>4459/6630-a</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -16038,7 +16058,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>251218-10490</t>
+          <t>251218/10490</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -16078,7 +16098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>8723/768</t>
+          <t>8723/768-a</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -16178,7 +16198,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>3557/924</t>
+          <t>3557/924-a</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -16228,7 +16248,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>7261/438</t>
+          <t>7261/438-a</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -16316,7 +16336,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>9514/2198</t>
+          <t>4901080589514-a</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -16366,7 +16386,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>4345/34800</t>
+          <t>4904710434345</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -16506,7 +16526,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>7140/550</t>
+          <t>7140/550-a</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -16556,7 +16576,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>7201/774</t>
+          <t>7201/774-a</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -16606,7 +16626,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>7218/774</t>
+          <t>7218/774-a</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -16694,7 +16714,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>5106/990</t>
+          <t>4580632115106-a</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -16744,7 +16764,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>5106/1980</t>
+          <t>4580632115106-2-a</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -16946,8 +16966,10 @@
           <t>b0blghwbvt</t>
         </is>
       </c>
-      <c r="C360" t="n">
-        <v>21800</v>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>21800-a</t>
+        </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -17086,7 +17108,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>1877/19800</t>
+          <t>1877/23979</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -17186,7 +17208,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>5722/970</t>
+          <t>4901133415722-6</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -17236,7 +17258,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>5722/580</t>
+          <t>4901133415722-6</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -17336,7 +17358,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>4024/2130</t>
+          <t>4024/2130-a</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -17516,7 +17538,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>1297/2190</t>
+          <t>0194644121297</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -17826,7 +17848,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2509,2516/1534</t>
+          <t>SET-2509-2516</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -17954,8 +17976,10 @@
           <t>b0bsfhf9jq</t>
         </is>
       </c>
-      <c r="C382" t="n">
-        <v>8480</v>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>8720689004589-a</t>
+        </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -18074,7 +18098,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>4995/1534</t>
+          <t>4995/1534-a</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -18222,7 +18246,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>4305/660</t>
+          <t>4305/660-a</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -18272,7 +18296,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>4169/498</t>
+          <t>4169/498-a</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -18362,7 +18386,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>8095/396</t>
+          <t>8095/396-a</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -18412,7 +18436,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>8712/1272</t>
+          <t>4901080068712-3</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -18462,7 +18486,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>8712/1272</t>
+          <t>AST-0004-8712,9115,9118-a</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -18512,7 +18536,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>5677/2112</t>
+          <t>5677/2112-a</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -18562,7 +18586,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>5050/1725</t>
+          <t>4902407025050-a</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -18650,8 +18674,10 @@
           <t>b0bxbplt8t</t>
         </is>
       </c>
-      <c r="C397" t="n">
-        <v>358</v>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>358-a</t>
+        </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -18700,7 +18726,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>4254/358</t>
+          <t>4254/358-a</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -18750,7 +18776,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>4193/358</t>
+          <t>4903301344193-2-a</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -18888,7 +18914,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>8444/707</t>
+          <t>4906456578444-a</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -18928,7 +18954,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>1184/8480</t>
+          <t>4987176171184-a</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -19148,7 +19174,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>1401/1980</t>
+          <t>4901301421401-5-a</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -19198,7 +19224,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>1401/1584</t>
+          <t>4901301421401-4-a</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -19248,7 +19274,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>1432/9990</t>
+          <t>0194644131432</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -19298,7 +19324,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2856/25800</t>
+          <t>2856/25800-a</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -19338,7 +19364,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2870/22800</t>
+          <t>2870/22800-a</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -19388,7 +19414,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2414/2344</t>
+          <t>4901080052414-2-a</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -19438,7 +19464,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2414/3516</t>
+          <t>4901080052414-3-a</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -19652,7 +19678,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>7612/946</t>
+          <t>4936201107612-2-a</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -19702,7 +19728,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>6624,6631/385,660</t>
+          <t>6624,6631/385,660-a</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -19752,7 +19778,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>6624,6631/385,660</t>
+          <t>6624,6631/385,660-a</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -19802,7 +19828,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>5687/2430</t>
+          <t>5687/2430-a</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -19850,8 +19876,10 @@
           <t>b0c57y8qc8</t>
         </is>
       </c>
-      <c r="C423" t="n">
-        <v>18800</v>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>18800-a</t>
+        </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -19890,7 +19918,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>7534/13980</t>
+          <t>8720689017534-a</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -19938,8 +19966,10 @@
           <t>b0c5812gdq</t>
         </is>
       </c>
-      <c r="C425" t="n">
-        <v>15980</v>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>8720689017688-a</t>
+        </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -19978,7 +20008,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>7595/6490</t>
+          <t>0194644137595</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -20018,7 +20048,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>7595/6490</t>
+          <t>0194644137595</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -20138,7 +20168,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>5151/502</t>
+          <t>5151/502-a</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -20188,7 +20218,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>8507/2283</t>
+          <t>8507/2283-a</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -20278,7 +20308,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>1641/9952</t>
+          <t>1641/9952-a</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -20328,7 +20358,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>5829/1210</t>
+          <t>5829/1210-a</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -20368,7 +20398,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>4503/10524</t>
+          <t>8710103994503-a</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -20574,7 +20604,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>2571/271</t>
+          <t>2571/271-a</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -20614,7 +20644,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>5589/22800</t>
+          <t>4987176165589-h-a</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -20654,7 +20684,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>2687/1538</t>
+          <t>2687/1538-a</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -20702,8 +20732,10 @@
           <t>b0cc8ltjkm</t>
         </is>
       </c>
-      <c r="C443" t="n">
-        <v>605858638891</v>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>605,858,638,891-a</t>
+        </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -20740,8 +20772,10 @@
           <t>b0cc8ltjkm</t>
         </is>
       </c>
-      <c r="C444" t="n">
-        <v>605858638891</v>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>605,858,638,891-a</t>
+        </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -20778,8 +20812,10 @@
           <t>b0cc8ltjkm</t>
         </is>
       </c>
-      <c r="C445" t="n">
-        <v>605858638891</v>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>605,858,638,891-a</t>
+        </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -20816,8 +20852,10 @@
           <t>b0cc8ltjkm</t>
         </is>
       </c>
-      <c r="C446" t="n">
-        <v>605858638891</v>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>605,858,638,891-a</t>
+        </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -20856,7 +20894,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>2571/600</t>
+          <t>2571/600-a</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -20906,7 +20944,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>2714/880</t>
+          <t>2714/880-a</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -20956,7 +20994,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>9769/9980</t>
+          <t>4903588269769-a</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -20996,7 +21034,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>9279/1140</t>
+          <t>4987072089279-3-a</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -21094,7 +21132,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>5742/935</t>
+          <t>5742/935-a</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -21144,7 +21182,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>3058/357</t>
+          <t>3058/357-a</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -21194,7 +21232,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>4051/514</t>
+          <t>4051/514-a</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -21244,7 +21282,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>4051/1542</t>
+          <t>4051/1542-a</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -21294,7 +21332,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>4051/1028</t>
+          <t>4051/1028-a</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -21380,7 +21418,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>6448/1892</t>
+          <t>4936201106448-4-a</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -21418,7 +21456,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>6448/1448</t>
+          <t>4936201106448-3-a</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -21506,7 +21544,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>0811/1200</t>
+          <t>0811/1200-a</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -21606,7 +21644,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>2225/577</t>
+          <t>2225/577-a</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -21906,7 +21944,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>6737/1094</t>
+          <t>6737/1094-a</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -21956,7 +21994,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>4613/768</t>
+          <t>4613/768-a</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -22156,7 +22194,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>6644/574</t>
+          <t>6644/574-a</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -22206,7 +22244,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>6637/630</t>
+          <t>4902111776637-a</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -22296,7 +22334,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>0148/18800</t>
+          <t>4987176180148-a</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -22336,7 +22374,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>0155/15540</t>
+          <t>0155/14800-a</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -22436,7 +22474,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>8404/484</t>
+          <t>8404/484-a</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -22476,7 +22514,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>8268/605</t>
+          <t>8268/605-a</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -22516,7 +22554,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>3927/1514</t>
+          <t>3927/1514-a</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -22566,7 +22604,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>3927/2271</t>
+          <t>4580632123927-3-a</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -22616,7 +22654,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>2223/438</t>
+          <t>2223/438-a</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -22666,7 +22704,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>2223/876</t>
+          <t>2223/876-a</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -22716,7 +22754,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>2223/1314</t>
+          <t>2223/1314-a</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -22766,7 +22804,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>1160/860</t>
+          <t>1160/860-a</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -22966,7 +23004,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>4490,7570/1999</t>
+          <t>4490,7570/1999-a</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -23016,7 +23054,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>4476,7556/1999</t>
+          <t>4476,7556/1999-a</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -23066,7 +23104,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>3530/1296</t>
+          <t>3530/1296-a</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -23106,7 +23144,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>3530/1296</t>
+          <t>3530/1296-a</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -23146,7 +23184,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>8060/29800</t>
+          <t>4987176248060-a</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -23186,7 +23224,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>3516/874</t>
+          <t>3516/874-a</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -23236,7 +23274,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>4299/1494</t>
+          <t>4902407024299-3-a</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -23286,7 +23324,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>4050,4043,4067/461</t>
+          <t>4050,4043,4067/461-a</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -23326,7 +23364,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>4050,4043,4067/461</t>
+          <t>4050,4043,4067/461-a</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -23366,7 +23404,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>4050,4043,4067/461</t>
+          <t>4050,4043,4067/461-a</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -23712,7 +23750,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>4147/1275</t>
+          <t>4147/1275-a</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -23750,7 +23788,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>6001/858</t>
+          <t>6001/858-a</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -23790,7 +23828,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>8974/942</t>
+          <t>8974/942-a</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -23840,7 +23878,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>8974/942</t>
+          <t>8974/942-a</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -23878,7 +23916,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>8998/942</t>
+          <t>8998/942-a</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -23918,7 +23956,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>9018/942</t>
+          <t>9018/942-a</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -23996,7 +24034,7 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>7410/19800</t>
+          <t>8720689027410-a</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -24232,8 +24270,10 @@
           <t>b0d46jfxtr</t>
         </is>
       </c>
-      <c r="C523" t="n">
-        <v>33800</v>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>33800-a</t>
+        </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -24270,7 +24310,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>8747/239</t>
+          <t>8747/239-a</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -24308,7 +24348,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>5183/2090</t>
+          <t>5183/2090-a</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -24346,7 +24386,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>5183/3135</t>
+          <t>5183/3135-a</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -24386,7 +24426,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>0071/109</t>
+          <t>0071/109-a</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -24424,7 +24464,7 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>7476/</t>
+          <t>7476-a</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -24714,7 +24754,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>5111/1941</t>
+          <t>4902407025111-3-a</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -24764,7 +24804,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>5111,5166/1300</t>
+          <t>AST-0002-a</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -24864,7 +24904,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>0007/980</t>
+          <t>0007/980-a</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -24904,7 +24944,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>1720/219</t>
+          <t>0633/599-a</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -25102,8 +25142,10 @@
           <t>b0db48cfg7</t>
         </is>
       </c>
-      <c r="C544" t="n">
-        <v>6910</v>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>4987176264206-a</t>
+        </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -25222,7 +25264,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>4794/1320</t>
+          <t>4903588274794-a</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -25322,7 +25364,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>8492/455</t>
+          <t>8492/455-a</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -25410,8 +25452,10 @@
           <t>b0dfcpljq7</t>
         </is>
       </c>
-      <c r="C551" t="n">
-        <v>858</v>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>858-a</t>
+        </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -25460,7 +25504,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>0715/17800</t>
+          <t>4549980880715</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -25510,7 +25554,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>1415/720</t>
+          <t>1415/828</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -25610,7 +25654,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>0635/1856</t>
+          <t>0659/1856</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -25708,7 +25752,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>3353/1254</t>
+          <t>3353/1254-a</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
@@ -25746,7 +25790,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>5234/1254</t>
+          <t>5234/1254-a</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -25784,7 +25828,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>0802/537</t>
+          <t>0802/537-a</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -25822,7 +25866,7 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>0703/1100</t>
+          <t>0703/1100-a</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -25860,7 +25904,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>0901//2450</t>
+          <t>0901//2450-a</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -25898,7 +25942,7 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>1205/688</t>
+          <t>1205/688-a</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -25936,7 +25980,7 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>1007/2312</t>
+          <t>1007/2312-a</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -25974,7 +26018,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>1106/1278</t>
+          <t>1106/1278-a</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
@@ -26192,7 +26236,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>1185/1152</t>
+          <t>1185/1152-a</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -26232,7 +26276,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>3814/1152</t>
+          <t>3814/1152-a</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -26282,7 +26326,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>1178/1152</t>
+          <t>1178/1152-a</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -26330,7 +26374,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>3698/972</t>
+          <t>3698/972-a</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -26370,7 +26414,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>9599/660</t>
+          <t>9599/660-a</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -26508,7 +26552,7 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>0979/695</t>
+          <t>0979/695-a</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -26546,7 +26590,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>0979/695</t>
+          <t>0979/695-a</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -26584,7 +26628,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>0979/695</t>
+          <t>0979/695-a</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -26622,7 +26666,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>0979/695</t>
+          <t>0979/695-a</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -26660,7 +26704,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>0979/695</t>
+          <t>0979/695-a</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -26698,7 +26742,7 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>0979/695</t>
+          <t>0979/695-a</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -26733,7 +26777,7 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>4571,1365,1369,1372/1619</t>
+          <t>4571,1365,1369,1372/1690-a</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -26919,8 +26963,10 @@
           <t>b0dmrwrwrd</t>
         </is>
       </c>
-      <c r="C586" t="n">
-        <v>380</v>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>4520699635674 -2</t>
+        </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -27404,7 +27450,7 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>6708/1884</t>
+          <t>6708/1884-a</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
@@ -27454,7 +27500,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>6708,6715/903,678</t>
+          <t>6708,6715/903,678-a</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -27502,7 +27548,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>4335/1100</t>
+          <t>4335/1100-a</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
@@ -27540,7 +27586,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>1088/770,1155</t>
+          <t>1088/770,1155-a</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
@@ -27580,7 +27626,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>1088/770,1155</t>
+          <t>1088/770,1155-a</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -27620,7 +27666,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>0154/550</t>
+          <t>4906456510154 -2-a</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -27658,7 +27704,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>2807/1280</t>
+          <t>2807/1280-a</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -27696,7 +27742,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>6163/250</t>
+          <t>6163/250-a</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -27734,7 +27780,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>6163/250</t>
+          <t>6163/250-a</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -27772,7 +27818,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>6163/250</t>
+          <t>6163/250-a</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -27808,8 +27854,10 @@
           <t>b0dpfkqck7</t>
         </is>
       </c>
-      <c r="C609" t="n">
-        <v>320</v>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>4520699635674 -2</t>
+        </is>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -27846,7 +27894,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>3172/616,924</t>
+          <t>3172/616,924-a</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -27884,7 +27932,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>3172/616,924</t>
+          <t>3172/616,924-a</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -27924,7 +27972,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>6959/876</t>
+          <t>4903301366959-2</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -27972,7 +28020,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>3585,3592/624</t>
+          <t>3608/624-a</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -28010,7 +28058,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>3608/624</t>
+          <t>3608/624-a</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -28048,7 +28096,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>3516/780</t>
+          <t>3530/780-a</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -28086,7 +28134,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>3530/780</t>
+          <t>3530/780-a</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -28176,7 +28224,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>6284/814</t>
+          <t>4987176286284-2</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -28226,7 +28274,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>6307/436</t>
+          <t>4987176286307-2</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -28322,8 +28370,10 @@
           <t>b0ds7s7p82</t>
         </is>
       </c>
-      <c r="C621" t="n">
-        <v>747690</v>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>747,690</t>
+        </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -28360,8 +28410,10 @@
           <t>b0ds7s7p82</t>
         </is>
       </c>
-      <c r="C622" t="n">
-        <v>747690</v>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>747,690</t>
+        </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -28398,8 +28450,10 @@
           <t>b0dsjb2627</t>
         </is>
       </c>
-      <c r="C623" t="n">
-        <v>29800</v>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>4987176283993-h-a</t>
+        </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -28488,7 +28542,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>8418/384</t>
+          <t>8418/384-a</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -28538,7 +28592,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>4019/1275</t>
+          <t>4901080224019-3-a</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -28588,7 +28642,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>4019/850</t>
+          <t>4901080224019-2-a</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -28728,7 +28782,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>0640/599</t>
+          <t>0640/599-a</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
@@ -28768,7 +28822,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>0633/599</t>
+          <t>0633/599-a</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
@@ -28808,7 +28862,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>4132/1098</t>
+          <t>4571263114132-2-a</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -28908,7 +28962,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>3532/3590</t>
+          <t>0194644233532</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -28958,7 +29012,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>6715/1356</t>
+          <t>6715/1356-a</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -29008,7 +29062,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>4533/2323</t>
+          <t>4533/2323-a</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -29058,7 +29112,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>6002/2563</t>
+          <t>6002/2563-a</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -29098,7 +29152,7 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>6033,6040/803,803</t>
+          <t>6033,6040/803,803-a</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
@@ -29138,7 +29192,7 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>6033,6040/803,803</t>
+          <t>6033,6040/803,803-a</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -29178,7 +29232,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>6170,6187/297,572</t>
+          <t>6170,6187/297,572-a</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -29218,7 +29272,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>6170,6187/297,572</t>
+          <t>6170,6187/297,572-a</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
@@ -29408,7 +29462,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>0955/7794</t>
+          <t>4547410550955-3</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -29508,7 +29562,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>1246/329</t>
+          <t>1246/329-a</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -29548,7 +29602,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>7484/1242</t>
+          <t>7484/1242-a</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
@@ -29641,8 +29695,10 @@
           <t>b0f2hpb231-1</t>
         </is>
       </c>
-      <c r="C650" t="n">
-        <v>1086</v>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>1086-a</t>
+        </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -29681,7 +29737,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>8832/549</t>
+          <t>4901417788832-a</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -29721,7 +29777,7 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>7409/396</t>
+          <t>7409/396-a</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -29771,7 +29827,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>M-0089/1599</t>
+          <t>M-0089/1599-a</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -29821,7 +29877,7 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>621,1148,1480,589,932,1216</t>
+          <t>621,1148,1480,589,932,1216-a</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -29871,7 +29927,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>621,1148,1480,589,932,1216</t>
+          <t>621,1148,1480,589,932,1216-a</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
@@ -29921,7 +29977,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>621,1148,1480,589,932,1216</t>
+          <t>621,1148,1480,589,932,1216-a</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
@@ -29971,7 +30027,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>621,1148,1480,589,932,1216</t>
+          <t>621,1148,1480,589,932,1216-a</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -30021,7 +30077,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>621,1148,1480,589,932,1216</t>
+          <t>621,1148,1480,589,932,1216-a</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -30071,7 +30127,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>621,1148,1480,589,932,1216</t>
+          <t>621,1148,1480,589,932,1216-a</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
@@ -30121,7 +30177,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>8187/1630</t>
+          <t>8187/1630-a</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -30161,7 +30217,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>1680/1319</t>
+          <t>4987176301680</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -30261,7 +30317,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>1604/1429</t>
+          <t>4987176301604</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
@@ -30301,7 +30357,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>1499/1242</t>
+          <t>4987176301499-2</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -30351,7 +30407,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>5664/3280</t>
+          <t>4987176305664-2</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -30391,7 +30447,7 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>5732/1538</t>
+          <t>4987176305732-2</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
@@ -30439,8 +30495,10 @@
           <t>b0f3d2l45v</t>
         </is>
       </c>
-      <c r="C667" t="n">
-        <v>720</v>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>5701/1116</t>
+        </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -30539,7 +30597,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>1543/1319</t>
+          <t>4987176301543</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -30629,7 +30687,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>8806/1239</t>
+          <t>8806/1239-a</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
@@ -30679,7 +30737,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>4421/1164</t>
+          <t>4901548604421-3-a</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
@@ -30917,7 +30975,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>7978/2126</t>
+          <t>7978/2126-a</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -30965,8 +31023,10 @@
           <t>b0f62x11z1</t>
         </is>
       </c>
-      <c r="C678" t="n">
-        <v>4987176278388</v>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>8388/1253</t>
+        </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -31065,7 +31125,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>2111/3500</t>
+          <t>2111/3500-a</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
@@ -31105,7 +31165,7 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>8892/494</t>
+          <t>4550432248892</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
@@ -31225,7 +31285,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>7514/1300</t>
+          <t>4533141407514-50</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -31275,7 +31335,7 @@
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>7514/2600</t>
+          <t>4533141407514-100</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -31325,7 +31385,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>7514/5200</t>
+          <t>4533141407514-200</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -31375,7 +31435,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>1630/1511</t>
+          <t>1630/1511-a</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -31425,7 +31485,7 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>9134/1316</t>
+          <t>9134/1316-a</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -31475,7 +31535,7 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>9103/788</t>
+          <t>9103/788-a</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -31525,7 +31585,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>9097/1096</t>
+          <t>9097/1096-a</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -31575,7 +31635,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>0142/2004</t>
+          <t>0142/2004-a</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -31618,8 +31678,10 @@
           <t>b0f9932wn7</t>
         </is>
       </c>
-      <c r="C692" t="n">
-        <v>1040</v>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>1040-a</t>
+        </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -31656,7 +31718,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>5861/235</t>
+          <t>5861/235-a</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -31694,7 +31756,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>5861/564</t>
+          <t>5861/564-a</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -31732,8 +31794,10 @@
           <t>b0fcb839t7</t>
         </is>
       </c>
-      <c r="C695" t="n">
-        <v>1170</v>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>1170-a</t>
+        </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -31765,8 +31829,10 @@
           <t>b0fcb8nrrt</t>
         </is>
       </c>
-      <c r="C696" t="n">
-        <v>785</v>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>785-a</t>
+        </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -31800,7 +31866,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>1161,1192,1178,1185/1152</t>
+          <t>1161,1192,1178,1185/1152-a</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
@@ -31840,7 +31906,7 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>1277/869</t>
+          <t>1277/869-a</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
@@ -31885,7 +31951,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>2526,2540,2533/1182</t>
+          <t>2526,2540,2533/1182-a</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
@@ -31918,8 +31984,10 @@
           <t>b0fdgc838r</t>
         </is>
       </c>
-      <c r="C700" t="n">
-        <v>1122</v>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>1122-a</t>
+        </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -31953,7 +32021,7 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>4712/1122</t>
+          <t>4712/1122-a</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -32026,7 +32094,7 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>3017/740</t>
+          <t>3017/740-a</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -32064,7 +32132,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>4737/2230</t>
+          <t>4549980884737-2-a</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -32097,8 +32165,10 @@
           <t>b0fh7137w6</t>
         </is>
       </c>
-      <c r="C705" t="n">
-        <v>3882</v>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>3882-a</t>
+        </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -32130,8 +32200,10 @@
           <t>b0fh715wj6</t>
         </is>
       </c>
-      <c r="C706" t="n">
-        <v>2588</v>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>2588-a</t>
+        </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -32163,8 +32235,10 @@
           <t>b0fj2hvbtl</t>
         </is>
       </c>
-      <c r="C707" t="n">
-        <v>830</v>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>830-a</t>
+        </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -32236,7 +32310,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>3516,3530,3523/874</t>
+          <t>3516,3530,3523/874-a</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
@@ -32276,7 +32350,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>0646,0653/504</t>
+          <t>0646,0653/504-a</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
@@ -32316,7 +32390,7 @@
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>0646,0653/504</t>
+          <t>0646,0653/504-a</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
@@ -32419,8 +32493,10 @@
           <t>b0fl6wtk7g</t>
         </is>
       </c>
-      <c r="C714" t="n">
-        <v>946</v>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>946-a</t>
+        </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -32457,7 +32533,7 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>6718/13480</t>
+          <t>6718/13480-a</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -32493,8 +32569,10 @@
           <t>b0fnm4k5lr</t>
         </is>
       </c>
-      <c r="C716" t="n">
-        <v>4512</v>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>4512-a</t>
+        </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -32683,7 +32761,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>0292/7907</t>
+          <t>0292/7907-a</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -33083,7 +33161,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>1131,1148,1155,1162,1179,1186</t>
+          <t>1131,1148,1155,1162,1179,1186-a</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -33123,7 +33201,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>1131,1148,1155,1162,1179,1186</t>
+          <t>1131,1148,1155,1162,1179,1186-a</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
@@ -33163,7 +33241,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>1131,1148,1155,1162,1179,1186</t>
+          <t>1131,1148,1155,1162,1179,1186-a</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -33203,7 +33281,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>1131,1148,1155,1162,1179,1186</t>
+          <t>1131,1148,1155,1162,1179,1186-a</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
@@ -33243,7 +33321,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>1131,1148,1155,1162,1179,1186</t>
+          <t>1131,1148,1155,1162,1179,1186-a</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
@@ -33283,7 +33361,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>1131,1148,1155,1162,1179,1186</t>
+          <t>1131,1148,1155,1162,1179,1186-a</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
@@ -33718,7 +33796,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>8485/835</t>
+          <t>8485/835-a</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
@@ -33753,7 +33831,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>3684,3707,3691,3714,3721/1672</t>
+          <t>3684,3707,3691,3714,3721/1338-a</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
@@ -33788,7 +33866,7 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>7704,7711/650</t>
+          <t>AST-0003-a</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
@@ -33828,7 +33906,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>6897/39800</t>
+          <t>6897/39800-a</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
@@ -33914,7 +33992,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>6104/1320</t>
+          <t>4932804366104-2-a</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
@@ -33952,7 +34030,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>0445/1100</t>
+          <t>4901477100445-2-a</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
@@ -33992,7 +34070,7 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>1208,3632/1394</t>
+          <t>1208,3632/1394-a</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
@@ -34192,7 +34270,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>2220,2237,2244,2251/1148</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
@@ -34232,7 +34310,7 @@
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>2220,2237,2244,2251/1148</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
@@ -34272,7 +34350,7 @@
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>2220,2237,2244,2251/1148</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
@@ -34312,7 +34390,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>2220,2237,2244,2251/1148</t>
+          <t>2220,2237,2244,2251/4592-a</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
@@ -34464,8 +34542,10 @@
           <t>b0gsqcp1mx-a</t>
         </is>
       </c>
-      <c r="C760" t="n">
-        <v>2000</v>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>2220,2237,2244,2251/4592-a</t>
+        </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -34504,7 +34584,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>2220,2237,2244,2251/4592</t>
+          <t>2220,2237,2244,2251/4592-a</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
@@ -34924,7 +35004,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>9656,8703/1584</t>
+          <t>9656,8703/1584-a</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
@@ -35087,6 +35167,11 @@
           <t>br-0001</t>
         </is>
       </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>BR-0001-a</t>
+        </is>
+      </c>
       <c r="D774" t="inlineStr">
         <is>
           <t>B0CB648B93</t>
@@ -35122,6 +35207,11 @@
           <t>br-0001</t>
         </is>
       </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>BR-0001-a</t>
+        </is>
+      </c>
       <c r="D775" t="inlineStr">
         <is>
           <t>B0CB65C7W3</t>
@@ -35157,6 +35247,11 @@
           <t>br-0001</t>
         </is>
       </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>BR-0001-a</t>
+        </is>
+      </c>
       <c r="D776" t="inlineStr">
         <is>
           <t>B0CB65N8RC</t>
@@ -35192,6 +35287,11 @@
           <t>br-0001</t>
         </is>
       </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>BR-0001-a</t>
+        </is>
+      </c>
       <c r="D777" t="inlineStr">
         <is>
           <t>B0CB65SGYG</t>
@@ -35227,6 +35327,11 @@
           <t>br-0001</t>
         </is>
       </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>BR-0001-a</t>
+        </is>
+      </c>
       <c r="D778" t="inlineStr">
         <is>
           <t>B0CB68MNFL</t>
@@ -35260,6 +35365,11 @@
       <c r="B779" t="inlineStr">
         <is>
           <t>br-0001</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>BR-0001-a</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
@@ -35367,7 +35477,7 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>8902,8919/1682</t>
+          <t>set-0002-a</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">

--- a/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
+++ b/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
@@ -77,7 +77,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -108,6 +108,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -189,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -234,6 +239,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1431,76 +1437,80 @@
       </c>
     </row>
     <row r="25" ht="13.5" customHeight="1">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>4550391012718</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="28" t="n">
         <v>4550391012718</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t>2787,2794,2800,2817,2824/2088-a</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="28" t="n">
         <v>4550391012718</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="28" t="inlineStr">
         <is>
           <t>【全6種セット】【正規品】クーリア ぷちぷにらいふしーる 6種セット がーりーらいふ ゆにらいふ はぴはむらいふ えながらいふ ぱんらいふ きゃわうさらいふ シールセット ぷっくりシール 立体シール デコシール 手帳デコ トレカデコ スマホデコ ぷちぷに ボンボンドロップ</t>
         </is>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="28" t="n">
         <v>1980</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" s="28" t="n">
         <v>768</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="28">
         <f>SUM(G25*H25)</f>
         <v/>
       </c>
+      <c r="J25" s="28" t="n"/>
+      <c r="K25" s="28" t="n"/>
     </row>
     <row r="26" ht="13.5" customHeight="1">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>4550391012718</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="28" t="n">
         <v>4550391012787</v>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="28" t="inlineStr">
         <is>
           <t>2787,2794,2800,2817,2824/2088-a</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="28" t="n">
         <v>4550391012718</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="28" t="inlineStr">
         <is>
           <t>【全6種セット】クーリア キラキラシールバインダー リボンA リボンB デイジーA デイジーB ハートA ハートB シール収納 ステッカー収納 バインダー コレクトブック 推し活 トレカ収納 デコ コレクション 文房具 かわいい 女の子向け プレゼント ギフト クーリア まとめ買い</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="28" t="n">
         <v>5980</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" s="28" t="n">
         <v>2088</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="28">
         <f>SUM(G26*H26)</f>
         <v/>
       </c>
+      <c r="J26" s="28" t="n"/>
+      <c r="K26" s="28" t="n"/>
     </row>
     <row r="27" ht="13.5" customHeight="1">
       <c r="A27" t="inlineStr">
@@ -2123,76 +2133,80 @@
       </c>
     </row>
     <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="28" t="inlineStr">
         <is>
           <t>4550451352129</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" s="28" t="n">
         <v>4550451352129</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="28" t="inlineStr">
         <is>
           <t>2129,2167/1210</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="28" t="n">
         <v>4550451352129</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="28" t="inlineStr">
         <is>
           <t>【セット品】サンリオ コットンパフィーシール 3種セット マイメロディ クロミ シナモロール ハローキティ レオパード クラックス COTTON PUFFY ぷっくりシール デコシール 手帳デコ ノートデコ キャラクターシール 文房具 ステッカー アソートセット シール 立体 かわいい</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="28" t="n">
         <v>4480</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44" s="28" t="n">
         <v>605</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="28">
         <f>SUM(G44*H44)</f>
         <v/>
       </c>
+      <c r="J44" s="28" t="n"/>
+      <c r="K44" s="28" t="n"/>
     </row>
     <row r="45" ht="13.5" customHeight="1">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="28" t="inlineStr">
         <is>
           <t>4550451352129</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" s="28" t="n">
         <v>4550451352167</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="28" t="inlineStr">
         <is>
           <t>2129,2167/1210</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="28" t="n">
         <v>4550451352129</v>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="28" t="inlineStr">
         <is>
           <t>【セット品】サンリオ コットンパフィーシール 2種セット マイメロディ クロミ ハローキティ レオパード クラックス COTTON PUFFY ぷっくりシール デコシール 手帳デコ ノートデコ キャラクターシール 文房具 ステッカー アソートセット シール 立体 かわいい</t>
         </is>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="28" t="n">
         <v>3080</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45" s="28" t="n">
         <v>605</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="28">
         <f>SUM(G45*H45)</f>
         <v/>
       </c>
+      <c r="J45" s="28" t="n"/>
+      <c r="K45" s="28" t="n"/>
     </row>
     <row r="46" ht="13.5" customHeight="1">
       <c r="A46" t="inlineStr">
@@ -17196,100 +17210,100 @@
       </c>
     </row>
     <row r="365" ht="13.5" customHeight="1">
-      <c r="A365" t="inlineStr">
+      <c r="A365" s="28" t="inlineStr">
         <is>
           <t>9000326168003</t>
         </is>
       </c>
-      <c r="B365" t="inlineStr">
+      <c r="B365" s="28" t="inlineStr">
         <is>
           <t>b0bltqq367</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr">
+      <c r="C365" s="28" t="inlineStr">
         <is>
           <t>4901133415722-6</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr">
+      <c r="D365" s="28" t="inlineStr">
         <is>
           <t>b0bltqq367</t>
         </is>
       </c>
-      <c r="E365" t="inlineStr">
+      <c r="E365" s="28" t="inlineStr">
         <is>
           <t>いなば チャオ(CIAO)ちゅ～るごはん とりささみ 総合栄養食 14g×4P ６袋セット 猫 猫用 おやつ 国産 液状 キャットフード 人気 グレインフリー</t>
         </is>
       </c>
-      <c r="F365" t="n">
+      <c r="F365" s="28" t="n">
         <v>1780</v>
       </c>
-      <c r="G365" t="n">
+      <c r="G365" s="28" t="n">
         <v>970</v>
       </c>
-      <c r="H365" t="n">
+      <c r="H365" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="I365">
+      <c r="I365" s="28">
         <f>SUM(G365*H365)</f>
         <v/>
       </c>
-      <c r="J365" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K365" t="inlineStr">
+      <c r="J365" s="28" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K365" s="28" t="inlineStr">
         <is>
           <t>9000326168003</t>
         </is>
       </c>
     </row>
     <row r="366" ht="13.5" customHeight="1">
-      <c r="A366" t="inlineStr">
+      <c r="A366" s="28" t="inlineStr">
         <is>
           <t>9000326168003</t>
         </is>
       </c>
-      <c r="B366" t="inlineStr">
+      <c r="B366" s="28" t="inlineStr">
         <is>
           <t>b0bltqq367-1</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr">
+      <c r="C366" s="28" t="inlineStr">
         <is>
           <t>4901133415722-6</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr">
+      <c r="D366" s="28" t="inlineStr">
         <is>
           <t>b0bltqq367</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr">
+      <c r="E366" s="28" t="inlineStr">
         <is>
           <t>いなば チャオ(CIAO)ちゅ～るごはん とりささみ 総合栄養食 14g×4P 4袋セット 猫 猫用 おやつ 国産 液状 キャットフード 人気 グレインフリー</t>
         </is>
       </c>
-      <c r="F366" t="n">
+      <c r="F366" s="28" t="n">
         <v>1080</v>
       </c>
-      <c r="G366" t="n">
+      <c r="G366" s="28" t="n">
         <v>580</v>
       </c>
-      <c r="H366" t="n">
+      <c r="H366" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="I366">
+      <c r="I366" s="28">
         <f>SUM(G366*H366)</f>
         <v/>
       </c>
-      <c r="J366" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K366" t="inlineStr">
+      <c r="J366" s="28" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K366" s="28" t="inlineStr">
         <is>
           <t>9000326168003</t>
         </is>
@@ -24932,44 +24946,46 @@
       </c>
     </row>
     <row r="539" ht="13.5" customHeight="1">
-      <c r="A539" t="inlineStr">
+      <c r="A539" s="28" t="inlineStr">
         <is>
           <t>4901301420633</t>
         </is>
       </c>
-      <c r="B539" t="inlineStr">
+      <c r="B539" s="28" t="inlineStr">
         <is>
           <t>b0d9znvl7q</t>
         </is>
       </c>
-      <c r="C539" t="inlineStr">
+      <c r="C539" s="28" t="inlineStr">
         <is>
           <t>0633/599-a</t>
         </is>
       </c>
-      <c r="D539" t="inlineStr">
+      <c r="D539" s="28" t="inlineStr">
         <is>
           <t>B0DV57G9Z1</t>
         </is>
       </c>
-      <c r="E539" t="inlineStr">
+      <c r="E539" s="28" t="inlineStr">
         <is>
           <t>花王 フレアフレグランス ハミングフレア リッチフローラル 本体 520ml 部屋干し 雨の日 部屋 かろやか 香る きれい 清潔 衣類 静電気 防臭 抗菌 赤ちゃん ベビー 洗濯</t>
         </is>
       </c>
-      <c r="F539" t="n">
+      <c r="F539" s="28" t="n">
         <v>1280</v>
       </c>
-      <c r="G539" t="n">
+      <c r="G539" s="28" t="n">
         <v>219</v>
       </c>
-      <c r="H539" t="n">
+      <c r="H539" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="I539">
+      <c r="I539" s="28">
         <f>SUM(G539*H539)</f>
         <v/>
       </c>
+      <c r="J539" s="28" t="n"/>
+      <c r="K539" s="28" t="n"/>
     </row>
     <row r="540" ht="13.5" customHeight="1">
       <c r="A540" t="inlineStr">
@@ -25642,50 +25658,50 @@
       </c>
     </row>
     <row r="555" ht="13.5" customHeight="1">
-      <c r="A555" t="inlineStr">
+      <c r="A555" s="28" t="inlineStr">
         <is>
           <t>4987176260635</t>
         </is>
       </c>
-      <c r="B555" t="inlineStr">
+      <c r="B555" s="28" t="inlineStr">
         <is>
           <t>b0dfyjnwjt</t>
         </is>
       </c>
-      <c r="C555" t="inlineStr">
+      <c r="C555" s="28" t="inlineStr">
         <is>
           <t>0659/1856</t>
         </is>
       </c>
-      <c r="D555" t="inlineStr">
+      <c r="D555" s="28" t="inlineStr">
         <is>
           <t>b0dfyjnwjt</t>
         </is>
       </c>
-      <c r="E555" t="inlineStr">
+      <c r="E555" s="28" t="inlineStr">
         <is>
           <t>レノア リセット セラム ホワイトリリーの香り つめかえ 特大 750mL×2個セット 柔軟剤 部屋干し 雨の日 部屋 かろやか 香る きれい 清潔 衣類 静電気 防臭 抗菌 赤ちゃん ベビー 洗濯</t>
         </is>
       </c>
-      <c r="F555" t="n">
+      <c r="F555" s="28" t="n">
         <v>2980</v>
       </c>
-      <c r="G555" t="n">
+      <c r="G555" s="28" t="n">
         <v>1856</v>
       </c>
-      <c r="H555" t="n">
+      <c r="H555" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="I555">
+      <c r="I555" s="28">
         <f>SUM(G555*H555)</f>
         <v/>
       </c>
-      <c r="J555" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K555" t="inlineStr">
+      <c r="J555" s="28" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K555" s="28" t="inlineStr">
         <is>
           <t>4987176260635</t>
         </is>
@@ -26805,50 +26821,50 @@
       </c>
     </row>
     <row r="583" ht="13.5" customHeight="1">
-      <c r="A583" t="inlineStr">
+      <c r="A583" s="28" t="inlineStr">
         <is>
           <t>4987176260635</t>
         </is>
       </c>
-      <c r="B583" t="inlineStr">
+      <c r="B583" s="28" t="inlineStr">
         <is>
           <t>b0dktchdgk</t>
         </is>
       </c>
-      <c r="C583" t="inlineStr">
+      <c r="C583" s="28" t="inlineStr">
         <is>
           <t>0659/1856</t>
         </is>
       </c>
-      <c r="D583" t="inlineStr">
+      <c r="D583" s="28" t="inlineStr">
         <is>
           <t>b0dfyjnwjt</t>
         </is>
       </c>
-      <c r="E583" t="inlineStr">
+      <c r="E583" s="28" t="inlineStr">
         <is>
           <t>レノア リセット セラム ホワイトピーチ&amp;カモミールの香り つめかえ 特大 750mL×2個セット 柔軟剤 部屋干し 雨の日 部屋 かろやか 香る きれい 清潔 衣類 静電気 防臭 抗菌 赤ちゃん ベビー 洗濯</t>
         </is>
       </c>
-      <c r="F583" t="n">
+      <c r="F583" s="28" t="n">
         <v>2980</v>
       </c>
-      <c r="G583" t="n">
+      <c r="G583" s="28" t="n">
         <v>1856</v>
       </c>
-      <c r="H583" t="n">
+      <c r="H583" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="I583">
+      <c r="I583" s="28">
         <f>SUM(G583*H583)</f>
         <v/>
       </c>
-      <c r="J583" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K583" t="inlineStr">
+      <c r="J583" s="28" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K583" s="28" t="inlineStr">
         <is>
           <t>4987176260635</t>
         </is>
@@ -26955,42 +26971,44 @@
       </c>
     </row>
     <row r="586" ht="13.5" customHeight="1">
-      <c r="A586" t="n">
+      <c r="A586" s="28" t="n">
         <v>4520699694367</v>
       </c>
-      <c r="B586" t="inlineStr">
+      <c r="B586" s="28" t="inlineStr">
         <is>
           <t>b0dmrwrwrd</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr">
+      <c r="C586" s="28" t="inlineStr">
         <is>
           <t>4520699635674 -2</t>
         </is>
       </c>
-      <c r="D586" t="inlineStr">
+      <c r="D586" s="28" t="inlineStr">
         <is>
           <t>b0dmrwrwrd</t>
         </is>
       </c>
-      <c r="E586" t="inlineStr">
+      <c r="E586" s="28" t="inlineStr">
         <is>
           <t>【セット品】銀のスプーン 三ツ星グルメ にっぽんSelect とろリッチ 2種のお魚味アソート 48g（6g×8本）×2コ 総合栄養食</t>
         </is>
       </c>
-      <c r="F586" t="n">
+      <c r="F586" s="28" t="n">
         <v>799</v>
       </c>
-      <c r="G586" t="n">
+      <c r="G586" s="28" t="n">
         <v>380</v>
       </c>
-      <c r="H586" t="n">
+      <c r="H586" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="I586">
+      <c r="I586" s="28">
         <f>SUM(G586*H586)</f>
         <v/>
       </c>
+      <c r="J586" s="28" t="n"/>
+      <c r="K586" s="28" t="n"/>
     </row>
     <row r="587" ht="13.5" customHeight="1">
       <c r="A587" t="inlineStr">
@@ -27846,42 +27864,44 @@
       </c>
     </row>
     <row r="609" ht="13.5" customHeight="1">
-      <c r="A609" t="n">
+      <c r="A609" s="28" t="n">
         <v>4520699635674</v>
       </c>
-      <c r="B609" t="inlineStr">
+      <c r="B609" s="28" t="inlineStr">
         <is>
           <t>b0dpfkqck7</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr">
+      <c r="C609" s="28" t="inlineStr">
         <is>
           <t>4520699635674 -2</t>
         </is>
       </c>
-      <c r="D609" t="inlineStr">
+      <c r="D609" s="28" t="inlineStr">
         <is>
           <t>b0dmrwrwrd</t>
         </is>
       </c>
-      <c r="E609" t="inlineStr">
+      <c r="E609" s="28" t="inlineStr">
         <is>
           <t>【セット品】銀のスプーン 三ツ星グルメ にっぽんSelect とろリッチ 2種のアソート 48g（6g×8本）×2コ</t>
         </is>
       </c>
-      <c r="F609" t="n">
+      <c r="F609" s="28" t="n">
         <v>799</v>
       </c>
-      <c r="G609" t="n">
+      <c r="G609" s="28" t="n">
         <v>320</v>
       </c>
-      <c r="H609" t="n">
+      <c r="H609" s="28" t="n">
         <v>10</v>
       </c>
-      <c r="I609">
+      <c r="I609" s="28">
         <f>SUM(G609*H609)</f>
         <v/>
       </c>
+      <c r="J609" s="28" t="n"/>
+      <c r="K609" s="28" t="n"/>
     </row>
     <row r="610" ht="13.5" customHeight="1">
       <c r="A610" t="n">
@@ -28010,156 +28030,164 @@
       </c>
     </row>
     <row r="613" ht="13.5" customHeight="1">
-      <c r="A613" t="n">
+      <c r="A613" s="28" t="n">
         <v>4970501033592</v>
       </c>
-      <c r="B613" t="inlineStr">
+      <c r="B613" s="28" t="inlineStr">
         <is>
           <t>b0dq7vk36r</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr">
+      <c r="C613" s="28" t="inlineStr">
         <is>
           <t>3608/624-a</t>
         </is>
       </c>
-      <c r="D613" t="inlineStr">
+      <c r="D613" s="28" t="inlineStr">
         <is>
           <t>b0dq7vk36r</t>
         </is>
       </c>
-      <c r="E613" t="inlineStr">
+      <c r="E613" s="28" t="inlineStr">
         <is>
           <t>【セット品】デビフ おさんぽくん 犬 おやつ 60g(15g×4袋)×4袋セット ササミ 鶏肉 レバー 国産 犬用おやつ 小分け ご褒美 トレーニング 散歩 dbf アソート</t>
         </is>
       </c>
-      <c r="F613" t="n">
+      <c r="F613" s="28" t="n">
         <v>1480</v>
       </c>
-      <c r="G613" t="n">
+      <c r="G613" s="28" t="n">
         <v>624</v>
       </c>
-      <c r="H613" t="n">
+      <c r="H613" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="I613">
+      <c r="I613" s="28">
         <f>SUM(G613*H613)</f>
         <v/>
       </c>
+      <c r="J613" s="28" t="n"/>
+      <c r="K613" s="28" t="n"/>
     </row>
     <row r="614" ht="13.5" customHeight="1">
-      <c r="A614" t="n">
+      <c r="A614" s="28" t="n">
         <v>4970501033608</v>
       </c>
-      <c r="B614" t="inlineStr">
+      <c r="B614" s="28" t="inlineStr">
         <is>
           <t>b0dq7zx95d</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr">
+      <c r="C614" s="28" t="inlineStr">
         <is>
           <t>3608/624-a</t>
         </is>
       </c>
-      <c r="D614" t="inlineStr">
+      <c r="D614" s="28" t="inlineStr">
         <is>
           <t>b0dq7vk36r</t>
         </is>
       </c>
-      <c r="E614" t="inlineStr">
+      <c r="E614" s="28" t="inlineStr">
         <is>
           <t>【4個セット】デビフ おさんぽくん ササミ シニア犬用 60g（15g×4袋）×4袋セット 犬 おやつ 国産 小分け 高齢犬 シニア犬 ごほうび トレーニング 散歩 携帯用 おやつ 犬用スナック</t>
         </is>
       </c>
-      <c r="F614" t="n">
+      <c r="F614" s="28" t="n">
         <v>1480</v>
       </c>
-      <c r="G614" t="n">
+      <c r="G614" s="28" t="n">
         <v>624</v>
       </c>
-      <c r="H614" t="n">
+      <c r="H614" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="I614">
+      <c r="I614" s="28">
         <f>SUM(G614*H614)</f>
         <v/>
       </c>
+      <c r="J614" s="28" t="n"/>
+      <c r="K614" s="28" t="n"/>
     </row>
     <row r="615" ht="13.5" customHeight="1">
-      <c r="A615" t="n">
+      <c r="A615" s="28" t="n">
         <v>4970501033516</v>
       </c>
-      <c r="B615" t="inlineStr">
+      <c r="B615" s="28" t="inlineStr">
         <is>
           <t>b0dq83k574</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr">
+      <c r="C615" s="28" t="inlineStr">
         <is>
           <t>3530/780-a</t>
         </is>
       </c>
-      <c r="D615" t="inlineStr">
+      <c r="D615" s="28" t="inlineStr">
         <is>
           <t>b0dq889rzt</t>
         </is>
       </c>
-      <c r="E615" t="inlineStr">
+      <c r="E615" s="28" t="inlineStr">
         <is>
           <t>デビフ おすわりくん ササミ ７５ｇ ×４袋セット 犬用 おやつ</t>
         </is>
       </c>
-      <c r="F615" t="n">
+      <c r="F615" s="28" t="n">
         <v>1280</v>
       </c>
-      <c r="G615" t="n">
+      <c r="G615" s="28" t="n">
         <v>780</v>
       </c>
-      <c r="H615" t="n">
+      <c r="H615" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="I615">
+      <c r="I615" s="28">
         <f>SUM(G615*H615)</f>
         <v/>
       </c>
+      <c r="J615" s="28" t="n"/>
+      <c r="K615" s="28" t="n"/>
     </row>
     <row r="616" ht="13.5" customHeight="1">
-      <c r="A616" t="n">
+      <c r="A616" s="28" t="n">
         <v>4970501033530</v>
       </c>
-      <c r="B616" t="inlineStr">
+      <c r="B616" s="28" t="inlineStr">
         <is>
           <t>b0dq889rzt</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr">
+      <c r="C616" s="28" t="inlineStr">
         <is>
           <t>3530/780-a</t>
         </is>
       </c>
-      <c r="D616" t="inlineStr">
+      <c r="D616" s="28" t="inlineStr">
         <is>
           <t>b0dq889rzt</t>
         </is>
       </c>
-      <c r="E616" t="inlineStr">
+      <c r="E616" s="28" t="inlineStr">
         <is>
           <t>デビフ おすわりくん 超小粒 ササミ ７５ｇ ×４袋セット 犬用 おやつ</t>
         </is>
       </c>
-      <c r="F616" t="n">
+      <c r="F616" s="28" t="n">
         <v>1280</v>
       </c>
-      <c r="G616" t="n">
+      <c r="G616" s="28" t="n">
         <v>780</v>
       </c>
-      <c r="H616" t="n">
+      <c r="H616" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="I616">
+      <c r="I616" s="28">
         <f>SUM(G616*H616)</f>
         <v/>
       </c>
+      <c r="J616" s="28" t="n"/>
+      <c r="K616" s="28" t="n"/>
     </row>
     <row r="617" ht="13.5" customHeight="1">
       <c r="A617" t="inlineStr">
@@ -28810,44 +28838,46 @@
       </c>
     </row>
     <row r="631" ht="13.5" customHeight="1">
-      <c r="A631" t="inlineStr">
+      <c r="A631" s="28" t="inlineStr">
         <is>
           <t>4901301420633</t>
         </is>
       </c>
-      <c r="B631" t="inlineStr">
+      <c r="B631" s="28" t="inlineStr">
         <is>
           <t>b0dv57g9z1</t>
         </is>
       </c>
-      <c r="C631" t="inlineStr">
+      <c r="C631" s="28" t="inlineStr">
         <is>
           <t>0633/599-a</t>
         </is>
       </c>
-      <c r="D631" t="inlineStr">
+      <c r="D631" s="28" t="inlineStr">
         <is>
           <t>B0DV57G9Z1</t>
         </is>
       </c>
-      <c r="E631" t="inlineStr">
+      <c r="E631" s="28" t="inlineStr">
         <is>
           <t>花王 ハミングフレア フレアフレグランス フローラル＆スウィート2L 詰め替え 420633 部屋干し 雨の日 部屋 かろやか 香る きれい 清潔 衣類 静電気 防臭 抗菌 赤ちゃん ベビー 洗濯</t>
         </is>
       </c>
-      <c r="F631" t="n">
+      <c r="F631" s="28" t="n">
         <v>2178</v>
       </c>
-      <c r="G631" t="n">
+      <c r="G631" s="28" t="n">
         <v>598</v>
       </c>
-      <c r="H631" t="n">
+      <c r="H631" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="I631">
+      <c r="I631" s="28">
         <f>SUM(G631*H631)</f>
         <v/>
       </c>
+      <c r="J631" s="28" t="n"/>
+      <c r="K631" s="28" t="n"/>
     </row>
     <row r="632" ht="13.5" customHeight="1">
       <c r="A632" t="inlineStr">
@@ -30485,100 +30515,100 @@
       </c>
     </row>
     <row r="667" ht="13.5" customHeight="1">
-      <c r="A667" t="inlineStr">
+      <c r="A667" s="28" t="inlineStr">
         <is>
           <t>4987176305701</t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
+      <c r="B667" s="28" t="inlineStr">
         <is>
           <t>b0f3d2l45v</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr">
+      <c r="C667" s="28" t="inlineStr">
         <is>
           <t>5701/1116</t>
         </is>
       </c>
-      <c r="D667" t="inlineStr">
+      <c r="D667" s="28" t="inlineStr">
         <is>
           <t>b0f3d2l45v</t>
         </is>
       </c>
-      <c r="E667" t="inlineStr">
+      <c r="E667" s="28" t="inlineStr">
         <is>
           <t>ファブリーズ 消臭スプレー PREMIUM パステルフローラル＆ブロッサムの香り 布用 詰め替え 特大 610mL 除菌 P&amp;Gジャパン</t>
         </is>
       </c>
-      <c r="F667" t="n">
+      <c r="F667" s="28" t="n">
         <v>1580</v>
       </c>
-      <c r="G667" t="n">
+      <c r="G667" s="28" t="n">
         <v>720</v>
       </c>
-      <c r="H667" t="n">
+      <c r="H667" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="I667">
+      <c r="I667" s="28">
         <f>SUM(G667*H667)</f>
         <v/>
       </c>
-      <c r="J667" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K667" t="inlineStr">
+      <c r="J667" s="28" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K667" s="28" t="inlineStr">
         <is>
           <t>4987176305701</t>
         </is>
       </c>
     </row>
     <row r="668" ht="13.5" customHeight="1">
-      <c r="A668" t="inlineStr">
+      <c r="A668" s="28" t="inlineStr">
         <is>
           <t>4987176305701</t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
+      <c r="B668" s="28" t="inlineStr">
         <is>
           <t>b0f3d2l45v-1</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr">
+      <c r="C668" s="28" t="inlineStr">
         <is>
           <t>5701/1116</t>
         </is>
       </c>
-      <c r="D668" t="inlineStr">
+      <c r="D668" s="28" t="inlineStr">
         <is>
           <t>b0f3d2l45v</t>
         </is>
       </c>
-      <c r="E668" t="inlineStr">
+      <c r="E668" s="28" t="inlineStr">
         <is>
           <t>ファブリーズ 消臭スプレー PREMIUM パステルフローラル＆ブロッサムの香り 布用 詰め替え 特大 610mL×2 除菌 P&amp;Gジャパン</t>
         </is>
       </c>
-      <c r="F668" t="n">
+      <c r="F668" s="28" t="n">
         <v>2480</v>
       </c>
-      <c r="G668" t="n">
+      <c r="G668" s="28" t="n">
         <v>1116</v>
       </c>
-      <c r="H668" t="n">
+      <c r="H668" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="I668">
+      <c r="I668" s="28">
         <f>SUM(G668*H668)</f>
         <v/>
       </c>
-      <c r="J668" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K668" t="inlineStr">
+      <c r="J668" s="28" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K668" s="28" t="inlineStr">
         <is>
           <t>4987176305701</t>
         </is>
@@ -32849,300 +32879,300 @@
       </c>
     </row>
     <row r="722" ht="13.5" customHeight="1">
-      <c r="A722" t="inlineStr">
+      <c r="A722" s="28" t="inlineStr">
         <is>
           <t>4550391912131</t>
         </is>
       </c>
-      <c r="B722" t="inlineStr">
+      <c r="B722" s="28" t="inlineStr">
         <is>
           <t>b0frs8pb58</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr">
+      <c r="C722" s="28" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D722" t="inlineStr">
+      <c r="D722" s="28" t="inlineStr">
         <is>
           <t>B0DVSV4W6Q-2131</t>
         </is>
       </c>
-      <c r="E722" t="inlineStr">
+      <c r="E722" s="28" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + しずくちゃんシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F722" t="n">
+      <c r="F722" s="28" t="n">
         <v>3980</v>
       </c>
-      <c r="G722" t="n">
+      <c r="G722" s="28" t="n">
         <v>1133</v>
       </c>
-      <c r="H722" t="n">
+      <c r="H722" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I722">
+      <c r="I722" s="28">
         <f>SUM(G722*H722)</f>
         <v/>
       </c>
-      <c r="J722" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K722" t="inlineStr">
+      <c r="J722" s="28" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K722" s="28" t="inlineStr">
         <is>
           <t>4550391912131</t>
         </is>
       </c>
     </row>
     <row r="723" ht="13.5" customHeight="1">
-      <c r="A723" t="inlineStr">
+      <c r="A723" s="28" t="inlineStr">
         <is>
           <t>4550391912094</t>
         </is>
       </c>
-      <c r="B723" t="inlineStr">
+      <c r="B723" s="28" t="inlineStr">
         <is>
           <t>b0frs8pb58</t>
         </is>
       </c>
-      <c r="C723" t="inlineStr">
+      <c r="C723" s="28" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D723" t="inlineStr">
+      <c r="D723" s="28" t="inlineStr">
         <is>
           <t>B0DVSW1YS7-2094</t>
         </is>
       </c>
-      <c r="E723" t="inlineStr">
+      <c r="E723" s="28" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + しずくちゃんシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F723" t="n">
+      <c r="F723" s="28" t="n">
         <v>3980</v>
       </c>
-      <c r="G723" t="n">
+      <c r="G723" s="28" t="n">
         <v>1133</v>
       </c>
-      <c r="H723" t="n">
+      <c r="H723" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I723">
+      <c r="I723" s="28">
         <f>SUM(G723*H723)</f>
         <v/>
       </c>
-      <c r="J723" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K723" t="inlineStr">
+      <c r="J723" s="28" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K723" s="28" t="inlineStr">
         <is>
           <t>4550391912094</t>
         </is>
       </c>
     </row>
     <row r="724" ht="13.5" customHeight="1">
-      <c r="A724" t="inlineStr">
+      <c r="A724" s="28" t="inlineStr">
         <is>
           <t>4550391011469</t>
         </is>
       </c>
-      <c r="B724" t="inlineStr">
+      <c r="B724" s="28" t="inlineStr">
         <is>
           <t>b0frs8pb58</t>
         </is>
       </c>
-      <c r="C724" t="inlineStr">
+      <c r="C724" s="28" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D724" t="inlineStr">
+      <c r="D724" s="28" t="inlineStr">
         <is>
           <t>B0FRS8PB58-1469</t>
         </is>
       </c>
-      <c r="E724" t="inlineStr">
+      <c r="E724" s="28" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + しずくちゃんシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F724" t="n">
+      <c r="F724" s="28" t="n">
         <v>3980</v>
       </c>
-      <c r="G724" t="n">
+      <c r="G724" s="28" t="n">
         <v>1133</v>
       </c>
-      <c r="H724" t="n">
+      <c r="H724" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I724">
+      <c r="I724" s="28">
         <f>SUM(G724*H724)</f>
         <v/>
       </c>
-      <c r="J724" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K724" t="inlineStr">
+      <c r="J724" s="28" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K724" s="28" t="inlineStr">
         <is>
           <t>4550391011469</t>
         </is>
       </c>
     </row>
     <row r="725" ht="13.5" customHeight="1">
-      <c r="A725" t="inlineStr">
+      <c r="A725" s="28" t="inlineStr">
         <is>
           <t>4550391011360</t>
         </is>
       </c>
-      <c r="B725" t="inlineStr">
+      <c r="B725" s="28" t="inlineStr">
         <is>
           <t>b0frs8pb58</t>
         </is>
       </c>
-      <c r="C725" t="inlineStr">
+      <c r="C725" s="28" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D725" t="inlineStr">
+      <c r="D725" s="28" t="inlineStr">
         <is>
           <t>B0FRS8X8M7-1360</t>
         </is>
       </c>
-      <c r="E725" t="inlineStr">
+      <c r="E725" s="28" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + しずくちゃんシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F725" t="n">
+      <c r="F725" s="28" t="n">
         <v>3980</v>
       </c>
-      <c r="G725" t="n">
+      <c r="G725" s="28" t="n">
         <v>1133</v>
       </c>
-      <c r="H725" t="n">
+      <c r="H725" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I725">
+      <c r="I725" s="28">
         <f>SUM(G725*H725)</f>
         <v/>
       </c>
-      <c r="J725" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K725" t="inlineStr">
+      <c r="J725" s="28" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K725" s="28" t="inlineStr">
         <is>
           <t>4550391011360</t>
         </is>
       </c>
     </row>
     <row r="726" ht="13.5" customHeight="1">
-      <c r="A726" t="inlineStr">
+      <c r="A726" s="28" t="inlineStr">
         <is>
           <t>4550391011476</t>
         </is>
       </c>
-      <c r="B726" t="inlineStr">
+      <c r="B726" s="28" t="inlineStr">
         <is>
           <t>b0frs8pb58</t>
         </is>
       </c>
-      <c r="C726" t="inlineStr">
+      <c r="C726" s="28" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D726" t="inlineStr">
+      <c r="D726" s="28" t="inlineStr">
         <is>
           <t>B0FRS9W3FT-1476</t>
         </is>
       </c>
-      <c r="E726" t="inlineStr">
+      <c r="E726" s="28" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + しずくちゃんシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F726" t="n">
+      <c r="F726" s="28" t="n">
         <v>3980</v>
       </c>
-      <c r="G726" t="n">
+      <c r="G726" s="28" t="n">
         <v>1133</v>
       </c>
-      <c r="H726" t="n">
+      <c r="H726" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I726">
+      <c r="I726" s="28">
         <f>SUM(G726*H726)</f>
         <v/>
       </c>
-      <c r="J726" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K726" t="inlineStr">
+      <c r="J726" s="28" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K726" s="28" t="inlineStr">
         <is>
           <t>4550391011476</t>
         </is>
       </c>
     </row>
     <row r="727" ht="13.5" customHeight="1">
-      <c r="A727" t="inlineStr">
+      <c r="A727" s="28" t="inlineStr">
         <is>
           <t>4550391043903</t>
         </is>
       </c>
-      <c r="B727" t="inlineStr">
+      <c r="B727" s="28" t="inlineStr">
         <is>
           <t>b0frs8pb58</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr">
+      <c r="C727" s="28" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D727" t="inlineStr">
+      <c r="D727" s="28" t="inlineStr">
         <is>
           <t>B0FW4K6VZY-3903</t>
         </is>
       </c>
-      <c r="E727" t="inlineStr">
+      <c r="E727" s="28" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + しずくちゃんシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F727" t="n">
+      <c r="F727" s="28" t="n">
         <v>3980</v>
       </c>
-      <c r="G727" t="n">
+      <c r="G727" s="28" t="n">
         <v>1133</v>
       </c>
-      <c r="H727" t="n">
+      <c r="H727" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I727">
+      <c r="I727" s="28">
         <f>SUM(G727*H727)</f>
         <v/>
       </c>
-      <c r="J727" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K727" t="inlineStr">
+      <c r="J727" s="28" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K727" s="28" t="inlineStr">
         <is>
           <t>4550391043903</t>
         </is>
@@ -33389,300 +33419,300 @@
       </c>
     </row>
     <row r="734" ht="13.5" customHeight="1">
-      <c r="A734" t="inlineStr">
+      <c r="A734" s="28" t="inlineStr">
         <is>
           <t>4550391912131</t>
         </is>
       </c>
-      <c r="B734" t="inlineStr">
+      <c r="B734" s="28" t="inlineStr">
         <is>
           <t>b0frs9w3ft</t>
         </is>
       </c>
-      <c r="C734" t="inlineStr">
+      <c r="C734" s="28" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D734" t="inlineStr">
+      <c r="D734" s="28" t="inlineStr">
         <is>
           <t>B0DVSV4W6Q-2131</t>
         </is>
       </c>
-      <c r="E734" t="inlineStr">
+      <c r="E734" s="28" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + ボンボンドロップシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F734" t="n">
+      <c r="F734" s="28" t="n">
         <v>3980</v>
       </c>
-      <c r="G734" t="n">
+      <c r="G734" s="28" t="n">
         <v>1133</v>
       </c>
-      <c r="H734" t="n">
+      <c r="H734" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I734">
+      <c r="I734" s="28">
         <f>SUM(G734*H734)</f>
         <v/>
       </c>
-      <c r="J734" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K734" t="inlineStr">
+      <c r="J734" s="28" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K734" s="28" t="inlineStr">
         <is>
           <t>4550391912131</t>
         </is>
       </c>
     </row>
     <row r="735" ht="13.5" customHeight="1">
-      <c r="A735" t="inlineStr">
+      <c r="A735" s="28" t="inlineStr">
         <is>
           <t>4550391912094</t>
         </is>
       </c>
-      <c r="B735" t="inlineStr">
+      <c r="B735" s="28" t="inlineStr">
         <is>
           <t>b0frs9w3ft</t>
         </is>
       </c>
-      <c r="C735" t="inlineStr">
+      <c r="C735" s="28" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D735" t="inlineStr">
+      <c r="D735" s="28" t="inlineStr">
         <is>
           <t>B0DVSW1YS7-2094</t>
         </is>
       </c>
-      <c r="E735" t="inlineStr">
+      <c r="E735" s="28" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + ボンボンドロップシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F735" t="n">
+      <c r="F735" s="28" t="n">
         <v>3980</v>
       </c>
-      <c r="G735" t="n">
+      <c r="G735" s="28" t="n">
         <v>1133</v>
       </c>
-      <c r="H735" t="n">
+      <c r="H735" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I735">
+      <c r="I735" s="28">
         <f>SUM(G735*H735)</f>
         <v/>
       </c>
-      <c r="J735" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K735" t="inlineStr">
+      <c r="J735" s="28" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K735" s="28" t="inlineStr">
         <is>
           <t>4550391912094</t>
         </is>
       </c>
     </row>
     <row r="736" ht="13.5" customHeight="1">
-      <c r="A736" t="inlineStr">
+      <c r="A736" s="28" t="inlineStr">
         <is>
           <t>4550391011469</t>
         </is>
       </c>
-      <c r="B736" t="inlineStr">
+      <c r="B736" s="28" t="inlineStr">
         <is>
           <t>b0frs9w3ft</t>
         </is>
       </c>
-      <c r="C736" t="inlineStr">
+      <c r="C736" s="28" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D736" t="inlineStr">
+      <c r="D736" s="28" t="inlineStr">
         <is>
           <t>B0FRS8PB58-1469</t>
         </is>
       </c>
-      <c r="E736" t="inlineStr">
+      <c r="E736" s="28" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + ボンボンドロップシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F736" t="n">
+      <c r="F736" s="28" t="n">
         <v>3980</v>
       </c>
-      <c r="G736" t="n">
+      <c r="G736" s="28" t="n">
         <v>1133</v>
       </c>
-      <c r="H736" t="n">
+      <c r="H736" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I736">
+      <c r="I736" s="28">
         <f>SUM(G736*H736)</f>
         <v/>
       </c>
-      <c r="J736" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K736" t="inlineStr">
+      <c r="J736" s="28" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K736" s="28" t="inlineStr">
         <is>
           <t>4550391011469</t>
         </is>
       </c>
     </row>
     <row r="737" ht="13.5" customHeight="1">
-      <c r="A737" t="inlineStr">
+      <c r="A737" s="28" t="inlineStr">
         <is>
           <t>4550391011360</t>
         </is>
       </c>
-      <c r="B737" t="inlineStr">
+      <c r="B737" s="28" t="inlineStr">
         <is>
           <t>b0frs9w3ft</t>
         </is>
       </c>
-      <c r="C737" t="inlineStr">
+      <c r="C737" s="28" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D737" t="inlineStr">
+      <c r="D737" s="28" t="inlineStr">
         <is>
           <t>B0FRS8X8M7-1360</t>
         </is>
       </c>
-      <c r="E737" t="inlineStr">
+      <c r="E737" s="28" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + ボンボンドロップシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F737" t="n">
+      <c r="F737" s="28" t="n">
         <v>3980</v>
       </c>
-      <c r="G737" t="n">
+      <c r="G737" s="28" t="n">
         <v>1133</v>
       </c>
-      <c r="H737" t="n">
+      <c r="H737" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I737">
+      <c r="I737" s="28">
         <f>SUM(G737*H737)</f>
         <v/>
       </c>
-      <c r="J737" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K737" t="inlineStr">
+      <c r="J737" s="28" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K737" s="28" t="inlineStr">
         <is>
           <t>4550391011360</t>
         </is>
       </c>
     </row>
     <row r="738" ht="13.5" customHeight="1">
-      <c r="A738" t="inlineStr">
+      <c r="A738" s="28" t="inlineStr">
         <is>
           <t>4550391011476</t>
         </is>
       </c>
-      <c r="B738" t="inlineStr">
+      <c r="B738" s="28" t="inlineStr">
         <is>
           <t>b0frs9w3ft</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr">
+      <c r="C738" s="28" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D738" t="inlineStr">
+      <c r="D738" s="28" t="inlineStr">
         <is>
           <t>B0FRS9W3FT-1476</t>
         </is>
       </c>
-      <c r="E738" t="inlineStr">
+      <c r="E738" s="28" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + ボンボンドロップシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F738" t="n">
+      <c r="F738" s="28" t="n">
         <v>3980</v>
       </c>
-      <c r="G738" t="n">
+      <c r="G738" s="28" t="n">
         <v>1133</v>
       </c>
-      <c r="H738" t="n">
+      <c r="H738" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I738">
+      <c r="I738" s="28">
         <f>SUM(G738*H738)</f>
         <v/>
       </c>
-      <c r="J738" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K738" t="inlineStr">
+      <c r="J738" s="28" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K738" s="28" t="inlineStr">
         <is>
           <t>4550391011476</t>
         </is>
       </c>
     </row>
     <row r="739" ht="13.5" customHeight="1">
-      <c r="A739" t="inlineStr">
+      <c r="A739" s="28" t="inlineStr">
         <is>
           <t>4550391043903</t>
         </is>
       </c>
-      <c r="B739" t="inlineStr">
+      <c r="B739" s="28" t="inlineStr">
         <is>
           <t>b0frs9w3ft</t>
         </is>
       </c>
-      <c r="C739" t="inlineStr">
+      <c r="C739" s="28" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D739" t="inlineStr">
+      <c r="D739" s="28" t="inlineStr">
         <is>
           <t>B0FW4K6VZY-3903</t>
         </is>
       </c>
-      <c r="E739" t="inlineStr">
+      <c r="E739" s="28" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + ボンボンドロップシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F739" t="n">
+      <c r="F739" s="28" t="n">
         <v>3980</v>
       </c>
-      <c r="G739" t="n">
+      <c r="G739" s="28" t="n">
         <v>1133</v>
       </c>
-      <c r="H739" t="n">
+      <c r="H739" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I739">
+      <c r="I739" s="28">
         <f>SUM(G739*H739)</f>
         <v/>
       </c>
-      <c r="J739" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K739" t="inlineStr">
+      <c r="J739" s="28" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K739" s="28" t="inlineStr">
         <is>
           <t>4550391043903</t>
         </is>
@@ -34258,358 +34288,376 @@
       </c>
     </row>
     <row r="753" ht="13.5" customHeight="1">
-      <c r="A753" t="inlineStr">
+      <c r="A753" s="28" t="inlineStr">
         <is>
           <t>4550391012244</t>
         </is>
       </c>
-      <c r="B753" t="inlineStr">
+      <c r="B753" s="28" t="inlineStr">
         <is>
           <t>b0gsqcp1mx</t>
         </is>
       </c>
-      <c r="C753" t="inlineStr">
+      <c r="C753" s="28" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="D753" t="inlineStr">
+      <c r="D753" s="28" t="inlineStr">
         <is>
           <t>B0GSQ2Q1RY</t>
         </is>
       </c>
-      <c r="E753" t="inlineStr">
+      <c r="E753" s="28" t="inlineStr">
         <is>
           <t>クーリア ボンボンドロップシール シールバインダー セット キャンディツインズ エナガマーチ ナイトミャウ マイリボンクローゼット ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集</t>
         </is>
       </c>
-      <c r="F753" t="n">
+      <c r="F753" s="28" t="n">
         <v>2580</v>
       </c>
-      <c r="G753" t="n">
+      <c r="G753" s="28" t="n">
         <v>1148</v>
       </c>
-      <c r="H753" t="n">
+      <c r="H753" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="I753">
+      <c r="I753" s="28">
         <f>SUM(G753*H753)</f>
         <v/>
       </c>
+      <c r="J753" s="28" t="n"/>
+      <c r="K753" s="28" t="n"/>
     </row>
     <row r="754" ht="13.5" customHeight="1">
-      <c r="A754" t="inlineStr">
+      <c r="A754" s="28" t="inlineStr">
         <is>
           <t>4550391012251</t>
         </is>
       </c>
-      <c r="B754" t="inlineStr">
+      <c r="B754" s="28" t="inlineStr">
         <is>
           <t>b0gsqcp1mx</t>
         </is>
       </c>
-      <c r="C754" t="inlineStr">
+      <c r="C754" s="28" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="D754" t="inlineStr">
+      <c r="D754" s="28" t="inlineStr">
         <is>
           <t>B0GSQC8JP3</t>
         </is>
       </c>
-      <c r="E754" t="inlineStr">
+      <c r="E754" s="28" t="inlineStr">
         <is>
           <t>クーリア ボンボンドロップシール シールバインダー セット キャンディツインズ エナガマーチ ナイトミャウ マイリボンクローゼット ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集</t>
         </is>
       </c>
-      <c r="F754" t="n">
+      <c r="F754" s="28" t="n">
         <v>2580</v>
       </c>
-      <c r="G754" t="n">
+      <c r="G754" s="28" t="n">
         <v>1148</v>
       </c>
-      <c r="H754" t="n">
+      <c r="H754" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="I754">
+      <c r="I754" s="28">
         <f>SUM(G754*H754)</f>
         <v/>
       </c>
+      <c r="J754" s="28" t="n"/>
+      <c r="K754" s="28" t="n"/>
     </row>
     <row r="755" ht="13.5" customHeight="1">
-      <c r="A755" t="inlineStr">
+      <c r="A755" s="28" t="inlineStr">
         <is>
           <t>4550391012220</t>
         </is>
       </c>
-      <c r="B755" t="inlineStr">
+      <c r="B755" s="28" t="inlineStr">
         <is>
           <t>b0gsqcp1mx</t>
         </is>
       </c>
-      <c r="C755" t="inlineStr">
+      <c r="C755" s="28" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="D755" t="inlineStr">
+      <c r="D755" s="28" t="inlineStr">
         <is>
           <t>B0GSQCP1MX</t>
         </is>
       </c>
-      <c r="E755" t="inlineStr">
+      <c r="E755" s="28" t="inlineStr">
         <is>
           <t>クーリア ボンボンドロップシール シールバインダー セット キャンディツインズ エナガマーチ ナイトミャウ マイリボンクローゼット ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集</t>
         </is>
       </c>
-      <c r="F755" t="n">
+      <c r="F755" s="28" t="n">
         <v>2580</v>
       </c>
-      <c r="G755" t="n">
+      <c r="G755" s="28" t="n">
         <v>1148</v>
       </c>
-      <c r="H755" t="n">
+      <c r="H755" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="I755">
+      <c r="I755" s="28">
         <f>SUM(G755*H755)</f>
         <v/>
       </c>
+      <c r="J755" s="28" t="n"/>
+      <c r="K755" s="28" t="n"/>
     </row>
     <row r="756" ht="13.5" customHeight="1">
-      <c r="A756" t="inlineStr">
+      <c r="A756" s="28" t="inlineStr">
         <is>
           <t>4550391012237</t>
         </is>
       </c>
-      <c r="B756" t="inlineStr">
+      <c r="B756" s="28" t="inlineStr">
         <is>
           <t>b0gsqcp1mx</t>
         </is>
       </c>
-      <c r="C756" t="inlineStr">
+      <c r="C756" s="28" t="inlineStr">
         <is>
           <t>2220,2237,2244,2251/4592-a</t>
         </is>
       </c>
-      <c r="D756" t="inlineStr">
+      <c r="D756" s="28" t="inlineStr">
         <is>
           <t>B0GSQHQRV7</t>
         </is>
       </c>
-      <c r="E756" t="inlineStr">
+      <c r="E756" s="28" t="inlineStr">
         <is>
           <t>クーリア ボンボンドロップシール シールバインダー セット キャンディツインズ エナガマーチ ナイトミャウ マイリボンクローゼット ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集</t>
         </is>
       </c>
-      <c r="F756" t="n">
+      <c r="F756" s="28" t="n">
         <v>2580</v>
       </c>
-      <c r="G756" t="n">
+      <c r="G756" s="28" t="n">
         <v>1148</v>
       </c>
-      <c r="H756" t="n">
+      <c r="H756" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="I756">
+      <c r="I756" s="28">
         <f>SUM(G756*H756)</f>
         <v/>
       </c>
+      <c r="J756" s="28" t="n"/>
+      <c r="K756" s="28" t="n"/>
     </row>
     <row r="757" ht="13.5" customHeight="1">
-      <c r="A757" t="inlineStr">
+      <c r="A757" s="28" t="inlineStr">
         <is>
           <t>4550391012244</t>
         </is>
       </c>
-      <c r="B757" t="inlineStr">
+      <c r="B757" s="28" t="inlineStr">
         <is>
           <t>b0gsqcp1mx-a</t>
         </is>
       </c>
-      <c r="C757" t="n">
+      <c r="C757" s="28" t="n">
         <v>2000</v>
       </c>
-      <c r="D757" t="inlineStr">
+      <c r="D757" s="28" t="inlineStr">
         <is>
           <t>B0GSQ2Q1RY</t>
         </is>
       </c>
-      <c r="E757" t="inlineStr">
+      <c r="E757" s="28" t="inlineStr">
         <is>
           <t>【福袋】【計3点セット】【正規品】 クーリア シールバインダーセット(ボンボンドロップシール付き) + しずくちゃんシリーズ + クーリアシール｜ボンボンドロップ ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集 キラキラ 3D立体 女の子 平成女子 本家</t>
         </is>
       </c>
-      <c r="F757" t="n">
+      <c r="F757" s="28" t="n">
         <v>4480</v>
       </c>
-      <c r="G757" t="n">
+      <c r="G757" s="28" t="n">
         <v>2000</v>
       </c>
-      <c r="H757" t="n">
+      <c r="H757" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="I757">
+      <c r="I757" s="28">
         <f>SUM(G757*H757)</f>
         <v/>
       </c>
+      <c r="J757" s="28" t="n"/>
+      <c r="K757" s="28" t="n"/>
     </row>
     <row r="758" ht="13.5" customHeight="1">
-      <c r="A758" t="inlineStr">
+      <c r="A758" s="28" t="inlineStr">
         <is>
           <t>4550391012251</t>
         </is>
       </c>
-      <c r="B758" t="inlineStr">
+      <c r="B758" s="28" t="inlineStr">
         <is>
           <t>b0gsqcp1mx-a</t>
         </is>
       </c>
-      <c r="C758" t="n">
+      <c r="C758" s="28" t="n">
         <v>2000</v>
       </c>
-      <c r="D758" t="inlineStr">
+      <c r="D758" s="28" t="inlineStr">
         <is>
           <t>B0GSQC8JP3</t>
         </is>
       </c>
-      <c r="E758" t="inlineStr">
+      <c r="E758" s="28" t="inlineStr">
         <is>
           <t>【福袋】【計3点セット】【正規品】 クーリア シールバインダーセット(ボンボンドロップシール付き) + しずくちゃんシリーズ + クーリアシール｜ボンボンドロップ ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集 キラキラ 3D立体 女の子 平成女子 本家</t>
         </is>
       </c>
-      <c r="F758" t="n">
+      <c r="F758" s="28" t="n">
         <v>4480</v>
       </c>
-      <c r="G758" t="n">
+      <c r="G758" s="28" t="n">
         <v>2000</v>
       </c>
-      <c r="H758" t="n">
+      <c r="H758" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="I758">
+      <c r="I758" s="28">
         <f>SUM(G758*H758)</f>
         <v/>
       </c>
+      <c r="J758" s="28" t="n"/>
+      <c r="K758" s="28" t="n"/>
     </row>
     <row r="759" ht="13.5" customHeight="1">
-      <c r="A759" t="inlineStr">
+      <c r="A759" s="28" t="inlineStr">
         <is>
           <t>4550391012220</t>
         </is>
       </c>
-      <c r="B759" t="inlineStr">
+      <c r="B759" s="28" t="inlineStr">
         <is>
           <t>b0gsqcp1mx-a</t>
         </is>
       </c>
-      <c r="C759" t="n">
+      <c r="C759" s="28" t="n">
         <v>2000</v>
       </c>
-      <c r="D759" t="inlineStr">
+      <c r="D759" s="28" t="inlineStr">
         <is>
           <t>B0GSQCP1MX</t>
         </is>
       </c>
-      <c r="E759" t="inlineStr">
+      <c r="E759" s="28" t="inlineStr">
         <is>
           <t>【福袋】【計3点セット】【正規品】 クーリア シールバインダーセット(ボンボンドロップシール付き) + しずくちゃんシリーズ + クーリアシール｜ボンボンドロップ ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集 キラキラ 3D立体 女の子 平成女子 本家</t>
         </is>
       </c>
-      <c r="F759" t="n">
+      <c r="F759" s="28" t="n">
         <v>4480</v>
       </c>
-      <c r="G759" t="n">
+      <c r="G759" s="28" t="n">
         <v>2000</v>
       </c>
-      <c r="H759" t="n">
+      <c r="H759" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="I759">
+      <c r="I759" s="28">
         <f>SUM(G759*H759)</f>
         <v/>
       </c>
+      <c r="J759" s="28" t="n"/>
+      <c r="K759" s="28" t="n"/>
     </row>
     <row r="760" ht="13.5" customHeight="1">
-      <c r="A760" t="inlineStr">
+      <c r="A760" s="28" t="inlineStr">
         <is>
           <t>4550391012237</t>
         </is>
       </c>
-      <c r="B760" t="inlineStr">
+      <c r="B760" s="28" t="inlineStr">
         <is>
           <t>b0gsqcp1mx-a</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr">
+      <c r="C760" s="28" t="inlineStr">
         <is>
           <t>2220,2237,2244,2251/4592-a</t>
         </is>
       </c>
-      <c r="D760" t="inlineStr">
+      <c r="D760" s="28" t="inlineStr">
         <is>
           <t>B0GSQHQRV7</t>
         </is>
       </c>
-      <c r="E760" t="inlineStr">
+      <c r="E760" s="28" t="inlineStr">
         <is>
           <t>【福袋】【計3点セット】【正規品】 クーリア シールバインダーセット(ボンボンドロップシール付き) + しずくちゃんシリーズ + クーリアシール｜ボンボンドロップ ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集 キラキラ 3D立体 女の子 平成女子 本家</t>
         </is>
       </c>
-      <c r="F760" t="n">
+      <c r="F760" s="28" t="n">
         <v>4480</v>
       </c>
-      <c r="G760" t="n">
+      <c r="G760" s="28" t="n">
         <v>2000</v>
       </c>
-      <c r="H760" t="n">
+      <c r="H760" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="I760">
+      <c r="I760" s="28">
         <f>SUM(G760*H760)</f>
         <v/>
       </c>
+      <c r="J760" s="28" t="n"/>
+      <c r="K760" s="28" t="n"/>
     </row>
     <row r="761" ht="13.5" customHeight="1">
-      <c r="A761" t="inlineStr">
+      <c r="A761" s="28" t="inlineStr">
         <is>
           <t>4550391012237</t>
         </is>
       </c>
-      <c r="B761" t="inlineStr">
+      <c r="B761" s="28" t="inlineStr">
         <is>
           <t>b0gsqhqrv7</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr">
+      <c r="C761" s="28" t="inlineStr">
         <is>
           <t>2220,2237,2244,2251/4592-a</t>
         </is>
       </c>
-      <c r="D761" t="inlineStr">
+      <c r="D761" s="28" t="inlineStr">
         <is>
           <t>B0GSQHQRV7</t>
         </is>
       </c>
-      <c r="E761" t="inlineStr">
+      <c r="E761" s="28" t="inlineStr">
         <is>
           <t>【4種セット】 クーリア ボンボンドロップシール シールバインダー 4種 キャンディツインズ エナガマーチ ナイトミャウ マイリボンクローゼット ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集</t>
         </is>
       </c>
-      <c r="F761" t="n">
+      <c r="F761" s="28" t="n">
         <v>9480</v>
       </c>
-      <c r="G761" t="n">
+      <c r="G761" s="28" t="n">
         <v>1148</v>
       </c>
-      <c r="H761" t="n">
+      <c r="H761" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="I761">
+      <c r="I761" s="28">
         <f>SUM(G761*H761)</f>
         <v/>
       </c>
+      <c r="J761" s="28" t="n"/>
+      <c r="K761" s="28" t="n"/>
     </row>
     <row r="762" ht="13.5" customHeight="1">
       <c r="A762" t="inlineStr">

--- a/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
+++ b/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
@@ -91,7 +91,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -117,6 +117,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -170,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -195,6 +200,12 @@
     <xf numFmtId="164" fontId="6" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1392,82 +1403,78 @@
       </c>
     </row>
     <row r="25" ht="13.5" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>4550391012718</t>
         </is>
       </c>
-      <c r="B25" s="19" t="n">
+      <c r="B25" s="15" t="n">
         <v>4550391012718</v>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>AST-0010</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>4550391012718</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>【全6種セット】【正規品】クーリア ぷちぷにらいふしーる 6種セット がーりーらいふ ゆにらいふ はぴはむらいふ えながらいふ ぱんらいふ きゃわうさらいふ シールセット ぷっくりシール 立体シール デコシール 手帳デコ トレカデコ スマホデコ ぷちぷに ボンボンドロップ</t>
         </is>
       </c>
-      <c r="F25" s="7" t="n">
+      <c r="F25" t="n">
         <v>1980</v>
       </c>
-      <c r="G25" s="7" t="n">
+      <c r="G25" t="n">
         <v>768</v>
       </c>
-      <c r="H25" s="7" t="n">
+      <c r="H25" t="n">
         <v>25</v>
       </c>
-      <c r="I25" s="7">
+      <c r="I25">
         <f>SUM(G25*H25)</f>
         <v/>
       </c>
-      <c r="J25" s="7" t="n"/>
-      <c r="K25" s="7" t="n"/>
     </row>
     <row r="26" ht="13.5" customHeight="1">
-      <c r="A26" s="19" t="n">
+      <c r="A26" s="15" t="n">
         <v>4550391012787</v>
       </c>
-      <c r="B26" s="19" t="n">
+      <c r="B26" s="15" t="n">
         <v>4550391012787</v>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>2787,2794,2800,2817,2824/2088-a</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>4550391012718</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>【全6種セット】クーリア キラキラシールバインダー リボンA リボンB デイジーA デイジーB ハートA ハートB シール収納 ステッカー収納 バインダー コレクトブック 推し活 トレカ収納 デコ コレクション 文房具 かわいい 女の子向け プレゼント ギフト クーリア まとめ買い</t>
         </is>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F26" t="n">
         <v>5980</v>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="G26" t="n">
         <v>2088</v>
       </c>
-      <c r="H26" s="7" t="n">
+      <c r="H26" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="7">
+      <c r="I26">
         <f>SUM(G26*H26)</f>
         <v/>
       </c>
-      <c r="J26" s="7" t="n"/>
-      <c r="K26" s="7" t="n"/>
     </row>
     <row r="27" ht="13.5" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
@@ -2090,80 +2097,78 @@
       </c>
     </row>
     <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" s="19" t="inlineStr">
+      <c r="A44" s="22" t="inlineStr">
         <is>
           <t>4550451352129</t>
         </is>
       </c>
-      <c r="B44" s="19" t="n">
+      <c r="B44" s="22" t="n">
         <v>4550451352129</v>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C44" s="23" t="inlineStr">
         <is>
           <t>2129,2167/1210</t>
         </is>
       </c>
-      <c r="D44" s="19" t="n">
+      <c r="D44" s="22" t="n">
         <v>4550451352129</v>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E44" s="23" t="inlineStr">
         <is>
           <t>【セット品】サンリオ コットンパフィーシール 3種セット マイメロディ クロミ シナモロール ハローキティ レオパード クラックス COTTON PUFFY ぷっくりシール デコシール 手帳デコ ノートデコ キャラクターシール 文房具 ステッカー アソートセット シール 立体 かわいい</t>
         </is>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="F44" s="23" t="n">
         <v>4480</v>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="G44" s="23" t="n">
         <v>605</v>
       </c>
-      <c r="H44" s="7" t="n">
+      <c r="H44" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="I44" s="7">
+      <c r="I44" s="23">
         <f>SUM(G44*H44)</f>
         <v/>
       </c>
-      <c r="J44" s="7" t="n"/>
-      <c r="K44" s="7" t="n"/>
+      <c r="J44" s="23" t="n"/>
+      <c r="K44" s="23" t="n"/>
     </row>
     <row r="45" ht="13.5" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>4550451352129</t>
         </is>
       </c>
-      <c r="B45" s="19" t="n">
+      <c r="B45" s="15" t="n">
         <v>4550451352167</v>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>2129,2167/1210</t>
         </is>
       </c>
-      <c r="D45" s="19" t="n">
+      <c r="D45" s="15" t="n">
         <v>4550451352129</v>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>【セット品】サンリオ コットンパフィーシール 2種セット マイメロディ クロミ ハローキティ レオパード クラックス COTTON PUFFY ぷっくりシール デコシール 手帳デコ ノートデコ キャラクターシール 文房具 ステッカー アソートセット シール 立体 かわいい</t>
         </is>
       </c>
-      <c r="F45" s="7" t="n">
+      <c r="F45" t="n">
         <v>3080</v>
       </c>
-      <c r="G45" s="7" t="n">
+      <c r="G45" t="n">
         <v>605</v>
       </c>
-      <c r="H45" s="7" t="n">
+      <c r="H45" t="n">
         <v>7</v>
       </c>
-      <c r="I45" s="7">
+      <c r="I45">
         <f>SUM(G45*H45)</f>
         <v/>
       </c>
-      <c r="J45" s="7" t="n"/>
-      <c r="K45" s="7" t="n"/>
     </row>
     <row r="46" ht="13.5" customHeight="1">
       <c r="A46" s="15" t="inlineStr">
@@ -17167,50 +17172,50 @@
       </c>
     </row>
     <row r="365" ht="13.5" customHeight="1">
-      <c r="A365" s="19" t="inlineStr">
+      <c r="A365" s="15" t="inlineStr">
         <is>
           <t>9000326168003</t>
         </is>
       </c>
-      <c r="B365" s="19" t="inlineStr">
+      <c r="B365" s="15" t="inlineStr">
         <is>
           <t>b0bltqq367</t>
         </is>
       </c>
-      <c r="C365" s="7" t="inlineStr">
+      <c r="C365" t="inlineStr">
         <is>
           <t>4901133415722-6</t>
         </is>
       </c>
-      <c r="D365" s="19" t="inlineStr">
+      <c r="D365" s="15" t="inlineStr">
         <is>
           <t>b0bltqq367</t>
         </is>
       </c>
-      <c r="E365" s="8" t="inlineStr">
+      <c r="E365" s="21" t="inlineStr">
         <is>
           <t>いなば チャオ(CIAO)ちゅ～るごはん とりささみ 総合栄養食 14g×4P ６袋セット 猫 猫用 おやつ 国産 液状 キャットフード 人気 グレインフリー</t>
         </is>
       </c>
-      <c r="F365" s="7" t="n">
+      <c r="F365" t="n">
         <v>1780</v>
       </c>
-      <c r="G365" s="7" t="n">
+      <c r="G365" t="n">
         <v>970</v>
       </c>
-      <c r="H365" s="7" t="n">
+      <c r="H365" t="n">
         <v>9</v>
       </c>
-      <c r="I365" s="7">
+      <c r="I365">
         <f>SUM(G365*H365)</f>
         <v/>
       </c>
-      <c r="J365" s="7" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K365" s="7" t="inlineStr">
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
         <is>
           <t>9000326168003</t>
         </is>
@@ -24853,44 +24858,44 @@
       </c>
     </row>
     <row r="538" ht="13.5" customHeight="1">
-      <c r="A538" s="19" t="n">
+      <c r="A538" s="22" t="n">
         <v>4901301441720</v>
       </c>
-      <c r="B538" s="19" t="inlineStr">
+      <c r="B538" s="22" t="inlineStr">
         <is>
           <t>b0d9znvl7q</t>
         </is>
       </c>
-      <c r="C538" s="7" t="inlineStr">
+      <c r="C538" s="23" t="inlineStr">
         <is>
           <t>0633/599-a</t>
         </is>
       </c>
-      <c r="D538" s="19" t="inlineStr">
+      <c r="D538" s="22" t="inlineStr">
         <is>
           <t>B0DV57G9Z1</t>
         </is>
       </c>
-      <c r="E538" s="8" t="inlineStr">
+      <c r="E538" s="24" t="inlineStr">
         <is>
           <t>花王 フレアフレグランス ハミングフレア リッチフローラル 本体 520ml 部屋干し 雨の日 部屋 かろやか 香る きれい 清潔 衣類 静電気 防臭 抗菌 赤ちゃん ベビー 洗濯</t>
         </is>
       </c>
-      <c r="F538" s="7" t="n">
+      <c r="F538" s="23" t="n">
         <v>1280</v>
       </c>
-      <c r="G538" s="7" t="n">
+      <c r="G538" s="23" t="n">
         <v>219</v>
       </c>
-      <c r="H538" s="7" t="n">
+      <c r="H538" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="I538" s="7">
+      <c r="I538" s="23">
         <f>SUM(G538*H538)</f>
         <v/>
       </c>
-      <c r="J538" s="7" t="n"/>
-      <c r="K538" s="7" t="n"/>
+      <c r="J538" s="23" t="n"/>
+      <c r="K538" s="23" t="n"/>
     </row>
     <row r="539" ht="13.5" customHeight="1">
       <c r="A539" s="15" t="inlineStr">
@@ -25563,50 +25568,50 @@
       </c>
     </row>
     <row r="554" ht="13.5" customHeight="1">
-      <c r="A554" s="19" t="inlineStr">
+      <c r="A554" s="22" t="inlineStr">
         <is>
           <t>4987176260635</t>
         </is>
       </c>
-      <c r="B554" s="19" t="inlineStr">
+      <c r="B554" s="22" t="inlineStr">
         <is>
           <t>b0dfyjnwjt</t>
         </is>
       </c>
-      <c r="C554" s="12" t="inlineStr">
+      <c r="C554" s="25" t="inlineStr">
         <is>
           <t>4987176260635-2</t>
         </is>
       </c>
-      <c r="D554" s="19" t="inlineStr">
+      <c r="D554" s="22" t="inlineStr">
         <is>
           <t>b0dfyjnwjt</t>
         </is>
       </c>
-      <c r="E554" s="7" t="inlineStr">
+      <c r="E554" s="23" t="inlineStr">
         <is>
           <t>レノア リセット セラム ホワイトリリーの香り つめかえ 特大 750mL×2個セット 柔軟剤 部屋干し 雨の日 部屋 かろやか 香る きれい 清潔 衣類 静電気 防臭 抗菌 赤ちゃん ベビー 洗濯</t>
         </is>
       </c>
-      <c r="F554" s="7" t="n">
+      <c r="F554" s="23" t="n">
         <v>2980</v>
       </c>
-      <c r="G554" s="7" t="n">
+      <c r="G554" s="23" t="n">
         <v>1856</v>
       </c>
-      <c r="H554" s="7" t="n">
+      <c r="H554" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="I554" s="7">
+      <c r="I554" s="23">
         <f>SUM(G554*H554)</f>
         <v/>
       </c>
-      <c r="J554" s="7" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K554" s="7" t="inlineStr">
+      <c r="J554" s="23" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K554" s="23" t="inlineStr">
         <is>
           <t>4987176260635</t>
         </is>
@@ -26726,48 +26731,48 @@
       </c>
     </row>
     <row r="582" ht="13.5" customHeight="1">
-      <c r="A582" s="19" t="n">
+      <c r="A582" s="22" t="n">
         <v>4987176260659</v>
       </c>
-      <c r="B582" s="19" t="inlineStr">
+      <c r="B582" s="22" t="inlineStr">
         <is>
           <t>b0dktchdgk</t>
         </is>
       </c>
-      <c r="C582" s="7" t="inlineStr">
+      <c r="C582" s="23" t="inlineStr">
         <is>
           <t>4987176260659-2</t>
         </is>
       </c>
-      <c r="D582" s="19" t="inlineStr">
+      <c r="D582" s="22" t="inlineStr">
         <is>
           <t>b0dfyjnwjt</t>
         </is>
       </c>
-      <c r="E582" s="7" t="inlineStr">
+      <c r="E582" s="23" t="inlineStr">
         <is>
           <t>レノア リセット セラム ホワイトピーチ&amp;カモミールの香り つめかえ 特大 750mL×2個セット 柔軟剤 部屋干し 雨の日 部屋 かろやか 香る きれい 清潔 衣類 静電気 防臭 抗菌 赤ちゃん ベビー 洗濯</t>
         </is>
       </c>
-      <c r="F582" s="7" t="n">
+      <c r="F582" s="23" t="n">
         <v>2980</v>
       </c>
-      <c r="G582" s="7" t="n">
+      <c r="G582" s="23" t="n">
         <v>1856</v>
       </c>
-      <c r="H582" s="7" t="n">
+      <c r="H582" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="I582" s="7">
+      <c r="I582" s="23">
         <f>SUM(G582*H582)</f>
         <v/>
       </c>
-      <c r="J582" s="7" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K582" s="7" t="inlineStr">
+      <c r="J582" s="23" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K582" s="23" t="inlineStr">
         <is>
           <t>4987176260635</t>
         </is>
@@ -26874,44 +26879,44 @@
       </c>
     </row>
     <row r="585" ht="13.5" customHeight="1">
-      <c r="A585" s="19" t="n">
+      <c r="A585" s="22" t="n">
         <v>4520699694367</v>
       </c>
-      <c r="B585" s="19" t="inlineStr">
+      <c r="B585" s="22" t="inlineStr">
         <is>
           <t>b0dmrwrwrd</t>
         </is>
       </c>
-      <c r="C585" s="7" t="inlineStr">
+      <c r="C585" s="23" t="inlineStr">
         <is>
           <t>4520699635674 -2</t>
         </is>
       </c>
-      <c r="D585" s="19" t="inlineStr">
+      <c r="D585" s="22" t="inlineStr">
         <is>
           <t>b0dmrwrwrd</t>
         </is>
       </c>
-      <c r="E585" s="7" t="inlineStr">
+      <c r="E585" s="23" t="inlineStr">
         <is>
           <t>【セット品】銀のスプーン 三ツ星グルメ にっぽんSelect とろリッチ 2種のお魚味アソート 48g（6g×8本）×2コ 総合栄養食</t>
         </is>
       </c>
-      <c r="F585" s="7" t="n">
+      <c r="F585" s="23" t="n">
         <v>799</v>
       </c>
-      <c r="G585" s="7" t="n">
+      <c r="G585" s="23" t="n">
         <v>380</v>
       </c>
-      <c r="H585" s="7" t="n">
+      <c r="H585" s="23" t="n">
         <v>98</v>
       </c>
-      <c r="I585" s="7">
+      <c r="I585" s="23">
         <f>SUM(G585*H585)</f>
         <v/>
       </c>
-      <c r="J585" s="7" t="n"/>
-      <c r="K585" s="7" t="n"/>
+      <c r="J585" s="23" t="n"/>
+      <c r="K585" s="23" t="n"/>
     </row>
     <row r="586" ht="13.5" customHeight="1">
       <c r="A586" s="15" t="inlineStr">
@@ -27767,44 +27772,42 @@
       </c>
     </row>
     <row r="608" ht="13.5" customHeight="1">
-      <c r="A608" s="19" t="n">
+      <c r="A608" s="15" t="n">
         <v>4520699635674</v>
       </c>
-      <c r="B608" s="19" t="inlineStr">
+      <c r="B608" s="15" t="inlineStr">
         <is>
           <t>b0dpfkqck7</t>
         </is>
       </c>
-      <c r="C608" s="7" t="inlineStr">
+      <c r="C608" t="inlineStr">
         <is>
           <t>4520699635674 -2</t>
         </is>
       </c>
-      <c r="D608" s="19" t="inlineStr">
+      <c r="D608" s="15" t="inlineStr">
         <is>
           <t>b0dmrwrwrd</t>
         </is>
       </c>
-      <c r="E608" s="7" t="inlineStr">
+      <c r="E608" t="inlineStr">
         <is>
           <t>【セット品】銀のスプーン 三ツ星グルメ にっぽんSelect とろリッチ 2種のアソート 48g（6g×8本）×2コ</t>
         </is>
       </c>
-      <c r="F608" s="7" t="n">
+      <c r="F608" t="n">
         <v>799</v>
       </c>
-      <c r="G608" s="7" t="n">
+      <c r="G608" t="n">
         <v>320</v>
       </c>
-      <c r="H608" s="7" t="n">
+      <c r="H608" t="n">
         <v>10</v>
       </c>
-      <c r="I608" s="7">
+      <c r="I608">
         <f>SUM(G608*H608)</f>
         <v/>
       </c>
-      <c r="J608" s="7" t="n"/>
-      <c r="K608" s="7" t="n"/>
     </row>
     <row r="609" ht="13.5" customHeight="1">
       <c r="A609" s="15" t="n">
@@ -27933,164 +27936,160 @@
       </c>
     </row>
     <row r="612" ht="13.5" customHeight="1">
-      <c r="A612" s="19" t="n">
+      <c r="A612" s="22" t="n">
         <v>4970501033592</v>
       </c>
-      <c r="B612" s="19" t="inlineStr">
+      <c r="B612" s="22" t="inlineStr">
         <is>
           <t>b0dq7vk36r</t>
         </is>
       </c>
-      <c r="C612" s="7" t="inlineStr">
+      <c r="C612" s="23" t="inlineStr">
         <is>
           <t>3608/624-a</t>
         </is>
       </c>
-      <c r="D612" s="19" t="inlineStr">
+      <c r="D612" s="22" t="inlineStr">
         <is>
           <t>b0dq7vk36r</t>
         </is>
       </c>
-      <c r="E612" s="7" t="inlineStr">
+      <c r="E612" s="23" t="inlineStr">
         <is>
           <t>【セット品】デビフ おさんぽくん 犬 おやつ 60g(15g×4袋)×4袋セット ササミ 鶏肉 レバー 国産 犬用おやつ 小分け ご褒美 トレーニング 散歩 dbf アソート</t>
         </is>
       </c>
-      <c r="F612" s="7" t="n">
+      <c r="F612" s="23" t="n">
         <v>1480</v>
       </c>
-      <c r="G612" s="7" t="n">
+      <c r="G612" s="23" t="n">
         <v>624</v>
       </c>
-      <c r="H612" s="7" t="n">
+      <c r="H612" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="I612" s="7">
+      <c r="I612" s="23">
         <f>SUM(G612*H612)</f>
         <v/>
       </c>
-      <c r="J612" s="7" t="n"/>
-      <c r="K612" s="7" t="n"/>
+      <c r="J612" s="23" t="n"/>
+      <c r="K612" s="23" t="n"/>
     </row>
     <row r="613" ht="13.5" customHeight="1">
-      <c r="A613" s="19" t="n">
+      <c r="A613" s="15" t="n">
         <v>4970501033608</v>
       </c>
-      <c r="B613" s="19" t="inlineStr">
+      <c r="B613" s="15" t="inlineStr">
         <is>
           <t>b0dq7zx95d</t>
         </is>
       </c>
-      <c r="C613" s="7" t="inlineStr">
+      <c r="C613" t="inlineStr">
         <is>
           <t>3608/624-a</t>
         </is>
       </c>
-      <c r="D613" s="19" t="inlineStr">
+      <c r="D613" s="15" t="inlineStr">
         <is>
           <t>b0dq7vk36r</t>
         </is>
       </c>
-      <c r="E613" s="7" t="inlineStr">
+      <c r="E613" t="inlineStr">
         <is>
           <t>【4個セット】デビフ おさんぽくん ササミ シニア犬用 60g（15g×4袋）×4袋セット 犬 おやつ 国産 小分け 高齢犬 シニア犬 ごほうび トレーニング 散歩 携帯用 おやつ 犬用スナック</t>
         </is>
       </c>
-      <c r="F613" s="7" t="n">
+      <c r="F613" t="n">
         <v>1480</v>
       </c>
-      <c r="G613" s="7" t="n">
+      <c r="G613" t="n">
         <v>624</v>
       </c>
-      <c r="H613" s="7" t="n">
+      <c r="H613" t="n">
         <v>5</v>
       </c>
-      <c r="I613" s="7">
+      <c r="I613">
         <f>SUM(G613*H613)</f>
         <v/>
       </c>
-      <c r="J613" s="7" t="n"/>
-      <c r="K613" s="7" t="n"/>
     </row>
     <row r="614" ht="13.5" customHeight="1">
-      <c r="A614" s="19" t="n">
+      <c r="A614" s="22" t="n">
         <v>4970501033516</v>
       </c>
-      <c r="B614" s="19" t="inlineStr">
+      <c r="B614" s="22" t="inlineStr">
         <is>
           <t>b0dq83k574</t>
         </is>
       </c>
-      <c r="C614" s="7" t="inlineStr">
+      <c r="C614" s="23" t="inlineStr">
         <is>
           <t>3530/780-a</t>
         </is>
       </c>
-      <c r="D614" s="19" t="inlineStr">
+      <c r="D614" s="22" t="inlineStr">
         <is>
           <t>b0dq889rzt</t>
         </is>
       </c>
-      <c r="E614" s="7" t="inlineStr">
+      <c r="E614" s="23" t="inlineStr">
         <is>
           <t>デビフ おすわりくん ササミ ７５ｇ ×４袋セット 犬用 おやつ</t>
         </is>
       </c>
-      <c r="F614" s="7" t="n">
+      <c r="F614" s="23" t="n">
         <v>1280</v>
       </c>
-      <c r="G614" s="7" t="n">
+      <c r="G614" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="H614" s="7" t="n">
+      <c r="H614" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="I614" s="7">
+      <c r="I614" s="23">
         <f>SUM(G614*H614)</f>
         <v/>
       </c>
-      <c r="J614" s="7" t="n"/>
-      <c r="K614" s="7" t="n"/>
+      <c r="J614" s="23" t="n"/>
+      <c r="K614" s="23" t="n"/>
     </row>
     <row r="615" ht="13.5" customHeight="1">
-      <c r="A615" s="19" t="n">
+      <c r="A615" s="15" t="n">
         <v>4970501033530</v>
       </c>
-      <c r="B615" s="19" t="inlineStr">
+      <c r="B615" s="15" t="inlineStr">
         <is>
           <t>b0dq889rzt</t>
         </is>
       </c>
-      <c r="C615" s="7" t="inlineStr">
+      <c r="C615" t="inlineStr">
         <is>
           <t>3530/780-a</t>
         </is>
       </c>
-      <c r="D615" s="19" t="inlineStr">
+      <c r="D615" s="15" t="inlineStr">
         <is>
           <t>b0dq889rzt</t>
         </is>
       </c>
-      <c r="E615" s="7" t="inlineStr">
+      <c r="E615" t="inlineStr">
         <is>
           <t>デビフ おすわりくん 超小粒 ササミ ７５ｇ ×４袋セット 犬用 おやつ</t>
         </is>
       </c>
-      <c r="F615" s="7" t="n">
+      <c r="F615" t="n">
         <v>1280</v>
       </c>
-      <c r="G615" s="7" t="n">
+      <c r="G615" t="n">
         <v>780</v>
       </c>
-      <c r="H615" s="7" t="n">
+      <c r="H615" t="n">
         <v>5</v>
       </c>
-      <c r="I615" s="7">
+      <c r="I615">
         <f>SUM(G615*H615)</f>
         <v/>
       </c>
-      <c r="J615" s="7" t="n"/>
-      <c r="K615" s="7" t="n"/>
     </row>
     <row r="616" ht="13.5" customHeight="1">
       <c r="A616" s="15" t="inlineStr">
@@ -28741,46 +28740,44 @@
       </c>
     </row>
     <row r="630" ht="13.5" customHeight="1">
-      <c r="A630" s="19" t="inlineStr">
+      <c r="A630" s="15" t="inlineStr">
         <is>
           <t>4901301420633</t>
         </is>
       </c>
-      <c r="B630" s="19" t="inlineStr">
+      <c r="B630" s="15" t="inlineStr">
         <is>
           <t>b0dv57g9z1</t>
         </is>
       </c>
-      <c r="C630" s="7" t="inlineStr">
+      <c r="C630" t="inlineStr">
         <is>
           <t>0633/599-a</t>
         </is>
       </c>
-      <c r="D630" s="19" t="inlineStr">
+      <c r="D630" s="15" t="inlineStr">
         <is>
           <t>B0DV57G9Z1</t>
         </is>
       </c>
-      <c r="E630" s="7" t="inlineStr">
+      <c r="E630" t="inlineStr">
         <is>
           <t>花王 ハミングフレア フレアフレグランス フローラル＆スウィート2L 詰め替え 420633 部屋干し 雨の日 部屋 かろやか 香る きれい 清潔 衣類 静電気 防臭 抗菌 赤ちゃん ベビー 洗濯</t>
         </is>
       </c>
-      <c r="F630" s="7" t="n">
+      <c r="F630" t="n">
         <v>2178</v>
       </c>
-      <c r="G630" s="7" t="n">
+      <c r="G630" t="n">
         <v>598</v>
       </c>
-      <c r="H630" s="7" t="n">
+      <c r="H630" t="n">
         <v>7</v>
       </c>
-      <c r="I630" s="7">
+      <c r="I630">
         <f>SUM(G630*H630)</f>
         <v/>
       </c>
-      <c r="J630" s="7" t="n"/>
-      <c r="K630" s="7" t="n"/>
     </row>
     <row r="631" ht="13.5" customHeight="1">
       <c r="A631" s="15" t="inlineStr">
@@ -30418,100 +30415,100 @@
       </c>
     </row>
     <row r="666" ht="13.5" customHeight="1">
-      <c r="A666" s="19" t="inlineStr">
+      <c r="A666" s="22" t="inlineStr">
         <is>
           <t>4987176305701</t>
         </is>
       </c>
-      <c r="B666" s="19" t="inlineStr">
+      <c r="B666" s="22" t="inlineStr">
         <is>
           <t>b0f3d2l45v</t>
         </is>
       </c>
-      <c r="C666" s="7" t="inlineStr">
+      <c r="C666" s="23" t="inlineStr">
         <is>
           <t>5701/1116</t>
         </is>
       </c>
-      <c r="D666" s="19" t="inlineStr">
+      <c r="D666" s="22" t="inlineStr">
         <is>
           <t>b0f3d2l45v</t>
         </is>
       </c>
-      <c r="E666" s="7" t="inlineStr">
+      <c r="E666" s="23" t="inlineStr">
         <is>
           <t>ファブリーズ 消臭スプレー PREMIUM パステルフローラル＆ブロッサムの香り 布用 詰め替え 特大 610mL 除菌 P&amp;Gジャパン</t>
         </is>
       </c>
-      <c r="F666" s="7" t="n">
+      <c r="F666" s="23" t="n">
         <v>1580</v>
       </c>
-      <c r="G666" s="7" t="n">
+      <c r="G666" s="23" t="n">
         <v>720</v>
       </c>
-      <c r="H666" s="7" t="n">
+      <c r="H666" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="I666" s="7">
+      <c r="I666" s="23">
         <f>SUM(G666*H666)</f>
         <v/>
       </c>
-      <c r="J666" s="7" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K666" s="7" t="inlineStr">
+      <c r="J666" s="23" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K666" s="23" t="inlineStr">
         <is>
           <t>4987176305701</t>
         </is>
       </c>
     </row>
     <row r="667" ht="13.5" customHeight="1">
-      <c r="A667" s="19" t="inlineStr">
+      <c r="A667" s="15" t="inlineStr">
         <is>
           <t>4987176305701</t>
         </is>
       </c>
-      <c r="B667" s="19" t="inlineStr">
+      <c r="B667" s="15" t="inlineStr">
         <is>
           <t>b0f3d2l45v-1</t>
         </is>
       </c>
-      <c r="C667" s="7" t="inlineStr">
+      <c r="C667" t="inlineStr">
         <is>
           <t>5701/1116</t>
         </is>
       </c>
-      <c r="D667" s="19" t="inlineStr">
+      <c r="D667" s="15" t="inlineStr">
         <is>
           <t>b0f3d2l45v</t>
         </is>
       </c>
-      <c r="E667" s="7" t="inlineStr">
+      <c r="E667" t="inlineStr">
         <is>
           <t>ファブリーズ 消臭スプレー PREMIUM パステルフローラル＆ブロッサムの香り 布用 詰め替え 特大 610mL×2 除菌 P&amp;Gジャパン</t>
         </is>
       </c>
-      <c r="F667" s="7" t="n">
+      <c r="F667" t="n">
         <v>2480</v>
       </c>
-      <c r="G667" s="7" t="n">
+      <c r="G667" t="n">
         <v>1116</v>
       </c>
-      <c r="H667" s="7" t="n">
+      <c r="H667" t="n">
         <v>6</v>
       </c>
-      <c r="I667" s="7">
+      <c r="I667">
         <f>SUM(G667*H667)</f>
         <v/>
       </c>
-      <c r="J667" s="7" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K667" s="7" t="inlineStr">
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr">
         <is>
           <t>4987176305701</t>
         </is>
@@ -32782,300 +32779,300 @@
       </c>
     </row>
     <row r="721" ht="13.5" customHeight="1">
-      <c r="A721" s="19" t="inlineStr">
+      <c r="A721" s="15" t="inlineStr">
         <is>
           <t>4550391912131</t>
         </is>
       </c>
-      <c r="B721" s="19" t="inlineStr">
+      <c r="B721" s="15" t="inlineStr">
         <is>
           <t>b0frs8pb58</t>
         </is>
       </c>
-      <c r="C721" s="7" t="inlineStr">
+      <c r="C721" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D721" s="19" t="inlineStr">
+      <c r="D721" s="15" t="inlineStr">
         <is>
           <t>B0DVSV4W6Q-2131</t>
         </is>
       </c>
-      <c r="E721" s="7" t="inlineStr">
+      <c r="E721" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + しずくちゃんシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F721" s="7" t="n">
+      <c r="F721" t="n">
         <v>3980</v>
       </c>
-      <c r="G721" s="7" t="n">
+      <c r="G721" t="n">
         <v>1133</v>
       </c>
-      <c r="H721" s="7" t="n">
+      <c r="H721" t="n">
         <v>10</v>
       </c>
-      <c r="I721" s="7">
+      <c r="I721">
         <f>SUM(G721*H721)</f>
         <v/>
       </c>
-      <c r="J721" s="7" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K721" s="7" t="inlineStr">
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
         <is>
           <t>4550391912131</t>
         </is>
       </c>
     </row>
     <row r="722" ht="13.5" customHeight="1">
-      <c r="A722" s="19" t="inlineStr">
+      <c r="A722" s="15" t="inlineStr">
         <is>
           <t>4550391912094</t>
         </is>
       </c>
-      <c r="B722" s="19" t="inlineStr">
+      <c r="B722" s="15" t="inlineStr">
         <is>
           <t>b0frs8pb58</t>
         </is>
       </c>
-      <c r="C722" s="7" t="inlineStr">
+      <c r="C722" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D722" s="19" t="inlineStr">
+      <c r="D722" s="15" t="inlineStr">
         <is>
           <t>B0DVSW1YS7-2094</t>
         </is>
       </c>
-      <c r="E722" s="7" t="inlineStr">
+      <c r="E722" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + しずくちゃんシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F722" s="7" t="n">
+      <c r="F722" t="n">
         <v>3980</v>
       </c>
-      <c r="G722" s="7" t="n">
+      <c r="G722" t="n">
         <v>1133</v>
       </c>
-      <c r="H722" s="7" t="n">
+      <c r="H722" t="n">
         <v>10</v>
       </c>
-      <c r="I722" s="7">
+      <c r="I722">
         <f>SUM(G722*H722)</f>
         <v/>
       </c>
-      <c r="J722" s="7" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K722" s="7" t="inlineStr">
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K722" t="inlineStr">
         <is>
           <t>4550391912094</t>
         </is>
       </c>
     </row>
     <row r="723" ht="13.5" customHeight="1">
-      <c r="A723" s="19" t="inlineStr">
+      <c r="A723" s="15" t="inlineStr">
         <is>
           <t>4550391011469</t>
         </is>
       </c>
-      <c r="B723" s="19" t="inlineStr">
+      <c r="B723" s="15" t="inlineStr">
         <is>
           <t>b0frs8pb58</t>
         </is>
       </c>
-      <c r="C723" s="7" t="inlineStr">
+      <c r="C723" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D723" s="19" t="inlineStr">
+      <c r="D723" s="15" t="inlineStr">
         <is>
           <t>B0FRS8PB58-1469</t>
         </is>
       </c>
-      <c r="E723" s="7" t="inlineStr">
+      <c r="E723" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + しずくちゃんシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F723" s="7" t="n">
+      <c r="F723" t="n">
         <v>3980</v>
       </c>
-      <c r="G723" s="7" t="n">
+      <c r="G723" t="n">
         <v>1133</v>
       </c>
-      <c r="H723" s="7" t="n">
+      <c r="H723" t="n">
         <v>10</v>
       </c>
-      <c r="I723" s="7">
+      <c r="I723">
         <f>SUM(G723*H723)</f>
         <v/>
       </c>
-      <c r="J723" s="7" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K723" s="7" t="inlineStr">
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr">
         <is>
           <t>4550391011469</t>
         </is>
       </c>
     </row>
     <row r="724" ht="13.5" customHeight="1">
-      <c r="A724" s="19" t="inlineStr">
+      <c r="A724" s="15" t="inlineStr">
         <is>
           <t>4550391011360</t>
         </is>
       </c>
-      <c r="B724" s="19" t="inlineStr">
+      <c r="B724" s="15" t="inlineStr">
         <is>
           <t>b0frs8pb58</t>
         </is>
       </c>
-      <c r="C724" s="7" t="inlineStr">
+      <c r="C724" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D724" s="19" t="inlineStr">
+      <c r="D724" s="15" t="inlineStr">
         <is>
           <t>B0FRS8X8M7-1360</t>
         </is>
       </c>
-      <c r="E724" s="7" t="inlineStr">
+      <c r="E724" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + しずくちゃんシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F724" s="7" t="n">
+      <c r="F724" t="n">
         <v>3980</v>
       </c>
-      <c r="G724" s="7" t="n">
+      <c r="G724" t="n">
         <v>1133</v>
       </c>
-      <c r="H724" s="7" t="n">
+      <c r="H724" t="n">
         <v>9</v>
       </c>
-      <c r="I724" s="7">
+      <c r="I724">
         <f>SUM(G724*H724)</f>
         <v/>
       </c>
-      <c r="J724" s="7" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K724" s="7" t="inlineStr">
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
         <is>
           <t>4550391011360</t>
         </is>
       </c>
     </row>
     <row r="725" ht="13.5" customHeight="1">
-      <c r="A725" s="19" t="inlineStr">
+      <c r="A725" s="15" t="inlineStr">
         <is>
           <t>4550391011476</t>
         </is>
       </c>
-      <c r="B725" s="19" t="inlineStr">
+      <c r="B725" s="15" t="inlineStr">
         <is>
           <t>b0frs8pb58</t>
         </is>
       </c>
-      <c r="C725" s="7" t="inlineStr">
+      <c r="C725" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D725" s="19" t="inlineStr">
+      <c r="D725" s="15" t="inlineStr">
         <is>
           <t>B0FRS9W3FT-1476</t>
         </is>
       </c>
-      <c r="E725" s="7" t="inlineStr">
+      <c r="E725" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + しずくちゃんシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F725" s="7" t="n">
+      <c r="F725" t="n">
         <v>3980</v>
       </c>
-      <c r="G725" s="7" t="n">
+      <c r="G725" t="n">
         <v>1133</v>
       </c>
-      <c r="H725" s="7" t="n">
+      <c r="H725" t="n">
         <v>10</v>
       </c>
-      <c r="I725" s="7">
+      <c r="I725">
         <f>SUM(G725*H725)</f>
         <v/>
       </c>
-      <c r="J725" s="7" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K725" s="7" t="inlineStr">
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K725" t="inlineStr">
         <is>
           <t>4550391011476</t>
         </is>
       </c>
     </row>
     <row r="726" ht="13.5" customHeight="1">
-      <c r="A726" s="19" t="inlineStr">
+      <c r="A726" s="15" t="inlineStr">
         <is>
           <t>4550391043903</t>
         </is>
       </c>
-      <c r="B726" s="19" t="inlineStr">
+      <c r="B726" s="15" t="inlineStr">
         <is>
           <t>b0frs8pb58</t>
         </is>
       </c>
-      <c r="C726" s="7" t="inlineStr">
+      <c r="C726" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D726" s="19" t="inlineStr">
+      <c r="D726" s="15" t="inlineStr">
         <is>
           <t>B0FW4K6VZY-3903</t>
         </is>
       </c>
-      <c r="E726" s="7" t="inlineStr">
+      <c r="E726" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + しずくちゃんシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F726" s="7" t="n">
+      <c r="F726" t="n">
         <v>3980</v>
       </c>
-      <c r="G726" s="7" t="n">
+      <c r="G726" t="n">
         <v>1133</v>
       </c>
-      <c r="H726" s="7" t="n">
+      <c r="H726" t="n">
         <v>9</v>
       </c>
-      <c r="I726" s="7">
+      <c r="I726">
         <f>SUM(G726*H726)</f>
         <v/>
       </c>
-      <c r="J726" s="7" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K726" s="7" t="inlineStr">
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
         <is>
           <t>4550391043903</t>
         </is>
@@ -33322,300 +33319,300 @@
       </c>
     </row>
     <row r="733" ht="13.5" customHeight="1">
-      <c r="A733" s="19" t="inlineStr">
+      <c r="A733" s="15" t="inlineStr">
         <is>
           <t>4550391912131</t>
         </is>
       </c>
-      <c r="B733" s="19" t="inlineStr">
+      <c r="B733" s="15" t="inlineStr">
         <is>
           <t>b0frs9w3ft</t>
         </is>
       </c>
-      <c r="C733" s="7" t="inlineStr">
+      <c r="C733" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D733" s="19" t="inlineStr">
+      <c r="D733" s="15" t="inlineStr">
         <is>
           <t>B0DVSV4W6Q-2131</t>
         </is>
       </c>
-      <c r="E733" s="7" t="inlineStr">
+      <c r="E733" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + ボンボンドロップシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F733" s="7" t="n">
+      <c r="F733" t="n">
         <v>3980</v>
       </c>
-      <c r="G733" s="7" t="n">
+      <c r="G733" t="n">
         <v>1133</v>
       </c>
-      <c r="H733" s="7" t="n">
+      <c r="H733" t="n">
         <v>2</v>
       </c>
-      <c r="I733" s="7">
+      <c r="I733">
         <f>SUM(G733*H733)</f>
         <v/>
       </c>
-      <c r="J733" s="7" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K733" s="7" t="inlineStr">
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
         <is>
           <t>4550391912131</t>
         </is>
       </c>
     </row>
     <row r="734" ht="13.5" customHeight="1">
-      <c r="A734" s="19" t="inlineStr">
+      <c r="A734" s="15" t="inlineStr">
         <is>
           <t>4550391912094</t>
         </is>
       </c>
-      <c r="B734" s="19" t="inlineStr">
+      <c r="B734" s="15" t="inlineStr">
         <is>
           <t>b0frs9w3ft</t>
         </is>
       </c>
-      <c r="C734" s="7" t="inlineStr">
+      <c r="C734" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D734" s="19" t="inlineStr">
+      <c r="D734" s="15" t="inlineStr">
         <is>
           <t>B0DVSW1YS7-2094</t>
         </is>
       </c>
-      <c r="E734" s="7" t="inlineStr">
+      <c r="E734" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + ボンボンドロップシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F734" s="7" t="n">
+      <c r="F734" t="n">
         <v>3980</v>
       </c>
-      <c r="G734" s="7" t="n">
+      <c r="G734" t="n">
         <v>1133</v>
       </c>
-      <c r="H734" s="7" t="n">
+      <c r="H734" t="n">
         <v>2</v>
       </c>
-      <c r="I734" s="7">
+      <c r="I734">
         <f>SUM(G734*H734)</f>
         <v/>
       </c>
-      <c r="J734" s="7" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K734" s="7" t="inlineStr">
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
         <is>
           <t>4550391912094</t>
         </is>
       </c>
     </row>
     <row r="735" ht="13.5" customHeight="1">
-      <c r="A735" s="19" t="inlineStr">
+      <c r="A735" s="15" t="inlineStr">
         <is>
           <t>4550391011469</t>
         </is>
       </c>
-      <c r="B735" s="19" t="inlineStr">
+      <c r="B735" s="15" t="inlineStr">
         <is>
           <t>b0frs9w3ft</t>
         </is>
       </c>
-      <c r="C735" s="7" t="inlineStr">
+      <c r="C735" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D735" s="19" t="inlineStr">
+      <c r="D735" s="15" t="inlineStr">
         <is>
           <t>B0FRS8PB58-1469</t>
         </is>
       </c>
-      <c r="E735" s="7" t="inlineStr">
+      <c r="E735" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + ボンボンドロップシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F735" s="7" t="n">
+      <c r="F735" t="n">
         <v>3980</v>
       </c>
-      <c r="G735" s="7" t="n">
+      <c r="G735" t="n">
         <v>1133</v>
       </c>
-      <c r="H735" s="7" t="n">
+      <c r="H735" t="n">
         <v>2</v>
       </c>
-      <c r="I735" s="7">
+      <c r="I735">
         <f>SUM(G735*H735)</f>
         <v/>
       </c>
-      <c r="J735" s="7" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K735" s="7" t="inlineStr">
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
         <is>
           <t>4550391011469</t>
         </is>
       </c>
     </row>
     <row r="736" ht="13.5" customHeight="1">
-      <c r="A736" s="19" t="inlineStr">
+      <c r="A736" s="15" t="inlineStr">
         <is>
           <t>4550391011360</t>
         </is>
       </c>
-      <c r="B736" s="19" t="inlineStr">
+      <c r="B736" s="15" t="inlineStr">
         <is>
           <t>b0frs9w3ft</t>
         </is>
       </c>
-      <c r="C736" s="7" t="inlineStr">
+      <c r="C736" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D736" s="19" t="inlineStr">
+      <c r="D736" s="15" t="inlineStr">
         <is>
           <t>B0FRS8X8M7-1360</t>
         </is>
       </c>
-      <c r="E736" s="7" t="inlineStr">
+      <c r="E736" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + ボンボンドロップシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F736" s="7" t="n">
+      <c r="F736" t="n">
         <v>3980</v>
       </c>
-      <c r="G736" s="7" t="n">
+      <c r="G736" t="n">
         <v>1133</v>
       </c>
-      <c r="H736" s="7" t="n">
+      <c r="H736" t="n">
         <v>2</v>
       </c>
-      <c r="I736" s="7">
+      <c r="I736">
         <f>SUM(G736*H736)</f>
         <v/>
       </c>
-      <c r="J736" s="7" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K736" s="7" t="inlineStr">
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
         <is>
           <t>4550391011360</t>
         </is>
       </c>
     </row>
     <row r="737" ht="13.5" customHeight="1">
-      <c r="A737" s="19" t="inlineStr">
+      <c r="A737" s="15" t="inlineStr">
         <is>
           <t>4550391011476</t>
         </is>
       </c>
-      <c r="B737" s="19" t="inlineStr">
+      <c r="B737" s="15" t="inlineStr">
         <is>
           <t>b0frs9w3ft</t>
         </is>
       </c>
-      <c r="C737" s="7" t="inlineStr">
+      <c r="C737" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D737" s="19" t="inlineStr">
+      <c r="D737" s="15" t="inlineStr">
         <is>
           <t>B0FRS9W3FT-1476</t>
         </is>
       </c>
-      <c r="E737" s="7" t="inlineStr">
+      <c r="E737" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + ボンボンドロップシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F737" s="7" t="n">
+      <c r="F737" t="n">
         <v>3980</v>
       </c>
-      <c r="G737" s="7" t="n">
+      <c r="G737" t="n">
         <v>1133</v>
       </c>
-      <c r="H737" s="7" t="n">
+      <c r="H737" t="n">
         <v>2</v>
       </c>
-      <c r="I737" s="7">
+      <c r="I737">
         <f>SUM(G737*H737)</f>
         <v/>
       </c>
-      <c r="J737" s="7" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K737" s="7" t="inlineStr">
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
         <is>
           <t>4550391011476</t>
         </is>
       </c>
     </row>
     <row r="738" ht="13.5" customHeight="1">
-      <c r="A738" s="19" t="inlineStr">
+      <c r="A738" s="15" t="inlineStr">
         <is>
           <t>4550391043903</t>
         </is>
       </c>
-      <c r="B738" s="19" t="inlineStr">
+      <c r="B738" s="15" t="inlineStr">
         <is>
           <t>b0frs9w3ft</t>
         </is>
       </c>
-      <c r="C738" s="7" t="inlineStr">
+      <c r="C738" t="inlineStr">
         <is>
           <t>1469,1476,1360,3903,2131/1133</t>
         </is>
       </c>
-      <c r="D738" s="19" t="inlineStr">
+      <c r="D738" s="15" t="inlineStr">
         <is>
           <t>B0FW4K6VZY-3903</t>
         </is>
       </c>
-      <c r="E738" s="7" t="inlineStr">
+      <c r="E738" t="inlineStr">
         <is>
           <t>【数量限定 福袋】【計3点セット】【正規品】 クーリア シールバインダー + ボンボンドロップシリーズ + クーリアシール ボンボンドロップシール 3D キラキラ シール シール帳 シール交換 かわいい ぷっくり ぷくぷく 収集 立体 子供 女の子 本家 正規品 本物</t>
         </is>
       </c>
-      <c r="F738" s="7" t="n">
+      <c r="F738" t="n">
         <v>3980</v>
       </c>
-      <c r="G738" s="7" t="n">
+      <c r="G738" t="n">
         <v>1133</v>
       </c>
-      <c r="H738" s="7" t="n">
+      <c r="H738" t="n">
         <v>2</v>
       </c>
-      <c r="I738" s="7">
+      <c r="I738">
         <f>SUM(G738*H738)</f>
         <v/>
       </c>
-      <c r="J738" s="7" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K738" s="7" t="inlineStr">
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
         <is>
           <t>4550391043903</t>
         </is>
@@ -34191,376 +34188,368 @@
       </c>
     </row>
     <row r="752" ht="13.5" customHeight="1">
-      <c r="A752" s="19" t="inlineStr">
+      <c r="A752" s="22" t="inlineStr">
         <is>
           <t>4550391012244</t>
         </is>
       </c>
-      <c r="B752" s="19" t="inlineStr">
+      <c r="B752" s="22" t="inlineStr">
         <is>
           <t>b0gsqcp1mx</t>
         </is>
       </c>
-      <c r="C752" s="7" t="inlineStr">
+      <c r="C752" s="23" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="D752" s="19" t="inlineStr">
+      <c r="D752" s="22" t="inlineStr">
         <is>
           <t>B0GSQ2Q1RY</t>
         </is>
       </c>
-      <c r="E752" s="7" t="inlineStr">
+      <c r="E752" s="23" t="inlineStr">
         <is>
           <t>クーリア ボンボンドロップシール シールバインダー セット キャンディツインズ エナガマーチ ナイトミャウ マイリボンクローゼット ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集</t>
         </is>
       </c>
-      <c r="F752" s="7" t="n">
+      <c r="F752" s="23" t="n">
         <v>2580</v>
       </c>
-      <c r="G752" s="7" t="n">
+      <c r="G752" s="23" t="n">
         <v>1148</v>
       </c>
-      <c r="H752" s="7" t="n">
+      <c r="H752" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="I752" s="7">
+      <c r="I752" s="23">
         <f>SUM(G752*H752)</f>
         <v/>
       </c>
-      <c r="J752" s="7" t="n"/>
-      <c r="K752" s="7" t="n"/>
+      <c r="J752" s="23" t="n"/>
+      <c r="K752" s="23" t="n"/>
     </row>
     <row r="753" ht="13.5" customHeight="1">
-      <c r="A753" s="19" t="inlineStr">
+      <c r="A753" s="22" t="inlineStr">
         <is>
           <t>4550391012251</t>
         </is>
       </c>
-      <c r="B753" s="19" t="inlineStr">
+      <c r="B753" s="22" t="inlineStr">
         <is>
           <t>b0gsqcp1mx</t>
         </is>
       </c>
-      <c r="C753" s="7" t="inlineStr">
+      <c r="C753" s="23" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="D753" s="19" t="inlineStr">
+      <c r="D753" s="22" t="inlineStr">
         <is>
           <t>B0GSQC8JP3</t>
         </is>
       </c>
-      <c r="E753" s="7" t="inlineStr">
+      <c r="E753" s="23" t="inlineStr">
         <is>
           <t>クーリア ボンボンドロップシール シールバインダー セット キャンディツインズ エナガマーチ ナイトミャウ マイリボンクローゼット ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集</t>
         </is>
       </c>
-      <c r="F753" s="7" t="n">
+      <c r="F753" s="23" t="n">
         <v>2580</v>
       </c>
-      <c r="G753" s="7" t="n">
+      <c r="G753" s="23" t="n">
         <v>1148</v>
       </c>
-      <c r="H753" s="7" t="n">
+      <c r="H753" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="I753" s="7">
+      <c r="I753" s="23">
         <f>SUM(G753*H753)</f>
         <v/>
       </c>
-      <c r="J753" s="7" t="n"/>
-      <c r="K753" s="7" t="n"/>
+      <c r="J753" s="23" t="n"/>
+      <c r="K753" s="23" t="n"/>
     </row>
     <row r="754" ht="13.5" customHeight="1">
-      <c r="A754" s="19" t="inlineStr">
+      <c r="A754" s="22" t="inlineStr">
         <is>
           <t>4550391012220</t>
         </is>
       </c>
-      <c r="B754" s="19" t="inlineStr">
+      <c r="B754" s="22" t="inlineStr">
         <is>
           <t>b0gsqcp1mx</t>
         </is>
       </c>
-      <c r="C754" s="7" t="inlineStr">
+      <c r="C754" s="23" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="D754" s="19" t="inlineStr">
+      <c r="D754" s="22" t="inlineStr">
         <is>
           <t>B0GSQCP1MX</t>
         </is>
       </c>
-      <c r="E754" s="7" t="inlineStr">
+      <c r="E754" s="23" t="inlineStr">
         <is>
           <t>クーリア ボンボンドロップシール シールバインダー セット キャンディツインズ エナガマーチ ナイトミャウ マイリボンクローゼット ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集</t>
         </is>
       </c>
-      <c r="F754" s="7" t="n">
+      <c r="F754" s="23" t="n">
         <v>2580</v>
       </c>
-      <c r="G754" s="7" t="n">
+      <c r="G754" s="23" t="n">
         <v>1148</v>
       </c>
-      <c r="H754" s="7" t="n">
+      <c r="H754" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="I754" s="7">
+      <c r="I754" s="23">
         <f>SUM(G754*H754)</f>
         <v/>
       </c>
-      <c r="J754" s="7" t="n"/>
-      <c r="K754" s="7" t="n"/>
+      <c r="J754" s="23" t="n"/>
+      <c r="K754" s="23" t="n"/>
     </row>
     <row r="755" ht="13.5" customHeight="1">
-      <c r="A755" s="19" t="inlineStr">
+      <c r="A755" s="22" t="inlineStr">
         <is>
           <t>4550391012237</t>
         </is>
       </c>
-      <c r="B755" s="19" t="inlineStr">
+      <c r="B755" s="22" t="inlineStr">
         <is>
           <t>b0gsqcp1mx</t>
         </is>
       </c>
-      <c r="C755" s="7" t="inlineStr">
+      <c r="C755" s="23" t="inlineStr">
         <is>
           <t>2220,2237,2244,2251/4592-a</t>
         </is>
       </c>
-      <c r="D755" s="19" t="inlineStr">
+      <c r="D755" s="22" t="inlineStr">
         <is>
           <t>B0GSQHQRV7</t>
         </is>
       </c>
-      <c r="E755" s="7" t="inlineStr">
+      <c r="E755" s="23" t="inlineStr">
         <is>
           <t>クーリア ボンボンドロップシール シールバインダー セット キャンディツインズ エナガマーチ ナイトミャウ マイリボンクローゼット ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集</t>
         </is>
       </c>
-      <c r="F755" s="7" t="n">
+      <c r="F755" s="23" t="n">
         <v>2580</v>
       </c>
-      <c r="G755" s="7" t="n">
+      <c r="G755" s="23" t="n">
         <v>1148</v>
       </c>
-      <c r="H755" s="7" t="n">
+      <c r="H755" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="I755" s="7">
+      <c r="I755" s="23">
         <f>SUM(G755*H755)</f>
         <v/>
       </c>
-      <c r="J755" s="7" t="n"/>
-      <c r="K755" s="7" t="n"/>
+      <c r="J755" s="23" t="n"/>
+      <c r="K755" s="23" t="n"/>
     </row>
     <row r="756" ht="13.5" customHeight="1">
-      <c r="A756" s="19" t="inlineStr">
+      <c r="A756" s="15" t="inlineStr">
         <is>
           <t>4550391012244</t>
         </is>
       </c>
-      <c r="B756" s="19" t="inlineStr">
+      <c r="B756" s="15" t="inlineStr">
         <is>
           <t>b0gsqcp1mx-a</t>
         </is>
       </c>
-      <c r="C756" s="7" t="n">
+      <c r="C756" t="n">
         <v>2000</v>
       </c>
-      <c r="D756" s="19" t="inlineStr">
+      <c r="D756" s="15" t="inlineStr">
         <is>
           <t>B0GSQ2Q1RY</t>
         </is>
       </c>
-      <c r="E756" s="7" t="inlineStr">
+      <c r="E756" t="inlineStr">
         <is>
           <t>【福袋】【計3点セット】【正規品】 クーリア シールバインダーセット(ボンボンドロップシール付き) + しずくちゃんシリーズ + クーリアシール｜ボンボンドロップ ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集 キラキラ 3D立体 女の子 平成女子 本家</t>
         </is>
       </c>
-      <c r="F756" s="7" t="n">
+      <c r="F756" t="n">
         <v>4480</v>
       </c>
-      <c r="G756" s="7" t="n">
+      <c r="G756" t="n">
         <v>2000</v>
       </c>
-      <c r="H756" s="7" t="n">
+      <c r="H756" t="n">
         <v>5</v>
       </c>
-      <c r="I756" s="7">
+      <c r="I756">
         <f>SUM(G756*H756)</f>
         <v/>
       </c>
-      <c r="J756" s="7" t="n"/>
-      <c r="K756" s="7" t="n"/>
     </row>
     <row r="757" ht="13.5" customHeight="1">
-      <c r="A757" s="19" t="inlineStr">
+      <c r="A757" s="15" t="inlineStr">
         <is>
           <t>4550391012251</t>
         </is>
       </c>
-      <c r="B757" s="19" t="inlineStr">
+      <c r="B757" s="15" t="inlineStr">
         <is>
           <t>b0gsqcp1mx-a</t>
         </is>
       </c>
-      <c r="C757" s="7" t="n">
+      <c r="C757" t="n">
         <v>2000</v>
       </c>
-      <c r="D757" s="19" t="inlineStr">
+      <c r="D757" s="15" t="inlineStr">
         <is>
           <t>B0GSQC8JP3</t>
         </is>
       </c>
-      <c r="E757" s="7" t="inlineStr">
+      <c r="E757" t="inlineStr">
         <is>
           <t>【福袋】【計3点セット】【正規品】 クーリア シールバインダーセット(ボンボンドロップシール付き) + しずくちゃんシリーズ + クーリアシール｜ボンボンドロップ ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集 キラキラ 3D立体 女の子 平成女子 本家</t>
         </is>
       </c>
-      <c r="F757" s="7" t="n">
+      <c r="F757" t="n">
         <v>4480</v>
       </c>
-      <c r="G757" s="7" t="n">
+      <c r="G757" t="n">
         <v>2000</v>
       </c>
-      <c r="H757" s="7" t="n">
+      <c r="H757" t="n">
         <v>5</v>
       </c>
-      <c r="I757" s="7">
+      <c r="I757">
         <f>SUM(G757*H757)</f>
         <v/>
       </c>
-      <c r="J757" s="7" t="n"/>
-      <c r="K757" s="7" t="n"/>
     </row>
     <row r="758" ht="13.5" customHeight="1">
-      <c r="A758" s="19" t="inlineStr">
+      <c r="A758" s="15" t="inlineStr">
         <is>
           <t>4550391012220</t>
         </is>
       </c>
-      <c r="B758" s="19" t="inlineStr">
+      <c r="B758" s="15" t="inlineStr">
         <is>
           <t>b0gsqcp1mx-a</t>
         </is>
       </c>
-      <c r="C758" s="7" t="n">
+      <c r="C758" t="n">
         <v>2000</v>
       </c>
-      <c r="D758" s="19" t="inlineStr">
+      <c r="D758" s="15" t="inlineStr">
         <is>
           <t>B0GSQCP1MX</t>
         </is>
       </c>
-      <c r="E758" s="7" t="inlineStr">
+      <c r="E758" t="inlineStr">
         <is>
           <t>【福袋】【計3点セット】【正規品】 クーリア シールバインダーセット(ボンボンドロップシール付き) + しずくちゃんシリーズ + クーリアシール｜ボンボンドロップ ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集 キラキラ 3D立体 女の子 平成女子 本家</t>
         </is>
       </c>
-      <c r="F758" s="7" t="n">
+      <c r="F758" t="n">
         <v>4480</v>
       </c>
-      <c r="G758" s="7" t="n">
+      <c r="G758" t="n">
         <v>2000</v>
       </c>
-      <c r="H758" s="7" t="n">
+      <c r="H758" t="n">
         <v>5</v>
       </c>
-      <c r="I758" s="7">
+      <c r="I758">
         <f>SUM(G758*H758)</f>
         <v/>
       </c>
-      <c r="J758" s="7" t="n"/>
-      <c r="K758" s="7" t="n"/>
     </row>
     <row r="759" ht="13.5" customHeight="1">
-      <c r="A759" s="19" t="inlineStr">
+      <c r="A759" s="22" t="inlineStr">
         <is>
           <t>4550391012237</t>
         </is>
       </c>
-      <c r="B759" s="19" t="inlineStr">
+      <c r="B759" s="22" t="inlineStr">
         <is>
           <t>b0gsqcp1mx-a</t>
         </is>
       </c>
-      <c r="C759" s="7" t="inlineStr">
+      <c r="C759" s="23" t="inlineStr">
         <is>
           <t>2220,2237,2244,2251/4592-a</t>
         </is>
       </c>
-      <c r="D759" s="19" t="inlineStr">
+      <c r="D759" s="22" t="inlineStr">
         <is>
           <t>B0GSQHQRV7</t>
         </is>
       </c>
-      <c r="E759" s="7" t="inlineStr">
+      <c r="E759" s="23" t="inlineStr">
         <is>
           <t>【福袋】【計3点セット】【正規品】 クーリア シールバインダーセット(ボンボンドロップシール付き) + しずくちゃんシリーズ + クーリアシール｜ボンボンドロップ ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集 キラキラ 3D立体 女の子 平成女子 本家</t>
         </is>
       </c>
-      <c r="F759" s="7" t="n">
+      <c r="F759" s="23" t="n">
         <v>4480</v>
       </c>
-      <c r="G759" s="7" t="n">
+      <c r="G759" s="23" t="n">
         <v>2000</v>
       </c>
-      <c r="H759" s="7" t="n">
+      <c r="H759" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="I759" s="7">
+      <c r="I759" s="23">
         <f>SUM(G759*H759)</f>
         <v/>
       </c>
-      <c r="J759" s="7" t="n"/>
-      <c r="K759" s="7" t="n"/>
+      <c r="J759" s="23" t="n"/>
+      <c r="K759" s="23" t="n"/>
     </row>
     <row r="760" ht="13.5" customHeight="1">
-      <c r="A760" s="19" t="inlineStr">
+      <c r="A760" s="15" t="inlineStr">
         <is>
           <t>4550391012237</t>
         </is>
       </c>
-      <c r="B760" s="19" t="inlineStr">
+      <c r="B760" s="15" t="inlineStr">
         <is>
           <t>b0gsqhqrv7</t>
         </is>
       </c>
-      <c r="C760" s="7" t="inlineStr">
+      <c r="C760" t="inlineStr">
         <is>
           <t>2220,2237,2244,2251/4592-a</t>
         </is>
       </c>
-      <c r="D760" s="19" t="inlineStr">
+      <c r="D760" s="15" t="inlineStr">
         <is>
           <t>B0GSQHQRV7</t>
         </is>
       </c>
-      <c r="E760" s="7" t="inlineStr">
+      <c r="E760" t="inlineStr">
         <is>
           <t>【4種セット】 クーリア ボンボンドロップシール シールバインダー 4種 キャンディツインズ エナガマーチ ナイトミャウ マイリボンクローゼット ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集</t>
         </is>
       </c>
-      <c r="F760" s="7" t="n">
+      <c r="F760" t="n">
         <v>9480</v>
       </c>
-      <c r="G760" s="7" t="n">
+      <c r="G760" t="n">
         <v>1148</v>
       </c>
-      <c r="H760" s="7" t="n">
+      <c r="H760" t="n">
         <v>4</v>
       </c>
-      <c r="I760" s="7">
+      <c r="I760">
         <f>SUM(G760*H760)</f>
         <v/>
       </c>
-      <c r="J760" s="7" t="n"/>
-      <c r="K760" s="7" t="n"/>
     </row>
     <row r="761" ht="13.5" customHeight="1">
       <c r="A761" s="15" t="inlineStr">

--- a/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
+++ b/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
@@ -34188,172 +34188,164 @@
       </c>
     </row>
     <row r="752" ht="13.5" customHeight="1">
-      <c r="A752" s="22" t="inlineStr">
+      <c r="A752" s="15" t="inlineStr">
         <is>
           <t>4550391012244</t>
         </is>
       </c>
-      <c r="B752" s="22" t="inlineStr">
+      <c r="B752" s="15" t="inlineStr">
         <is>
           <t>b0gsqcp1mx</t>
         </is>
       </c>
-      <c r="C752" s="23" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D752" s="22" t="inlineStr">
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>2220,2237,2244,2251/1148-a</t>
+        </is>
+      </c>
+      <c r="D752" s="15" t="inlineStr">
         <is>
           <t>B0GSQ2Q1RY</t>
         </is>
       </c>
-      <c r="E752" s="23" t="inlineStr">
+      <c r="E752" t="inlineStr">
         <is>
           <t>クーリア ボンボンドロップシール シールバインダー セット キャンディツインズ エナガマーチ ナイトミャウ マイリボンクローゼット ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集</t>
         </is>
       </c>
-      <c r="F752" s="23" t="n">
+      <c r="F752" t="n">
         <v>2580</v>
       </c>
-      <c r="G752" s="23" t="n">
+      <c r="G752" t="n">
         <v>1148</v>
       </c>
-      <c r="H752" s="23" t="n">
+      <c r="H752" t="n">
         <v>4</v>
       </c>
-      <c r="I752" s="23">
+      <c r="I752">
         <f>SUM(G752*H752)</f>
         <v/>
       </c>
-      <c r="J752" s="23" t="n"/>
-      <c r="K752" s="23" t="n"/>
     </row>
     <row r="753" ht="13.5" customHeight="1">
-      <c r="A753" s="22" t="inlineStr">
+      <c r="A753" s="15" t="inlineStr">
         <is>
           <t>4550391012251</t>
         </is>
       </c>
-      <c r="B753" s="22" t="inlineStr">
+      <c r="B753" s="15" t="inlineStr">
         <is>
           <t>b0gsqcp1mx</t>
         </is>
       </c>
-      <c r="C753" s="23" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D753" s="22" t="inlineStr">
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>2220,2237,2244,2251/1148-a</t>
+        </is>
+      </c>
+      <c r="D753" s="15" t="inlineStr">
         <is>
           <t>B0GSQC8JP3</t>
         </is>
       </c>
-      <c r="E753" s="23" t="inlineStr">
+      <c r="E753" t="inlineStr">
         <is>
           <t>クーリア ボンボンドロップシール シールバインダー セット キャンディツインズ エナガマーチ ナイトミャウ マイリボンクローゼット ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集</t>
         </is>
       </c>
-      <c r="F753" s="23" t="n">
+      <c r="F753" t="n">
         <v>2580</v>
       </c>
-      <c r="G753" s="23" t="n">
+      <c r="G753" t="n">
         <v>1148</v>
       </c>
-      <c r="H753" s="23" t="n">
+      <c r="H753" t="n">
         <v>5</v>
       </c>
-      <c r="I753" s="23">
+      <c r="I753">
         <f>SUM(G753*H753)</f>
         <v/>
       </c>
-      <c r="J753" s="23" t="n"/>
-      <c r="K753" s="23" t="n"/>
     </row>
     <row r="754" ht="13.5" customHeight="1">
-      <c r="A754" s="22" t="inlineStr">
+      <c r="A754" s="15" t="inlineStr">
         <is>
           <t>4550391012220</t>
         </is>
       </c>
-      <c r="B754" s="22" t="inlineStr">
+      <c r="B754" s="15" t="inlineStr">
         <is>
           <t>b0gsqcp1mx</t>
         </is>
       </c>
-      <c r="C754" s="23" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D754" s="22" t="inlineStr">
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>2220,2237,2244,2251/1148-a</t>
+        </is>
+      </c>
+      <c r="D754" s="15" t="inlineStr">
         <is>
           <t>B0GSQCP1MX</t>
         </is>
       </c>
-      <c r="E754" s="23" t="inlineStr">
+      <c r="E754" t="inlineStr">
         <is>
           <t>クーリア ボンボンドロップシール シールバインダー セット キャンディツインズ エナガマーチ ナイトミャウ マイリボンクローゼット ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集</t>
         </is>
       </c>
-      <c r="F754" s="23" t="n">
+      <c r="F754" t="n">
         <v>2580</v>
       </c>
-      <c r="G754" s="23" t="n">
+      <c r="G754" t="n">
         <v>1148</v>
       </c>
-      <c r="H754" s="23" t="n">
+      <c r="H754" t="n">
         <v>3</v>
       </c>
-      <c r="I754" s="23">
+      <c r="I754">
         <f>SUM(G754*H754)</f>
         <v/>
       </c>
-      <c r="J754" s="23" t="n"/>
-      <c r="K754" s="23" t="n"/>
     </row>
     <row r="755" ht="13.5" customHeight="1">
-      <c r="A755" s="22" t="inlineStr">
+      <c r="A755" s="15" t="inlineStr">
         <is>
           <t>4550391012237</t>
         </is>
       </c>
-      <c r="B755" s="22" t="inlineStr">
+      <c r="B755" s="15" t="inlineStr">
         <is>
           <t>b0gsqcp1mx</t>
         </is>
       </c>
-      <c r="C755" s="23" t="inlineStr">
-        <is>
-          <t>2220,2237,2244,2251/4592-a</t>
-        </is>
-      </c>
-      <c r="D755" s="22" t="inlineStr">
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>2220,2237,2244,2251/1148-a</t>
+        </is>
+      </c>
+      <c r="D755" s="15" t="inlineStr">
         <is>
           <t>B0GSQHQRV7</t>
         </is>
       </c>
-      <c r="E755" s="23" t="inlineStr">
+      <c r="E755" t="inlineStr">
         <is>
           <t>クーリア ボンボンドロップシール シールバインダー セット キャンディツインズ エナガマーチ ナイトミャウ マイリボンクローゼット ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集</t>
         </is>
       </c>
-      <c r="F755" s="23" t="n">
+      <c r="F755" t="n">
         <v>2580</v>
       </c>
-      <c r="G755" s="23" t="n">
+      <c r="G755" t="n">
         <v>1148</v>
       </c>
-      <c r="H755" s="23" t="n">
+      <c r="H755" t="n">
         <v>2</v>
       </c>
-      <c r="I755" s="23">
+      <c r="I755">
         <f>SUM(G755*H755)</f>
         <v/>
       </c>
-      <c r="J755" s="23" t="n"/>
-      <c r="K755" s="23" t="n"/>
     </row>
     <row r="756" ht="13.5" customHeight="1">
       <c r="A756" s="15" t="inlineStr">
@@ -34470,46 +34462,44 @@
       </c>
     </row>
     <row r="759" ht="13.5" customHeight="1">
-      <c r="A759" s="22" t="inlineStr">
+      <c r="A759" s="15" t="inlineStr">
         <is>
           <t>4550391012237</t>
         </is>
       </c>
-      <c r="B759" s="22" t="inlineStr">
+      <c r="B759" s="15" t="inlineStr">
         <is>
           <t>b0gsqcp1mx-a</t>
         </is>
       </c>
-      <c r="C759" s="23" t="inlineStr">
-        <is>
-          <t>2220,2237,2244,2251/4592-a</t>
-        </is>
-      </c>
-      <c r="D759" s="22" t="inlineStr">
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="D759" s="15" t="inlineStr">
         <is>
           <t>B0GSQHQRV7</t>
         </is>
       </c>
-      <c r="E759" s="23" t="inlineStr">
+      <c r="E759" t="inlineStr">
         <is>
           <t>【福袋】【計3点セット】【正規品】 クーリア シールバインダーセット(ボンボンドロップシール付き) + しずくちゃんシリーズ + クーリアシール｜ボンボンドロップ ボンドロ かわいい 立体 シール ぷっくり ぷくぷく シール交換 収集 キラキラ 3D立体 女の子 平成女子 本家</t>
         </is>
       </c>
-      <c r="F759" s="23" t="n">
+      <c r="F759" t="n">
         <v>4480</v>
       </c>
-      <c r="G759" s="23" t="n">
+      <c r="G759" t="n">
         <v>2000</v>
       </c>
-      <c r="H759" s="23" t="n">
+      <c r="H759" t="n">
         <v>5</v>
       </c>
-      <c r="I759" s="23">
+      <c r="I759">
         <f>SUM(G759*H759)</f>
         <v/>
       </c>
-      <c r="J759" s="23" t="n"/>
-      <c r="K759" s="23" t="n"/>
     </row>
     <row r="760" ht="13.5" customHeight="1">
       <c r="A760" s="15" t="inlineStr">

--- a/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
+++ b/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
@@ -2097,42 +2097,40 @@
       </c>
     </row>
     <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" s="22" t="inlineStr">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>4550451352129</t>
         </is>
       </c>
-      <c r="B44" s="22" t="n">
+      <c r="B44" s="15" t="n">
         <v>4550451352129</v>
       </c>
-      <c r="C44" s="23" t="inlineStr">
-        <is>
-          <t>2129,2167/1210</t>
-        </is>
-      </c>
-      <c r="D44" s="22" t="n">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2129,2167,2136/1815</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="n">
         <v>4550451352129</v>
       </c>
-      <c r="E44" s="23" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>【セット品】サンリオ コットンパフィーシール 3種セット マイメロディ クロミ シナモロール ハローキティ レオパード クラックス COTTON PUFFY ぷっくりシール デコシール 手帳デコ ノートデコ キャラクターシール 文房具 ステッカー アソートセット シール 立体 かわいい</t>
         </is>
       </c>
-      <c r="F44" s="23" t="n">
+      <c r="F44" t="n">
         <v>4480</v>
       </c>
-      <c r="G44" s="23" t="n">
+      <c r="G44" t="n">
         <v>605</v>
       </c>
-      <c r="H44" s="23" t="n">
+      <c r="H44" t="n">
         <v>3</v>
       </c>
-      <c r="I44" s="23">
+      <c r="I44">
         <f>SUM(G44*H44)</f>
         <v/>
       </c>
-      <c r="J44" s="23" t="n"/>
-      <c r="K44" s="23" t="n"/>
     </row>
     <row r="45" ht="13.5" customHeight="1">
       <c r="A45" s="15" t="inlineStr">
@@ -24858,44 +24856,42 @@
       </c>
     </row>
     <row r="538" ht="13.5" customHeight="1">
-      <c r="A538" s="22" t="n">
+      <c r="A538" s="15" t="n">
         <v>4901301441720</v>
       </c>
-      <c r="B538" s="22" t="inlineStr">
+      <c r="B538" s="15" t="inlineStr">
         <is>
           <t>b0d9znvl7q</t>
         </is>
       </c>
-      <c r="C538" s="23" t="inlineStr">
-        <is>
-          <t>0633/599-a</t>
-        </is>
-      </c>
-      <c r="D538" s="22" t="inlineStr">
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>4901301441720</t>
+        </is>
+      </c>
+      <c r="D538" s="15" t="inlineStr">
         <is>
           <t>B0DV57G9Z1</t>
         </is>
       </c>
-      <c r="E538" s="24" t="inlineStr">
+      <c r="E538" s="21" t="inlineStr">
         <is>
           <t>花王 フレアフレグランス ハミングフレア リッチフローラル 本体 520ml 部屋干し 雨の日 部屋 かろやか 香る きれい 清潔 衣類 静電気 防臭 抗菌 赤ちゃん ベビー 洗濯</t>
         </is>
       </c>
-      <c r="F538" s="23" t="n">
+      <c r="F538" t="n">
         <v>1280</v>
       </c>
-      <c r="G538" s="23" t="n">
+      <c r="G538" t="n">
         <v>219</v>
       </c>
-      <c r="H538" s="23" t="n">
+      <c r="H538" t="n">
         <v>9</v>
       </c>
-      <c r="I538" s="23">
+      <c r="I538">
         <f>SUM(G538*H538)</f>
         <v/>
       </c>
-      <c r="J538" s="23" t="n"/>
-      <c r="K538" s="23" t="n"/>
     </row>
     <row r="539" ht="13.5" customHeight="1">
       <c r="A539" s="15" t="inlineStr">
@@ -25568,50 +25564,50 @@
       </c>
     </row>
     <row r="554" ht="13.5" customHeight="1">
-      <c r="A554" s="22" t="inlineStr">
+      <c r="A554" s="15" t="inlineStr">
         <is>
           <t>4987176260635</t>
         </is>
       </c>
-      <c r="B554" s="22" t="inlineStr">
+      <c r="B554" s="15" t="inlineStr">
         <is>
           <t>b0dfyjnwjt</t>
         </is>
       </c>
-      <c r="C554" s="25" t="inlineStr">
+      <c r="C554" s="20" t="inlineStr">
         <is>
           <t>4987176260635-2</t>
         </is>
       </c>
-      <c r="D554" s="22" t="inlineStr">
+      <c r="D554" s="15" t="inlineStr">
         <is>
           <t>b0dfyjnwjt</t>
         </is>
       </c>
-      <c r="E554" s="23" t="inlineStr">
+      <c r="E554" t="inlineStr">
         <is>
           <t>レノア リセット セラム ホワイトリリーの香り つめかえ 特大 750mL×2個セット 柔軟剤 部屋干し 雨の日 部屋 かろやか 香る きれい 清潔 衣類 静電気 防臭 抗菌 赤ちゃん ベビー 洗濯</t>
         </is>
       </c>
-      <c r="F554" s="23" t="n">
+      <c r="F554" t="n">
         <v>2980</v>
       </c>
-      <c r="G554" s="23" t="n">
+      <c r="G554" t="n">
         <v>1856</v>
       </c>
-      <c r="H554" s="23" t="n">
+      <c r="H554" t="n">
         <v>1</v>
       </c>
-      <c r="I554" s="23">
+      <c r="I554">
         <f>SUM(G554*H554)</f>
         <v/>
       </c>
-      <c r="J554" s="23" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K554" s="23" t="inlineStr">
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
         <is>
           <t>4987176260635</t>
         </is>
@@ -26731,48 +26727,48 @@
       </c>
     </row>
     <row r="582" ht="13.5" customHeight="1">
-      <c r="A582" s="22" t="n">
+      <c r="A582" s="15" t="n">
         <v>4987176260659</v>
       </c>
-      <c r="B582" s="22" t="inlineStr">
+      <c r="B582" s="15" t="inlineStr">
         <is>
           <t>b0dktchdgk</t>
         </is>
       </c>
-      <c r="C582" s="23" t="inlineStr">
+      <c r="C582" t="inlineStr">
         <is>
           <t>4987176260659-2</t>
         </is>
       </c>
-      <c r="D582" s="22" t="inlineStr">
+      <c r="D582" s="15" t="inlineStr">
         <is>
           <t>b0dfyjnwjt</t>
         </is>
       </c>
-      <c r="E582" s="23" t="inlineStr">
+      <c r="E582" t="inlineStr">
         <is>
           <t>レノア リセット セラム ホワイトピーチ&amp;カモミールの香り つめかえ 特大 750mL×2個セット 柔軟剤 部屋干し 雨の日 部屋 かろやか 香る きれい 清潔 衣類 静電気 防臭 抗菌 赤ちゃん ベビー 洗濯</t>
         </is>
       </c>
-      <c r="F582" s="23" t="n">
+      <c r="F582" t="n">
         <v>2980</v>
       </c>
-      <c r="G582" s="23" t="n">
+      <c r="G582" t="n">
         <v>1856</v>
       </c>
-      <c r="H582" s="23" t="n">
+      <c r="H582" t="n">
         <v>3</v>
       </c>
-      <c r="I582" s="23">
+      <c r="I582">
         <f>SUM(G582*H582)</f>
         <v/>
       </c>
-      <c r="J582" s="23" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K582" s="23" t="inlineStr">
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr">
         <is>
           <t>4987176260635</t>
         </is>
@@ -26879,44 +26875,42 @@
       </c>
     </row>
     <row r="585" ht="13.5" customHeight="1">
-      <c r="A585" s="22" t="n">
+      <c r="A585" s="15" t="n">
         <v>4520699694367</v>
       </c>
-      <c r="B585" s="22" t="inlineStr">
+      <c r="B585" s="15" t="inlineStr">
         <is>
           <t>b0dmrwrwrd</t>
         </is>
       </c>
-      <c r="C585" s="23" t="inlineStr">
-        <is>
-          <t>4520699635674 -2</t>
-        </is>
-      </c>
-      <c r="D585" s="22" t="inlineStr">
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>4520699694367-2</t>
+        </is>
+      </c>
+      <c r="D585" s="15" t="inlineStr">
         <is>
           <t>b0dmrwrwrd</t>
         </is>
       </c>
-      <c r="E585" s="23" t="inlineStr">
+      <c r="E585" t="inlineStr">
         <is>
           <t>【セット品】銀のスプーン 三ツ星グルメ にっぽんSelect とろリッチ 2種のお魚味アソート 48g（6g×8本）×2コ 総合栄養食</t>
         </is>
       </c>
-      <c r="F585" s="23" t="n">
+      <c r="F585" t="n">
         <v>799</v>
       </c>
-      <c r="G585" s="23" t="n">
+      <c r="G585" t="n">
         <v>380</v>
       </c>
-      <c r="H585" s="23" t="n">
+      <c r="H585" t="n">
         <v>98</v>
       </c>
-      <c r="I585" s="23">
+      <c r="I585">
         <f>SUM(G585*H585)</f>
         <v/>
       </c>
-      <c r="J585" s="23" t="n"/>
-      <c r="K585" s="23" t="n"/>
     </row>
     <row r="586" ht="13.5" customHeight="1">
       <c r="A586" s="15" t="inlineStr">
@@ -27936,44 +27930,42 @@
       </c>
     </row>
     <row r="612" ht="13.5" customHeight="1">
-      <c r="A612" s="22" t="n">
+      <c r="A612" s="15" t="n">
         <v>4970501033592</v>
       </c>
-      <c r="B612" s="22" t="inlineStr">
+      <c r="B612" s="15" t="inlineStr">
         <is>
           <t>b0dq7vk36r</t>
         </is>
       </c>
-      <c r="C612" s="23" t="inlineStr">
-        <is>
-          <t>3608/624-a</t>
-        </is>
-      </c>
-      <c r="D612" s="22" t="inlineStr">
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>3585,3592/624</t>
+        </is>
+      </c>
+      <c r="D612" s="15" t="inlineStr">
         <is>
           <t>b0dq7vk36r</t>
         </is>
       </c>
-      <c r="E612" s="23" t="inlineStr">
+      <c r="E612" t="inlineStr">
         <is>
           <t>【セット品】デビフ おさんぽくん 犬 おやつ 60g(15g×4袋)×4袋セット ササミ 鶏肉 レバー 国産 犬用おやつ 小分け ご褒美 トレーニング 散歩 dbf アソート</t>
         </is>
       </c>
-      <c r="F612" s="23" t="n">
+      <c r="F612" t="n">
         <v>1480</v>
       </c>
-      <c r="G612" s="23" t="n">
+      <c r="G612" t="n">
         <v>624</v>
       </c>
-      <c r="H612" s="23" t="n">
+      <c r="H612" t="n">
         <v>2</v>
       </c>
-      <c r="I612" s="23">
+      <c r="I612">
         <f>SUM(G612*H612)</f>
         <v/>
       </c>
-      <c r="J612" s="23" t="n"/>
-      <c r="K612" s="23" t="n"/>
     </row>
     <row r="613" ht="13.5" customHeight="1">
       <c r="A613" s="15" t="n">
@@ -28014,44 +28006,42 @@
       </c>
     </row>
     <row r="614" ht="13.5" customHeight="1">
-      <c r="A614" s="22" t="n">
+      <c r="A614" s="15" t="n">
         <v>4970501033516</v>
       </c>
-      <c r="B614" s="22" t="inlineStr">
+      <c r="B614" s="15" t="inlineStr">
         <is>
           <t>b0dq83k574</t>
         </is>
       </c>
-      <c r="C614" s="23" t="inlineStr">
-        <is>
-          <t>3530/780-a</t>
-        </is>
-      </c>
-      <c r="D614" s="22" t="inlineStr">
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>3516/780-a</t>
+        </is>
+      </c>
+      <c r="D614" s="15" t="inlineStr">
         <is>
           <t>b0dq889rzt</t>
         </is>
       </c>
-      <c r="E614" s="23" t="inlineStr">
+      <c r="E614" t="inlineStr">
         <is>
           <t>デビフ おすわりくん ササミ ７５ｇ ×４袋セット 犬用 おやつ</t>
         </is>
       </c>
-      <c r="F614" s="23" t="n">
+      <c r="F614" t="n">
         <v>1280</v>
       </c>
-      <c r="G614" s="23" t="n">
+      <c r="G614" t="n">
         <v>780</v>
       </c>
-      <c r="H614" s="23" t="n">
+      <c r="H614" t="n">
         <v>5</v>
       </c>
-      <c r="I614" s="23">
+      <c r="I614">
         <f>SUM(G614*H614)</f>
         <v/>
       </c>
-      <c r="J614" s="23" t="n"/>
-      <c r="K614" s="23" t="n"/>
     </row>
     <row r="615" ht="13.5" customHeight="1">
       <c r="A615" s="15" t="n">
@@ -30415,50 +30405,50 @@
       </c>
     </row>
     <row r="666" ht="13.5" customHeight="1">
-      <c r="A666" s="22" t="inlineStr">
+      <c r="A666" s="15" t="inlineStr">
         <is>
           <t>4987176305701</t>
         </is>
       </c>
-      <c r="B666" s="22" t="inlineStr">
+      <c r="B666" s="15" t="inlineStr">
         <is>
           <t>b0f3d2l45v</t>
         </is>
       </c>
-      <c r="C666" s="23" t="inlineStr">
-        <is>
-          <t>5701/1116</t>
-        </is>
-      </c>
-      <c r="D666" s="22" t="inlineStr">
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="D666" s="15" t="inlineStr">
         <is>
           <t>b0f3d2l45v</t>
         </is>
       </c>
-      <c r="E666" s="23" t="inlineStr">
+      <c r="E666" t="inlineStr">
         <is>
           <t>ファブリーズ 消臭スプレー PREMIUM パステルフローラル＆ブロッサムの香り 布用 詰め替え 特大 610mL 除菌 P&amp;Gジャパン</t>
         </is>
       </c>
-      <c r="F666" s="23" t="n">
+      <c r="F666" t="n">
         <v>1580</v>
       </c>
-      <c r="G666" s="23" t="n">
+      <c r="G666" t="n">
         <v>720</v>
       </c>
-      <c r="H666" s="23" t="n">
+      <c r="H666" t="n">
         <v>2</v>
       </c>
-      <c r="I666" s="23">
+      <c r="I666">
         <f>SUM(G666*H666)</f>
         <v/>
       </c>
-      <c r="J666" s="23" t="inlineStr">
-        <is>
-          <t>✓ 一致（SKU）</t>
-        </is>
-      </c>
-      <c r="K666" s="23" t="inlineStr">
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>✓ 一致（SKU）</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr">
         <is>
           <t>4987176305701</t>
         </is>

--- a/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
+++ b/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
@@ -26757,7 +26757,7 @@
         <v>1856</v>
       </c>
       <c r="H582" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I582">
         <f>SUM(G582*H582)</f>

--- a/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
+++ b/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
@@ -35775,7 +35775,9 @@
           <t>【3個セット】アース製薬 アース虫よけ線香 モンスーン 100巻×3 大容量 300巻 ラベンダーの香り 虫除け線香 蚊取り線香 屋外用 虫よけ対策 アウトドア キャンプ 登山 農作業 ガーデニング ブヨ アブ ユスリカ 不快害虫 長時間燃焼 約7時間 業務用 家庭用 夏対策 防虫線香</t>
         </is>
       </c>
-      <c r="G793" s="6" t="n"/>
+      <c r="G793" t="n">
+        <v>3819</v>
+      </c>
       <c r="H793" t="n">
         <v>5</v>
       </c>
@@ -36311,7 +36313,9 @@
           <t>【2個セット】 日本カルシウム工業 アルカリイオン水素水×2個セット 浄水スティック 浄水パック ペットボトル用 携帯浄水器 水質改善 カルキ除去 アルカリイオン水 日本製 節約 防災対策 【お茶パック付き】</t>
         </is>
       </c>
-      <c r="G810" s="6" t="n"/>
+      <c r="G810" t="n">
+        <v>7304</v>
+      </c>
       <c r="H810" t="n">
         <v>5</v>
       </c>
@@ -36499,7 +36503,9 @@
           <t>ペティオ (Petio)犬用食器 Porta 木目調 陶器食器 S</t>
         </is>
       </c>
-      <c r="G816" s="6" t="n"/>
+      <c r="G816" t="n">
+        <v>132</v>
+      </c>
       <c r="H816" t="n">
         <v>5</v>
       </c>
@@ -36655,7 +36661,9 @@
           <t>ペティオ (Petio) 猫用おもちゃ とぎぐるみ 組み替えられるハニワポール</t>
         </is>
       </c>
-      <c r="G821" s="6" t="n"/>
+      <c r="G821" t="n">
+        <v>605</v>
+      </c>
       <c r="H821" t="n">
         <v>5</v>
       </c>
@@ -36843,7 +36851,9 @@
           <t>ブラウン シリーズ5 電気シェーバー 52-M1200s ミント 髭剃り メンズ 電動シェーバー 防水 充電式 コードレス キワゾリトリマー ディープキャッチ網刃 深剃り 肌にやさしい 剃刀 シェービング 男性用 ヒゲ剃り フェイスケア スキンケア 旅行 出張 ケア トラベルケース付き</t>
         </is>
       </c>
-      <c r="G827" s="6" t="n"/>
+      <c r="G827" t="n">
+        <v>8980</v>
+      </c>
       <c r="H827" t="n">
         <v>15</v>
       </c>
@@ -36937,7 +36947,9 @@
           <t>エクセル コスモスラクト バード 30ml 鳥用 乳酸菌生成エキス インコ サプリメント 小鳥サプリ 鳥サプリ 栄養補給 腸内環境 健康維持 健康管理 セキセイインコ オカメインコ 文鳥 フィンチ 換羽期 栄養補助食品 乳酸菌サプリ 小鳥用品 鳥用品 ペットサプリ 国産</t>
         </is>
       </c>
-      <c r="G830" s="6" t="n"/>
+      <c r="G830" t="n">
+        <v>1287</v>
+      </c>
       <c r="H830" t="n">
         <v>10</v>
       </c>
@@ -36999,7 +37011,9 @@
           <t>【6個セット】GOAT’S MILK ゴートミルク ソープ 6個セット スイートベビーパウダーの香り 固形石鹸 ヤギミルク 保湿 しっとり 洗顔 ボディケア スキンケア 全身用 乾燥肌 ケア ヒアルロン酸 コラーゲン シアバター まとめ買い 女性 男性 家族用</t>
         </is>
       </c>
-      <c r="G832" s="6" t="n"/>
+      <c r="G832" t="n">
+        <v>438</v>
+      </c>
       <c r="H832" t="n">
         <v>4</v>
       </c>
@@ -37507,7 +37521,9 @@
           <t>【6個セット】ビオレ 冷タオル 子どもも使える 5本入×6 冷却タオル ひんやりタオル クールタオル 冷感タオル 熱中症対策 暑さ対策 首 冷やす 携帯用 冷感グッズ 外出用 夏 スポーツ アウトドア 通学 通園 部活 運動会 花王 まとめ買い</t>
         </is>
       </c>
-      <c r="G848" s="6" t="n"/>
+      <c r="G848" t="n">
+        <v>3294</v>
+      </c>
       <c r="H848" t="n">
         <v>2</v>
       </c>
@@ -37807,7 +37823,9 @@
           <t>【セット品】いなば 鴨づくし 60g×18袋 3種セット キャットフード 猫用 パウチ ウェットフード かもだし仕立て かも軟骨入り かつお節入り ゼリータイプ 一般食 国産 猫 ごはん ねこ エサ 餌 レトルト パウチフード 水分補給 バラエティ アソート まとめ買い INABA</t>
         </is>
       </c>
-      <c r="G858" s="6" t="n"/>
+      <c r="G858" t="n">
+        <v>1182</v>
+      </c>
       <c r="H858" t="n">
         <v>2</v>
       </c>
@@ -37837,7 +37855,9 @@
           <t>【セット品】アース モンスーン 虫よけ線香 100巻 保存缶セット アース製薬 防虫 蚊取り線香 線香立て付き 缶入り 屋外 キャンプ ガーデニング ベランダ 庭 アウトドア 虫除け 蚊 ハエ ブヨ ヤブ蚊 対策 大容量 まとめ買い</t>
         </is>
       </c>
-      <c r="G859" s="6" t="n"/>
+      <c r="G859" t="n">
+        <v>2649</v>
+      </c>
       <c r="H859" t="n">
         <v>4</v>
       </c>

--- a/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
+++ b/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
@@ -35471,6 +35471,11 @@
       </c>
     </row>
     <row r="784" ht="13.5" customHeight="1">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>4562149054178</t>
+        </is>
+      </c>
       <c r="B784" s="19" t="inlineStr">
         <is>
           <t>4562149054178-2</t>
@@ -35503,6 +35508,11 @@
       </c>
     </row>
     <row r="785" ht="13.5" customHeight="1">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>4901301438683</t>
+        </is>
+      </c>
       <c r="B785" s="19" t="inlineStr">
         <is>
           <t>4901301438683-2</t>
@@ -35535,6 +35545,11 @@
       </c>
     </row>
     <row r="786" ht="13.5" customHeight="1">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>4902201213219</t>
+        </is>
+      </c>
       <c r="B786" s="19" t="inlineStr">
         <is>
           <t>4902201213219-12</t>
@@ -35567,6 +35582,11 @@
       </c>
     </row>
     <row r="787" ht="13.5" customHeight="1">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>4903301186427</t>
+        </is>
+      </c>
       <c r="B787" s="19" t="inlineStr">
         <is>
           <t>4903301186427-3</t>
@@ -35599,6 +35619,11 @@
       </c>
     </row>
     <row r="788" ht="13.5" customHeight="1">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>4903301355687</t>
+        </is>
+      </c>
       <c r="B788" s="19" t="inlineStr">
         <is>
           <t>4903301355687-3</t>
@@ -35629,6 +35654,11 @@
       </c>
     </row>
     <row r="789" ht="13.5" customHeight="1">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>4987176315830</t>
+        </is>
+      </c>
       <c r="B789" s="19" t="inlineStr">
         <is>
           <t>4987176315830</t>
@@ -35659,6 +35689,11 @@
       </c>
     </row>
     <row r="790" ht="13.5" customHeight="1">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>4571411204838</t>
+        </is>
+      </c>
       <c r="B790" s="19" t="inlineStr">
         <is>
           <t>4571411204838</t>
@@ -35915,6 +35950,11 @@
       </c>
     </row>
     <row r="798" ht="13.5" customHeight="1">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>4987176354273</t>
+        </is>
+      </c>
       <c r="B798" s="19" t="inlineStr">
         <is>
           <t>b0fy1j62w9-2</t>
@@ -35979,6 +36019,11 @@
       </c>
     </row>
     <row r="800" ht="13.5" customHeight="1">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>4901301466426</t>
+        </is>
+      </c>
       <c r="B800" s="19" t="inlineStr">
         <is>
           <t>b0gm6xjjst-2</t>
@@ -36011,6 +36056,11 @@
       </c>
     </row>
     <row r="801" ht="13.5" customHeight="1">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>4901301466303</t>
+        </is>
+      </c>
       <c r="B801" s="19" t="inlineStr">
         <is>
           <t>b0gm6y6yj4-2</t>
@@ -36169,6 +36219,11 @@
       </c>
     </row>
     <row r="806" ht="13.5" customHeight="1">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>4544059032330</t>
+        </is>
+      </c>
       <c r="B806" s="19" t="inlineStr">
         <is>
           <t>b001ai51n2-2</t>
@@ -36199,6 +36254,11 @@
       </c>
     </row>
     <row r="807" ht="13.5" customHeight="1">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>4544059032866</t>
+        </is>
+      </c>
       <c r="B807" s="19" t="inlineStr">
         <is>
           <t>b0174ujypa-2</t>
@@ -36229,6 +36289,11 @@
       </c>
     </row>
     <row r="808" ht="13.5" customHeight="1">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>4571104713265</t>
+        </is>
+      </c>
       <c r="B808" s="19" t="inlineStr">
         <is>
           <t>b0179h2jvo-6</t>
@@ -36293,6 +36358,11 @@
       </c>
     </row>
     <row r="810" ht="13.5" customHeight="1">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>4544059033153</t>
+        </is>
+      </c>
       <c r="B810" s="19" t="inlineStr">
         <is>
           <t>b01gzq2xyi-2</t>
@@ -36325,6 +36395,11 @@
       </c>
     </row>
     <row r="811" ht="13.5" customHeight="1">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>4589530701046</t>
+        </is>
+      </c>
       <c r="B811" s="19" t="inlineStr">
         <is>
           <t>b01mtemme0</t>
@@ -36357,6 +36432,11 @@
       </c>
     </row>
     <row r="812" ht="13.5" customHeight="1">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>4514610005035</t>
+        </is>
+      </c>
       <c r="B812" s="19" t="inlineStr">
         <is>
           <t>b075gk2mzw</t>
@@ -36419,6 +36499,11 @@
       </c>
     </row>
     <row r="814" ht="13.5" customHeight="1">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>5060144645562</t>
+        </is>
+      </c>
       <c r="B814" s="19" t="inlineStr">
         <is>
           <t>b07vl5tf8z</t>
@@ -36451,6 +36536,11 @@
       </c>
     </row>
     <row r="815" ht="13.5" customHeight="1">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>4902430898706</t>
+        </is>
+      </c>
       <c r="B815" s="19" t="inlineStr">
         <is>
           <t>b08gpdl9ky</t>
@@ -36483,6 +36573,11 @@
       </c>
     </row>
     <row r="816" ht="13.5" customHeight="1">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>4903588265082</t>
+        </is>
+      </c>
       <c r="B816" s="19" t="inlineStr">
         <is>
           <t>b08xbhldw9</t>
@@ -36515,6 +36610,11 @@
       </c>
     </row>
     <row r="817" ht="13.5" customHeight="1">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>4901301397355</t>
+        </is>
+      </c>
       <c r="B817" s="19" t="inlineStr">
         <is>
           <t>b0915ngd2j-6</t>
@@ -36611,6 +36711,11 @@
       </c>
     </row>
     <row r="820" ht="13.5" customHeight="1">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>4891228313036</t>
+        </is>
+      </c>
       <c r="B820" s="19" t="inlineStr">
         <is>
           <t>b0bs3k6d56</t>
@@ -36641,6 +36746,11 @@
       </c>
     </row>
     <row r="821" ht="13.5" customHeight="1">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>4903588271632</t>
+        </is>
+      </c>
       <c r="B821" s="19" t="inlineStr">
         <is>
           <t>b0bx2rl7zx</t>
@@ -36705,6 +36815,11 @@
       </c>
     </row>
     <row r="823" ht="13.5" customHeight="1">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>4987176194398</t>
+        </is>
+      </c>
       <c r="B823" s="19" t="inlineStr">
         <is>
           <t>b0ckj4fcmh-2</t>
@@ -36735,6 +36850,11 @@
       </c>
     </row>
     <row r="824" ht="13.5" customHeight="1">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>4582228251861</t>
+        </is>
+      </c>
       <c r="B824" s="19" t="inlineStr">
         <is>
           <t>b0cp51ckvd</t>
@@ -36767,6 +36887,11 @@
       </c>
     </row>
     <row r="825" ht="13.5" customHeight="1">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>4987176228697</t>
+        </is>
+      </c>
       <c r="B825" s="19" t="inlineStr">
         <is>
           <t>b0csctf87w-2</t>
@@ -36799,6 +36924,11 @@
       </c>
     </row>
     <row r="826" ht="13.5" customHeight="1">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>4902111776996</t>
+        </is>
+      </c>
       <c r="B826" s="19" t="inlineStr">
         <is>
           <t>b0ctbg4l1x</t>
@@ -36831,6 +36961,11 @@
       </c>
     </row>
     <row r="827" ht="13.5" customHeight="1">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>4987176180261</t>
+        </is>
+      </c>
       <c r="B827" s="19" t="inlineStr">
         <is>
           <t>b0ctq1xfrl</t>
@@ -36895,6 +37030,11 @@
       </c>
     </row>
     <row r="829" ht="13.5" customHeight="1">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>4901301432391</t>
+        </is>
+      </c>
       <c r="B829" s="19" t="inlineStr">
         <is>
           <t>b0czhr33rf-3</t>
@@ -36927,6 +37067,11 @@
       </c>
     </row>
     <row r="830" ht="13.5" customHeight="1">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>4542750119701</t>
+        </is>
+      </c>
       <c r="B830" s="19" t="inlineStr">
         <is>
           <t>b0d1p44ht9</t>
@@ -36959,6 +37104,11 @@
       </c>
     </row>
     <row r="831" ht="13.5" customHeight="1">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>4987176243928</t>
+        </is>
+      </c>
       <c r="B831" s="19" t="inlineStr">
         <is>
           <t>b0d6g9rw9y-2</t>
@@ -36991,6 +37141,11 @@
       </c>
     </row>
     <row r="832" ht="13.5" customHeight="1">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>4549777709625</t>
+        </is>
+      </c>
       <c r="B832" s="19" t="inlineStr">
         <is>
           <t>b0d6gckfcp</t>
@@ -37023,6 +37178,11 @@
       </c>
     </row>
     <row r="833" ht="13.5" customHeight="1">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>4979750819926</t>
+        </is>
+      </c>
       <c r="B833" s="19" t="inlineStr">
         <is>
           <t>b0d8pmzsgc</t>
@@ -37055,6 +37215,11 @@
       </c>
     </row>
     <row r="834" ht="13.5" customHeight="1">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>4987176312822</t>
+        </is>
+      </c>
       <c r="B834" s="19" t="inlineStr">
         <is>
           <t>b0dvsjz4fn</t>
@@ -37085,6 +37250,11 @@
       </c>
     </row>
     <row r="835" ht="13.5" customHeight="1">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>0194644233532</t>
+        </is>
+      </c>
       <c r="B835" s="19" t="inlineStr">
         <is>
           <t>b0dwmpnclc</t>
@@ -37117,6 +37287,11 @@
       </c>
     </row>
     <row r="836" ht="13.5" customHeight="1">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>4901301450135</t>
+        </is>
+      </c>
       <c r="B836" s="19" t="inlineStr">
         <is>
           <t>b0dxnblx52-3</t>
@@ -37149,6 +37324,11 @@
       </c>
     </row>
     <row r="837" ht="13.5" customHeight="1">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>4987176305657</t>
+        </is>
+      </c>
       <c r="B837" s="19" t="inlineStr">
         <is>
           <t>b0f3d1ls31</t>
@@ -37181,6 +37361,11 @@
       </c>
     </row>
     <row r="838" ht="13.5" customHeight="1">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>0840414620421</t>
+        </is>
+      </c>
       <c r="B838" s="19" t="inlineStr">
         <is>
           <t>b0f7zf7w9p</t>
@@ -37213,6 +37398,11 @@
       </c>
     </row>
     <row r="839" ht="13.5" customHeight="1">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>4987176309099</t>
+        </is>
+      </c>
       <c r="B839" s="19" t="inlineStr">
         <is>
           <t>b0fcfk55zk-4</t>
@@ -37245,6 +37435,11 @@
       </c>
     </row>
     <row r="840" ht="13.5" customHeight="1">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>4903301375173</t>
+        </is>
+      </c>
       <c r="B840" s="19" t="inlineStr">
         <is>
           <t>b0fpvbqv49-2</t>
@@ -37341,6 +37536,11 @@
       </c>
     </row>
     <row r="843" ht="13.5" customHeight="1">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>0840414684973</t>
+        </is>
+      </c>
       <c r="B843" s="19" t="inlineStr">
         <is>
           <t>b0g2tqzmy1</t>
@@ -37373,6 +37573,11 @@
       </c>
     </row>
     <row r="844" ht="13.5" customHeight="1">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>0840414639447</t>
+        </is>
+      </c>
       <c r="B844" s="19" t="inlineStr">
         <is>
           <t>b0g3ycrjkx</t>
@@ -37405,6 +37610,11 @@
       </c>
     </row>
     <row r="845" ht="13.5" customHeight="1">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>4987176364166</t>
+        </is>
+      </c>
       <c r="B845" s="19" t="inlineStr">
         <is>
           <t>b0g4mfq7cw-2</t>
@@ -37437,6 +37647,11 @@
       </c>
     </row>
     <row r="846" ht="13.5" customHeight="1">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>4987176364289</t>
+        </is>
+      </c>
       <c r="B846" s="19" t="inlineStr">
         <is>
           <t>b0g4mhkqp8-2</t>
@@ -37469,6 +37684,11 @@
       </c>
     </row>
     <row r="847" ht="13.5" customHeight="1">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>4901301466280</t>
+        </is>
+      </c>
       <c r="B847" s="19" t="inlineStr">
         <is>
           <t>b0gm6xmjmn-2</t>
@@ -37501,6 +37721,11 @@
       </c>
     </row>
     <row r="848" ht="13.5" customHeight="1">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>4901301448330</t>
+        </is>
+      </c>
       <c r="B848" s="19" t="inlineStr">
         <is>
           <t>b0h6xvg97y-6</t>
@@ -37623,6 +37848,11 @@
       </c>
     </row>
     <row r="852" ht="13.5" customHeight="1">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>4901477705435</t>
+        </is>
+      </c>
       <c r="B852" s="19" t="inlineStr">
         <is>
           <t>b0hb31z1y8</t>
@@ -37653,6 +37883,11 @@
       </c>
     </row>
     <row r="853" ht="13.5" customHeight="1">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>4936201100941</t>
+        </is>
+      </c>
       <c r="B853" s="19" t="inlineStr">
         <is>
           <t>b0hb3sfnpm</t>
@@ -56651,6 +56886,11 @@
       </c>
     </row>
     <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>4562149054178</t>
+        </is>
+      </c>
       <c r="B413" s="25" t="inlineStr">
         <is>
           <t>4562149054178-2</t>
@@ -56683,6 +56923,11 @@
       </c>
     </row>
     <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>4901301438683</t>
+        </is>
+      </c>
       <c r="B414" s="25" t="inlineStr">
         <is>
           <t>4901301438683-2</t>
@@ -56715,6 +56960,11 @@
       </c>
     </row>
     <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>4902201213219</t>
+        </is>
+      </c>
       <c r="B415" s="23" t="inlineStr">
         <is>
           <t>4902201213219-12</t>
@@ -56747,6 +56997,11 @@
       </c>
     </row>
     <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>4903301186427</t>
+        </is>
+      </c>
       <c r="B416" s="23" t="inlineStr">
         <is>
           <t>4903301186427-3</t>
@@ -56779,6 +57034,11 @@
       </c>
     </row>
     <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>4571411204838</t>
+        </is>
+      </c>
       <c r="B417" s="23" t="inlineStr">
         <is>
           <t>4571411204838</t>
@@ -57003,6 +57263,11 @@
       </c>
     </row>
     <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>4987176354273</t>
+        </is>
+      </c>
       <c r="B424" s="23" t="inlineStr">
         <is>
           <t>b0fy1j62w9-2</t>
@@ -57067,6 +57332,11 @@
       </c>
     </row>
     <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>4901301466426</t>
+        </is>
+      </c>
       <c r="B426" s="23" t="inlineStr">
         <is>
           <t>b0gm6xjjst-2</t>
@@ -57099,6 +57369,11 @@
       </c>
     </row>
     <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>4901301466303</t>
+        </is>
+      </c>
       <c r="B427" s="23" t="inlineStr">
         <is>
           <t>b0gm6y6yj4-2</t>
@@ -57227,6 +57502,11 @@
       </c>
     </row>
     <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>4571104713265</t>
+        </is>
+      </c>
       <c r="B431" s="23" t="inlineStr">
         <is>
           <t>b0179h2jvo-6</t>
@@ -57291,6 +57571,11 @@
       </c>
     </row>
     <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>4589530701046</t>
+        </is>
+      </c>
       <c r="B433" s="23" t="inlineStr">
         <is>
           <t>b01mtemme0</t>
@@ -57355,6 +57640,11 @@
       </c>
     </row>
     <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>5060144645562</t>
+        </is>
+      </c>
       <c r="B435" s="23" t="inlineStr">
         <is>
           <t>b07vl5tf8z</t>
@@ -57385,6 +57675,11 @@
       </c>
     </row>
     <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>4902430898706</t>
+        </is>
+      </c>
       <c r="B436" s="23" t="inlineStr">
         <is>
           <t>b08gpdl9ky</t>
@@ -57417,6 +57712,11 @@
       </c>
     </row>
     <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>4901301397355</t>
+        </is>
+      </c>
       <c r="B437" s="23" t="inlineStr">
         <is>
           <t>b0915ngd2j-6</t>
@@ -57545,6 +57845,11 @@
       </c>
     </row>
     <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>4582228251861</t>
+        </is>
+      </c>
       <c r="B441" s="23" t="inlineStr">
         <is>
           <t>b0cp51ckvd</t>
@@ -57577,6 +57882,11 @@
       </c>
     </row>
     <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>4987176228697</t>
+        </is>
+      </c>
       <c r="B442" s="23" t="inlineStr">
         <is>
           <t>b0csctf87w-2</t>
@@ -57609,6 +57919,11 @@
       </c>
     </row>
     <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>4902111776996</t>
+        </is>
+      </c>
       <c r="B443" s="23" t="inlineStr">
         <is>
           <t>b0ctbg4l1x</t>
@@ -57673,6 +57988,11 @@
       </c>
     </row>
     <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>4901301432391</t>
+        </is>
+      </c>
       <c r="B445" s="23" t="inlineStr">
         <is>
           <t>b0czhr33rf-3</t>
@@ -57705,6 +58025,11 @@
       </c>
     </row>
     <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>4987176243928</t>
+        </is>
+      </c>
       <c r="B446" s="23" t="inlineStr">
         <is>
           <t>b0d6g9rw9y-2</t>
@@ -57737,6 +58062,11 @@
       </c>
     </row>
     <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>4979750819926</t>
+        </is>
+      </c>
       <c r="B447" s="23" t="inlineStr">
         <is>
           <t>b0d8pmzsgc</t>
@@ -57769,6 +58099,11 @@
       </c>
     </row>
     <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>0194644233532</t>
+        </is>
+      </c>
       <c r="B448" s="23" t="inlineStr">
         <is>
           <t>b0dwmpnclc</t>
@@ -57801,6 +58136,11 @@
       </c>
     </row>
     <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>4901301450135</t>
+        </is>
+      </c>
       <c r="B449" s="23" t="inlineStr">
         <is>
           <t>b0dxnblx52-3</t>
@@ -57833,6 +58173,11 @@
       </c>
     </row>
     <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>4987176305657</t>
+        </is>
+      </c>
       <c r="B450" s="23" t="inlineStr">
         <is>
           <t>b0f3d1ls31</t>
@@ -57865,6 +58210,11 @@
       </c>
     </row>
     <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>0840414620421</t>
+        </is>
+      </c>
       <c r="B451" s="23" t="inlineStr">
         <is>
           <t>b0f7zf7w9p</t>
@@ -57897,6 +58247,11 @@
       </c>
     </row>
     <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>4987176309099</t>
+        </is>
+      </c>
       <c r="B452" s="23" t="inlineStr">
         <is>
           <t>b0fcfk55zk-4</t>
@@ -57929,6 +58284,11 @@
       </c>
     </row>
     <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>4903301375173</t>
+        </is>
+      </c>
       <c r="B453" s="23" t="inlineStr">
         <is>
           <t>b0fpvbqv49-2</t>
@@ -58025,6 +58385,11 @@
       </c>
     </row>
     <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>0840414684973</t>
+        </is>
+      </c>
       <c r="B456" s="23" t="inlineStr">
         <is>
           <t>b0g2tqzmy1</t>
@@ -58057,6 +58422,11 @@
       </c>
     </row>
     <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>0840414639447</t>
+        </is>
+      </c>
       <c r="B457" s="23" t="inlineStr">
         <is>
           <t>b0g3ycrjkx</t>
@@ -58089,6 +58459,11 @@
       </c>
     </row>
     <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>4987176364166</t>
+        </is>
+      </c>
       <c r="B458" s="23" t="inlineStr">
         <is>
           <t>b0g4mfq7cw-2</t>
@@ -58121,6 +58496,11 @@
       </c>
     </row>
     <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>4987176364289</t>
+        </is>
+      </c>
       <c r="B459" s="23" t="inlineStr">
         <is>
           <t>b0g4mhkqp8-2</t>
@@ -58153,6 +58533,11 @@
       </c>
     </row>
     <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>4901301466280</t>
+        </is>
+      </c>
       <c r="B460" s="23" t="inlineStr">
         <is>
           <t>b0gm6xmjmn-2</t>

--- a/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
+++ b/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
@@ -35644,7 +35644,9 @@
           <t>【3個セット】トップ クリアリキッド抗菌 部屋干し 詰め替え 500g×3個セット ライオン 洗濯洗剤 液体洗剤 詰替え 抗菌 消臭 部屋干し洗剤 生乾き臭 ニオイ対策 まとめ買い 衣類用洗剤 洗濯用 液体 衣類ケア 洗濯用品 日用品 ストック 家庭用</t>
         </is>
       </c>
-      <c r="G788" s="6" t="n"/>
+      <c r="G788" t="n">
+        <v>525</v>
+      </c>
       <c r="H788" t="n">
         <v>3</v>
       </c>
@@ -36113,7 +36115,9 @@
           <t>【セット品】サラテクト 虫よけスプレー 無香料 400mL＋虫よけシート BIGサイズ 20枚入 セット アース製薬 虫除けスプレー 虫よけウェットティッシュ 虫よけシート 蚊 ブヨ マダニ アウトドア キャンプ レジャー 公園 散歩 ガーデニング 外出 携帯用 家族 大人 子ども 防虫</t>
         </is>
       </c>
-      <c r="G802" s="6" t="n"/>
+      <c r="G802" t="n">
+        <v>1126</v>
+      </c>
       <c r="H802" t="n">
         <v>5</v>
       </c>
@@ -36736,7 +36740,9 @@
           <t>ブルドッグ オリジナル 替刃 4個入 カミソリ替刃 5枚刃 アロエ配合 スムーザー 首振りヘッド キワ剃りトリマー シェービング 替え刃 メンズ 男性用 深剃り 肌にやさしい フェイスケア グルーミング バンブーホルダー対応 グラスホルダー対応 交換用 カートリッジ 純正 替え刃</t>
         </is>
       </c>
-      <c r="G820" s="6" t="n"/>
+      <c r="G820" t="n">
+        <v>1576</v>
+      </c>
       <c r="H820" t="n">
         <v>44</v>
       </c>
@@ -36840,7 +36846,9 @@
           <t>【2個セット】アリエール ジェルボール4D 微香 詰め替え メガジャンボ 83個×2個セット P&amp;G 洗濯洗剤 ジェルボール 洗剤 4D 抗菌 消臭 部屋干し すすぎ1回 詰替え 大容量 まとめ買い 黄ばみ 黒ずみ エリそで汚れ 洗濯槽防カビ ドラム式 縦型 ランドリー 日用品 ストック</t>
         </is>
       </c>
-      <c r="G823" s="6" t="n"/>
+      <c r="G823" t="n">
+        <v>3770</v>
+      </c>
       <c r="H823" t="n">
         <v>4</v>
       </c>
@@ -37240,7 +37248,9 @@
           <t>レノア 超消臭1WEEK 柔軟剤 スポーツ フレッシュシトラスの香り 詰替用 1900mL 大容量 生乾き臭 汗臭 消臭 抗菌 部屋干し 静電気防止 花粉ブロック 衣類ケア タオル スポーツウェア 作業着 ユニフォーム 寝具 ふんわり P&amp;G</t>
         </is>
       </c>
-      <c r="G834" s="6" t="n"/>
+      <c r="G834" t="n">
+        <v>1194</v>
+      </c>
       <c r="H834" t="n">
         <v>35</v>
       </c>
@@ -37778,7 +37788,9 @@
           <t>【セット品】アリエール ジェルボールPRO 爽快クール 涼感 リフレッシュクールの香り 大容量 85個+13個セット P&amp;G 洗濯洗剤 ジェルボール 洗剤 詰め合わせ 消臭 抗菌 部屋干し すすぎ1回 黄ばみ 黒ずみ エリそで汚れ ドラム式 縦型洗濯機 まとめ買い 日用品</t>
         </is>
       </c>
-      <c r="G849" s="6" t="n"/>
+      <c r="G849" t="n">
+        <v>2946</v>
+      </c>
       <c r="H849" t="n">
         <v>5</v>
       </c>
@@ -37808,7 +37820,9 @@
           <t>【セット品】IROKA イロカ ミュゲインザエア 本体540mL+詰め替え650mLセット 花王 柔軟剤 液体柔軟剤 香水のような香り ミュゲ リリー 上質 透明感 限定 詰替え 消臭 静電気防止 シワ防止 衣類ケア フレグランス 大容量 ランドリー 日用品 ギフト まとめ買い</t>
         </is>
       </c>
-      <c r="G850" s="6" t="n"/>
+      <c r="G850" t="n">
+        <v>1988</v>
+      </c>
       <c r="H850" t="n">
         <v>3</v>
       </c>
@@ -37838,7 +37852,9 @@
           <t>【セット品】アリエール MiRAi 超濃縮 液体洗剤 爽快COOL 本体410g+詰め替え920gセット 涼感 リフレッシュクールの香り P&amp;G 洗濯洗剤 コンパクト 消臭 抗菌 部屋干し 黄ばみ 黒ずみ エリそで汚れ すすぎ1回 ドラム式 縦型 省スペース 本体 詰替え 日用品 まとめ買い</t>
         </is>
       </c>
-      <c r="G851" s="6" t="n"/>
+      <c r="G851" t="n">
+        <v>1406</v>
+      </c>
       <c r="H851" t="n">
         <v>5</v>
       </c>
@@ -37873,7 +37889,9 @@
           <t>【2個セット】プライバシー UVパウダー SPF50+ PA++++ メイクの上から使える UVカット フェイスパウダー テカリ防止 化粧直し 日焼け止め 紫外線対策 ウォータープルーフ 透明パウダー 毛穴カバー 皮脂吸着 顔用 化粧品 UVケア メイクキープ 黒龍堂</t>
         </is>
       </c>
-      <c r="G852" s="6" t="n"/>
+      <c r="G852" t="n">
+        <v>1882</v>
+      </c>
       <c r="H852" t="n">
         <v>5</v>
       </c>
@@ -37938,7 +37956,9 @@
           <t>【6種セット】クーリア もっちもちシール シールセット クラウドポップタイム えながのおいしいごはん おやすみバニー なかよしうみあにまる ゆるかふぇびより ふわふわぽっぷ デコレーションシール 手帳 シール帳 ノート アルバム コレクション かわいい 文房具</t>
         </is>
       </c>
-      <c r="G854" s="6" t="n"/>
+      <c r="G854" t="n">
+        <v>1224</v>
+      </c>
       <c r="H854" t="n">
         <v>10</v>
       </c>
@@ -37968,7 +37988,9 @@
           <t>【6種セット】クーリア ウォーターシール スイートピンクタイム ハムハムエンジェル シュガーミエル シーグラスアイランド もちえなが キャンディツインズ デコシール キャラクター デコレーションシール 手帳 シール帳 ノート アルバム コレクション かわいい 文房具</t>
         </is>
       </c>
-      <c r="G855" s="6" t="n"/>
+      <c r="G855" t="n">
+        <v>1452</v>
+      </c>
       <c r="H855" t="n">
         <v>10</v>
       </c>
@@ -37998,7 +38020,9 @@
           <t>【6種セット】クーリア ウォーターシール スイートマジカル はむはむハムちゃん チャーミングルーム きらりんエナガマーチ ももいろみるく マイスパークル デコレーションシール シール 手帳 ノート アルバム スマホケース ステッカー まとめ買い 公式 本物 正規品</t>
         </is>
       </c>
-      <c r="G856" s="6" t="n"/>
+      <c r="G856" t="n">
+        <v>1452</v>
+      </c>
       <c r="H856" t="n">
         <v>10</v>
       </c>
@@ -38028,7 +38052,9 @@
           <t>【6種セット】クーリア クリアジェムステッカー エンジェル ストロベリー レモン グレープ ソーダ プラネット デコレーションシール クリアステッカー ジェムシール シール 手帳 ノート アルバム スマホケース ラッピング まとめ買い 公式 本物 正規品</t>
         </is>
       </c>
-      <c r="G857" s="6" t="n"/>
+      <c r="G857" t="n">
+        <v>1531</v>
+      </c>
       <c r="H857" t="n">
         <v>10</v>
       </c>

--- a/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
+++ b/MomijiStore_OS/01_InventoryManagement/SourceData/Import/楽天在庫リスト_import.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="165" formatCode="0_ "/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <color rgb="FF000000"/>
@@ -97,6 +97,9 @@
       <family val="2"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -178,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -209,6 +212,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -38503,10 +38507,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K468"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" style="23" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="19.33203125" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
@@ -38519,64 +38523,64 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="B1" s="24" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>楽天商品管理番号（ASIN)</t>
         </is>
       </c>
-      <c r="C1" s="13" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>商品番号</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>SKU管理番号</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>商品名</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>販売価格</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>単価</t>
         </is>
       </c>
-      <c r="H1" s="13" t="inlineStr">
+      <c r="H1" s="26" t="inlineStr">
         <is>
           <t>在庫数</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
+      <c r="I1" s="26" t="inlineStr">
         <is>
           <t>合計金額</t>
         </is>
       </c>
-      <c r="J1" s="13" t="inlineStr">
+      <c r="J1" s="26" t="inlineStr">
         <is>
           <t>JAN検証結果</t>
         </is>
       </c>
-      <c r="K1" s="13" t="inlineStr">
+      <c r="K1" s="26" t="inlineStr">
         <is>
           <t>AmazonのJAN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>14942298s1</t>
         </is>
@@ -38611,7 +38615,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>14993499s1</t>
         </is>
@@ -38651,7 +38655,7 @@
           <t>3264680009754</t>
         </is>
       </c>
-      <c r="B4" s="23" t="n">
+      <c r="B4" t="n">
         <v>3264680009754</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -38687,7 +38691,7 @@
           <t>3264680009761</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" t="n">
         <v>3264680009761</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -38725,7 +38729,7 @@
           <t>3264680009761</t>
         </is>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B6" t="n">
         <v>3264680009761</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -38763,7 +38767,7 @@
           <t>3264680009761</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B7" t="n">
         <v>3264680009761</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -38801,7 +38805,7 @@
           <t>3264680009808</t>
         </is>
       </c>
-      <c r="B8" s="23" t="n">
+      <c r="B8" t="n">
         <v>3264680009808</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -38837,7 +38841,7 @@
           <t>3264680015946</t>
         </is>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" t="n">
         <v>3264680015946</v>
       </c>
       <c r="C9" t="n">
@@ -38871,7 +38875,7 @@
           <t>4513574020337</t>
         </is>
       </c>
-      <c r="B10" s="23" t="n">
+      <c r="B10" t="n">
         <v>4513574020337</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -38907,7 +38911,7 @@
           <t>4550391011919</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" t="n">
         <v>4550391011919</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -38943,7 +38947,7 @@
           <t>4550391011926</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n">
+      <c r="B12" t="n">
         <v>4550391011926</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -38979,7 +38983,7 @@
           <t>4550391011940</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n">
+      <c r="B13" t="n">
         <v>4550391011940</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -39015,7 +39019,7 @@
           <t>4550391012053</t>
         </is>
       </c>
-      <c r="B14" s="23" t="n">
+      <c r="B14" t="n">
         <v>4550391012053</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -39051,7 +39055,7 @@
           <t>4550391012121</t>
         </is>
       </c>
-      <c r="B15" s="23" t="n">
+      <c r="B15" t="n">
         <v>4550391012121</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -39087,7 +39091,7 @@
           <t>4550391012435</t>
         </is>
       </c>
-      <c r="B16" s="23" t="n">
+      <c r="B16" t="n">
         <v>4550391012435</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -39123,7 +39127,7 @@
           <t>4550391012541</t>
         </is>
       </c>
-      <c r="B17" s="23" t="n">
+      <c r="B17" t="n">
         <v>4550391012541</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -39159,7 +39163,7 @@
           <t>4550391012718</t>
         </is>
       </c>
-      <c r="B18" s="23" t="n">
+      <c r="B18" t="n">
         <v>4550391012718</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -39197,7 +39201,7 @@
           <t>4550391042821</t>
         </is>
       </c>
-      <c r="B19" s="23" t="n">
+      <c r="B19" t="n">
         <v>4550391042821</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -39233,7 +39237,7 @@
           <t>4550391046508</t>
         </is>
       </c>
-      <c r="B20" s="23" t="n">
+      <c r="B20" t="n">
         <v>4550391046508</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -39271,7 +39275,7 @@
           <t>4550391046508</t>
         </is>
       </c>
-      <c r="B21" s="23" t="n">
+      <c r="B21" t="n">
         <v>4550391046508</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -39309,7 +39313,7 @@
           <t>4550391046508</t>
         </is>
       </c>
-      <c r="B22" s="23" t="n">
+      <c r="B22" t="n">
         <v>4550391046508</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -39347,7 +39351,7 @@
           <t>4550391046508</t>
         </is>
       </c>
-      <c r="B23" s="23" t="n">
+      <c r="B23" t="n">
         <v>4550391046508</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -39385,7 +39389,7 @@
           <t>4550391062164</t>
         </is>
       </c>
-      <c r="B24" s="23" t="n">
+      <c r="B24" t="n">
         <v>4550391062164</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -39421,7 +39425,7 @@
           <t>4550391062171</t>
         </is>
       </c>
-      <c r="B25" s="23" t="n">
+      <c r="B25" t="n">
         <v>4550391062164</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -39457,7 +39461,7 @@
           <t>4550391062188</t>
         </is>
       </c>
-      <c r="B26" s="23" t="n">
+      <c r="B26" t="n">
         <v>4550391062164</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -39493,7 +39497,7 @@
           <t>4550391062195</t>
         </is>
       </c>
-      <c r="B27" s="23" t="n">
+      <c r="B27" t="n">
         <v>4550391062164</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -39529,7 +39533,7 @@
           <t>4550391062201</t>
         </is>
       </c>
-      <c r="B28" s="23" t="n">
+      <c r="B28" t="n">
         <v>4550391062164</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -39565,7 +39569,7 @@
           <t>4550391062218</t>
         </is>
       </c>
-      <c r="B29" s="23" t="n">
+      <c r="B29" t="n">
         <v>4550391062164</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -39601,7 +39605,7 @@
           <t>4550391910564</t>
         </is>
       </c>
-      <c r="B30" s="23" t="n">
+      <c r="B30" t="n">
         <v>4550391910564</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -39637,7 +39641,7 @@
           <t>4550391911226</t>
         </is>
       </c>
-      <c r="B31" s="23" t="n">
+      <c r="B31" t="n">
         <v>4550391911226</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -39673,7 +39677,7 @@
           <t>4550432282988</t>
         </is>
       </c>
-      <c r="B32" s="23" t="n">
+      <c r="B32" t="n">
         <v>4550432282988</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -39709,7 +39713,7 @@
           <t>4550451352129</t>
         </is>
       </c>
-      <c r="B33" s="23" t="n">
+      <c r="B33" t="n">
         <v>4550451352129</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -39745,7 +39749,7 @@
           <t>4550451352129</t>
         </is>
       </c>
-      <c r="B34" s="23" t="n">
+      <c r="B34" t="n">
         <v>4550451352167</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -39781,7 +39785,7 @@
           <t>4550451375821</t>
         </is>
       </c>
-      <c r="B35" s="23" t="n">
+      <c r="B35" t="n">
         <v>4550451375821</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -39817,7 +39821,7 @@
           <t>4562201211907</t>
         </is>
       </c>
-      <c r="B36" s="23" t="n">
+      <c r="B36" t="n">
         <v>4562201211907</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -39853,7 +39857,7 @@
           <t>4571411204838</t>
         </is>
       </c>
-      <c r="B37" s="23" t="n">
+      <c r="B37" t="n">
         <v>4571411204838</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -39889,7 +39893,7 @@
           <t>4571411205538</t>
         </is>
       </c>
-      <c r="B38" s="23" t="n">
+      <c r="B38" t="n">
         <v>4571411205538</v>
       </c>
       <c r="C38" t="inlineStr">
@@ -39925,7 +39929,7 @@
           <t>4571411205552</t>
         </is>
       </c>
-      <c r="B39" s="23" t="n">
+      <c r="B39" t="n">
         <v>4571411205552</v>
       </c>
       <c r="C39" t="inlineStr">
@@ -39961,7 +39965,7 @@
           <t>4571411208300</t>
         </is>
       </c>
-      <c r="B40" s="23" t="n">
+      <c r="B40" t="n">
         <v>4571411208300</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -39997,7 +40001,7 @@
           <t>4571411208324</t>
         </is>
       </c>
-      <c r="B41" s="23" t="n">
+      <c r="B41" t="n">
         <v>4571411208324</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -40033,7 +40037,7 @@
           <t>4571411215971</t>
         </is>
       </c>
-      <c r="B42" s="23" t="n">
+      <c r="B42" t="n">
         <v>4571411215971</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -40069,7 +40073,7 @@
           <t>4571509303191</t>
         </is>
       </c>
-      <c r="B43" s="23" t="n">
+      <c r="B43" t="n">
         <v>4571509303191</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -40105,7 +40109,7 @@
           <t>4580313723736</t>
         </is>
       </c>
-      <c r="B44" s="23" t="n">
+      <c r="B44" t="n">
         <v>4580313723736</v>
       </c>
       <c r="C44" t="inlineStr">
@@ -40143,7 +40147,7 @@
           <t>4580313723736</t>
         </is>
       </c>
-      <c r="B45" s="23" t="n">
+      <c r="B45" t="n">
         <v>4580313723736</v>
       </c>
       <c r="C45" t="inlineStr">
@@ -40181,7 +40185,7 @@
           <t>4580313723736</t>
         </is>
       </c>
-      <c r="B46" s="23" t="n">
+      <c r="B46" t="n">
         <v>4580313723736</v>
       </c>
       <c r="C46" t="inlineStr">
@@ -40219,7 +40223,7 @@
           <t>4901301419859</t>
         </is>
       </c>
-      <c r="B47" s="23" t="n">
+      <c r="B47" t="n">
         <v>4901301419859</v>
       </c>
       <c r="C47" t="inlineStr">
@@ -40255,7 +40259,7 @@
           <t>4901416183737</t>
         </is>
       </c>
-      <c r="B48" s="23" t="n">
+      <c r="B48" t="n">
         <v>4901416183737</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -40291,7 +40295,7 @@
           <t>4901609017221</t>
         </is>
       </c>
-      <c r="B49" s="23" t="n">
+      <c r="B49" t="n">
         <v>4901609017221</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -40327,7 +40331,7 @@
           <t>4903301377597</t>
         </is>
       </c>
-      <c r="B50" s="23" t="n">
+      <c r="B50" t="n">
         <v>4903301377597</v>
       </c>
       <c r="C50" t="inlineStr">
@@ -40363,7 +40367,7 @@
           <t>4965858009567</t>
         </is>
       </c>
-      <c r="B51" s="23" t="n">
+      <c r="B51" t="n">
         <v>4965858009567</v>
       </c>
       <c r="C51" t="inlineStr">
@@ -40399,7 +40403,7 @@
           <t>4965858009581</t>
         </is>
       </c>
-      <c r="B52" s="23" t="n">
+      <c r="B52" t="n">
         <v>4965858009581</v>
       </c>
       <c r="C52" t="inlineStr">
@@ -40435,7 +40439,7 @@
           <t>4971710623789</t>
         </is>
       </c>
-      <c r="B53" s="23" t="n">
+      <c r="B53" t="n">
         <v>4971710623789</v>
       </c>
       <c r="C53" t="inlineStr">
@@ -40471,7 +40475,7 @@
           <t>4973307685309</t>
         </is>
       </c>
-      <c r="B54" s="23" t="n">
+      <c r="B54" t="n">
         <v>4973307685309</v>
       </c>
       <c r="D54" t="n">
@@ -40502,7 +40506,7 @@
           <t>4973307685354</t>
         </is>
       </c>
-      <c r="B55" s="23" t="n">
+      <c r="B55" t="n">
         <v>4973307685354</v>
       </c>
       <c r="C55" t="inlineStr">
@@ -40538,7 +40542,7 @@
           <t>4987176266804</t>
         </is>
       </c>
-      <c r="B56" s="23" t="n">
+      <c r="B56" t="n">
         <v>4987176266804</v>
       </c>
       <c r="C56" t="inlineStr">
@@ -40574,7 +40578,7 @@
           <t>6941057452425</t>
         </is>
       </c>
-      <c r="B57" s="23" t="n">
+      <c r="B57" t="n">
         <v>6941057452425</v>
       </c>
       <c r="C57" t="n">
@@ -40608,7 +40612,7 @@
           <t>840064400329</t>
         </is>
       </c>
-      <c r="B58" s="23" t="n">
+      <c r="B58" t="n">
         <v>840064400329</v>
       </c>
       <c r="C58" t="inlineStr">
@@ -40644,7 +40648,7 @@
           <t>8720689024570</t>
         </is>
       </c>
-      <c r="B59" s="23" t="n">
+      <c r="B59" t="n">
         <v>8720689024570</v>
       </c>
       <c r="C59" t="inlineStr">
@@ -40680,7 +40684,7 @@
           <t>6941057420004</t>
         </is>
       </c>
-      <c r="B60" s="23" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>b00004ysym</t>
         </is>
@@ -40730,7 +40734,7 @@
           <t>6941057420004</t>
         </is>
       </c>
-      <c r="B61" s="23" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>b00004ysym-1</t>
         </is>
@@ -40780,7 +40784,7 @@
           <t>3264680009785</t>
         </is>
       </c>
-      <c r="B62" s="23" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>b000o7lk1c</t>
         </is>
@@ -40828,7 +40832,7 @@
           <t>4902424424430</t>
         </is>
       </c>
-      <c r="B63" s="23" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>b000v2f0aw</t>
         </is>
@@ -40878,7 +40882,7 @@
           <t>4901422152505</t>
         </is>
       </c>
-      <c r="B64" s="23" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>b000vicipq</t>
         </is>
@@ -40918,7 +40922,7 @@
           <t>4901422153502</t>
         </is>
       </c>
-      <c r="B65" s="23" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>b0012vqlky</t>
         </is>
@@ -40968,7 +40972,7 @@
           <t>4901422153205</t>
         </is>
       </c>
-      <c r="B66" s="23" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>b0018b5c30</t>
         </is>
@@ -41018,7 +41022,7 @@
           <t>4901422151508</t>
         </is>
       </c>
-      <c r="B67" s="23" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>b0018b8fx4</t>
         </is>
@@ -41068,7 +41072,7 @@
           <t>4987072061725</t>
         </is>
       </c>
-      <c r="B68" s="23" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>b003al01iw</t>
         </is>
@@ -41118,7 +41122,7 @@
           <t>4901422361112</t>
         </is>
       </c>
-      <c r="B69" s="23" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>b003m76vj2</t>
         </is>
@@ -41158,7 +41162,7 @@
           <t>4250278603472</t>
         </is>
       </c>
-      <c r="B70" s="23" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>b006wtxlxq</t>
         </is>
@@ -41206,7 +41210,7 @@
       <c r="A71" t="n">
         <v>4903588240669</v>
       </c>
-      <c r="B71" s="23" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>b0082mtvt4</t>
         </is>
@@ -41246,7 +41250,7 @@
           <t>4562248604564</t>
         </is>
       </c>
-      <c r="B72" s="23" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>b00jpussb4</t>
         </is>
@@ -41294,7 +41298,7 @@
       <c r="A73" t="n">
         <v>4901133618680</v>
       </c>
-      <c r="B73" s="23" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>b00jrnlz1o</t>
         </is>
@@ -41334,7 +41338,7 @@
           <t>4901080281012</t>
         </is>
       </c>
-      <c r="B74" s="23" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>b00layzmas</t>
         </is>
@@ -41384,7 +41388,7 @@
           <t>4901080281012</t>
         </is>
       </c>
-      <c r="B75" s="23" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>b00layzmas-1</t>
         </is>
@@ -41434,7 +41438,7 @@
           <t>4992440034539</t>
         </is>
       </c>
-      <c r="B76" s="23" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>b00x3e44d4</t>
         </is>
@@ -41484,7 +41488,7 @@
           <t>4987072025581</t>
         </is>
       </c>
-      <c r="B77" s="23" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>b00xj3iark</t>
         </is>
@@ -41534,7 +41538,7 @@
           <t>4905009678969</t>
         </is>
       </c>
-      <c r="B78" s="23" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>b00xtvxexw</t>
         </is>
@@ -41574,7 +41578,7 @@
           <t>4901422360153</t>
         </is>
       </c>
-      <c r="B79" s="23" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>b00xtyr0js</t>
         </is>
@@ -41624,7 +41628,7 @@
           <t>4905009678938</t>
         </is>
       </c>
-      <c r="B80" s="23" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>b00xtzzlei</t>
         </is>
@@ -41674,7 +41678,7 @@
           <t>4905009678938</t>
         </is>
       </c>
-      <c r="B81" s="23" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>b00xtzzlei-1</t>
         </is>
@@ -41724,7 +41728,7 @@
           <t>9000103868003</t>
         </is>
       </c>
-      <c r="B82" s="23" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>b011q7trhc</t>
         </is>
@@ -41774,7 +41778,7 @@
           <t>4573234190312</t>
         </is>
       </c>
-      <c r="B83" s="23" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>b014kk2b98</t>
         </is>
@@ -41824,7 +41828,7 @@
           <t>0848061036985</t>
         </is>
       </c>
-      <c r="B84" s="23" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>b016xkhlck</t>
         </is>
@@ -41874,7 +41878,7 @@
           <t>4903367092458</t>
         </is>
       </c>
-      <c r="B85" s="23" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>b018rmwuhi</t>
         </is>
@@ -41924,7 +41928,7 @@
           <t>4901417621733</t>
         </is>
       </c>
-      <c r="B86" s="23" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>b019skzy3u</t>
         </is>
@@ -41974,7 +41978,7 @@
           <t>4972547032492</t>
         </is>
       </c>
-      <c r="B87" s="23" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>b01dlmhmja</t>
         </is>
@@ -42024,7 +42028,7 @@
           <t>4987072042779</t>
         </is>
       </c>
-      <c r="B88" s="23" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>b01fqca29k</t>
         </is>
@@ -42074,7 +42078,7 @@
           <t>4905009678983</t>
         </is>
       </c>
-      <c r="B89" s="23" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>b01lzqkw6a</t>
         </is>
@@ -42124,7 +42128,7 @@
           <t>4902430720700</t>
         </is>
       </c>
-      <c r="B90" s="23" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>b01mze6x6h</t>
         </is>
@@ -42174,7 +42178,7 @@
           <t>4902430720700</t>
         </is>
       </c>
-      <c r="B91" s="23" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>b01mze6x6h-1</t>
         </is>
@@ -42224,7 +42228,7 @@
           <t>0848061064377</t>
         </is>
       </c>
-      <c r="B92" s="23" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>b01n411r1a</t>
         </is>
@@ -42274,7 +42278,7 @@
           <t>0848061034912</t>
         </is>
       </c>
-      <c r="B93" s="23" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>b01navanrx</t>
         </is>
@@ -42324,7 +42328,7 @@
           <t>4537130101797</t>
         </is>
       </c>
-      <c r="B94" s="23" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>b01nguindv</t>
         </is>
@@ -42374,7 +42378,7 @@
           <t>4987072048986</t>
         </is>
       </c>
-      <c r="B95" s="23" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>b06xprwsz5</t>
         </is>
@@ -42424,7 +42428,7 @@
           <t>4961641011687</t>
         </is>
       </c>
-      <c r="B96" s="23" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>b06xw4t8n4</t>
         </is>
@@ -42472,7 +42476,7 @@
       <c r="A97" t="n">
         <v>3264680009761</v>
       </c>
-      <c r="B97" s="23" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>b06y13f2sg</t>
         </is>
@@ -42510,7 +42514,7 @@
           <t>4902424441727</t>
         </is>
       </c>
-      <c r="B98" s="23" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>b0752p9qt9</t>
         </is>
@@ -42560,7 +42564,7 @@
           <t>4992440036182</t>
         </is>
       </c>
-      <c r="B99" s="23" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>b076vdntgg</t>
         </is>
@@ -42610,7 +42614,7 @@
           <t>4560401500203</t>
         </is>
       </c>
-      <c r="B100" s="23" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>b079fnj832</t>
         </is>
@@ -42660,7 +42664,7 @@
           <t>4901133718991</t>
         </is>
       </c>
-      <c r="B101" s="23" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>b079ylfx6f</t>
         </is>
@@ -42700,7 +42704,7 @@
           <t>4901133718984</t>
         </is>
       </c>
-      <c r="B102" s="23" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>b079z1ccm6</t>
         </is>
@@ -42740,7 +42744,7 @@
           <t>4906456646488</t>
         </is>
       </c>
-      <c r="B103" s="23" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>b07fs56gbx</t>
         </is>
@@ -42790,7 +42794,7 @@
           <t>4988615128875</t>
         </is>
       </c>
-      <c r="B104" s="23" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>b07gy9vzc2</t>
         </is>
@@ -42840,7 +42844,7 @@
           <t>4901080682512</t>
         </is>
       </c>
-      <c r="B105" s="23" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>b07kpyw849</t>
         </is>
@@ -42890,7 +42894,7 @@
           <t>6941057416106</t>
         </is>
       </c>
-      <c r="B106" s="23" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>b07q5846pr</t>
         </is>
@@ -42940,7 +42944,7 @@
           <t>4987241162130</t>
         </is>
       </c>
-      <c r="B107" s="23" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>b07sqfg1yg</t>
         </is>
@@ -42990,7 +42994,7 @@
           <t>0848061014365</t>
         </is>
       </c>
-      <c r="B108" s="23" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>b07st84pf5</t>
         </is>
@@ -43040,7 +43044,7 @@
           <t>4901872973590</t>
         </is>
       </c>
-      <c r="B109" s="23" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>b07tr6ft6t</t>
         </is>
@@ -43090,7 +43094,7 @@
           <t>4902430886369</t>
         </is>
       </c>
-      <c r="B110" s="23" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>b07vv4cmrb</t>
         </is>
@@ -43140,7 +43144,7 @@
           <t>0194644141165</t>
         </is>
       </c>
-      <c r="B111" s="23" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>b07znfr6bf</t>
         </is>
@@ -43190,7 +43194,7 @@
           <t>4988659446157</t>
         </is>
       </c>
-      <c r="B112" s="23" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>b0842r98vl</t>
         </is>
@@ -43240,7 +43244,7 @@
           <t>4901301381965</t>
         </is>
       </c>
-      <c r="B113" s="23" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>b085p2f2v8</t>
         </is>
@@ -43288,7 +43292,7 @@
           <t>0840080511207</t>
         </is>
       </c>
-      <c r="B114" s="23" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>b085wv8664</t>
         </is>
@@ -43338,7 +43342,7 @@
           <t>3264680024382</t>
         </is>
       </c>
-      <c r="B115" s="23" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>b0866fcr7t</t>
         </is>
@@ -43386,7 +43390,7 @@
           <t>4971710396478</t>
         </is>
       </c>
-      <c r="B116" s="23" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>b086sndmbv</t>
         </is>
@@ -43436,7 +43440,7 @@
           <t>4971710396485</t>
         </is>
       </c>
-      <c r="B117" s="23" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>b086snzlfb</t>
         </is>
@@ -43486,7 +43490,7 @@
           <t>4903588262715</t>
         </is>
       </c>
-      <c r="B118" s="23" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>b087lzdd59</t>
         </is>
@@ -43536,7 +43540,7 @@
           <t>0194644143206</t>
         </is>
       </c>
-      <c r="B119" s="23" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>b087tb7ym7</t>
         </is>
@@ -43586,7 +43590,7 @@
           <t>7290108925937</t>
         </is>
       </c>
-      <c r="B120" s="23" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>b089flf3cm</t>
         </is>
@@ -43636,7 +43640,7 @@
           <t>4901301370174</t>
         </is>
       </c>
-      <c r="B121" s="23" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>b08bscmwln</t>
         </is>
@@ -43686,7 +43690,7 @@
           <t>4897039351632</t>
         </is>
       </c>
-      <c r="B122" s="23" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>b08f2zf5cv</t>
         </is>
@@ -43736,7 +43740,7 @@
           <t>4571263111773</t>
         </is>
       </c>
-      <c r="B123" s="23" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>b08f5bq5yd</t>
         </is>
@@ -43786,7 +43790,7 @@
           <t>4904740633077</t>
         </is>
       </c>
-      <c r="B124" s="23" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>b08gkwglsg</t>
         </is>
@@ -43836,7 +43840,7 @@
           <t>4902430898768</t>
         </is>
       </c>
-      <c r="B125" s="23" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>b08gp5xftt</t>
         </is>
@@ -43886,7 +43890,7 @@
           <t>4580171667401</t>
         </is>
       </c>
-      <c r="B126" s="23" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>b08kw4by71</t>
         </is>
@@ -43936,7 +43940,7 @@
           <t>4953685201155</t>
         </is>
       </c>
-      <c r="B127" s="23" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>b08lgjljsk</t>
         </is>
@@ -43986,7 +43990,7 @@
           <t>4589967505330</t>
         </is>
       </c>
-      <c r="B128" s="23" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>b08lh2tj1l</t>
         </is>
@@ -44036,7 +44040,7 @@
           <t>4901301388544</t>
         </is>
       </c>
-      <c r="B129" s="23" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>b08m3st1rj</t>
         </is>
@@ -44086,7 +44090,7 @@
           <t>4901080024619</t>
         </is>
       </c>
-      <c r="B130" s="23" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>b08rdrw831</t>
         </is>
@@ -44136,7 +44140,7 @@
           <t>4902407024787</t>
         </is>
       </c>
-      <c r="B131" s="23" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>b08vn5jgjx</t>
         </is>
@@ -44186,7 +44190,7 @@
           <t>4987072060674</t>
         </is>
       </c>
-      <c r="B132" s="23" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>b08x2gkrbk</t>
         </is>
@@ -44236,7 +44240,7 @@
           <t>4571138555268</t>
         </is>
       </c>
-      <c r="B133" s="23" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>b08xylwxs6</t>
         </is>
@@ -44276,7 +44280,7 @@
           <t>4901301388919</t>
         </is>
       </c>
-      <c r="B134" s="23" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>b08y95skcr-2</t>
         </is>
@@ -44326,7 +44330,7 @@
           <t>0194644145262</t>
         </is>
       </c>
-      <c r="B135" s="23" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>b093l5cmmt</t>
         </is>
@@ -44376,7 +44380,7 @@
           <t>0194644145286</t>
         </is>
       </c>
-      <c r="B136" s="23" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>b093l5cmmt</t>
         </is>
@@ -44426,7 +44430,7 @@
           <t>0194644145248</t>
         </is>
       </c>
-      <c r="B137" s="23" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>b093l5cmmt</t>
         </is>
@@ -44476,7 +44480,7 @@
           <t>0194644145255</t>
         </is>
       </c>
-      <c r="B138" s="23" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>b093l5cmmt</t>
         </is>
@@ -44526,7 +44530,7 @@
           <t>0194644084677</t>
         </is>
       </c>
-      <c r="B139" s="23" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>b093l5cmmt</t>
         </is>
@@ -44576,7 +44580,7 @@
           <t>0194644084691</t>
         </is>
       </c>
-      <c r="B140" s="23" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>b093l5cmmt</t>
         </is>
@@ -44626,7 +44630,7 @@
           <t>0194644145262</t>
         </is>
       </c>
-      <c r="B141" s="23" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>b093l5cmmt-1</t>
         </is>
@@ -44676,7 +44680,7 @@
           <t>0194644145286</t>
         </is>
       </c>
-      <c r="B142" s="23" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>b093l5cmmt-1</t>
         </is>
@@ -44726,7 +44730,7 @@
           <t>0194644145248</t>
         </is>
       </c>
-      <c r="B143" s="23" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>b093l5cmmt-1</t>
         </is>
@@ -44776,7 +44780,7 @@
           <t>0194644145255</t>
         </is>
       </c>
-      <c r="B144" s="23" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>b093l5cmmt-1</t>
         </is>
@@ -44826,7 +44830,7 @@
           <t>0194644084677</t>
         </is>
       </c>
-      <c r="B145" s="23" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>b093l5cmmt-1</t>
         </is>
@@ -44876,7 +44880,7 @@
           <t>0194644084691</t>
         </is>
       </c>
-      <c r="B146" s="23" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>b093l5cmmt-1</t>
         </is>
@@ -44926,7 +44930,7 @@
           <t>0194644145316</t>
         </is>
       </c>
-      <c r="B147" s="23" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>b093lnhzq2</t>
         </is>
@@ -44976,7 +44980,7 @@
           <t>0194644145293</t>
         </is>
       </c>
-      <c r="B148" s="23" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>b093lnhzq2</t>
         </is>
@@ -45026,7 +45030,7 @@
           <t>0194644145279</t>
         </is>
       </c>
-      <c r="B149" s="23" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>b093lnhzq2</t>
         </is>
@@ -45076,7 +45080,7 @@
           <t>0194644145309</t>
         </is>
       </c>
-      <c r="B150" s="23" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>b093lnhzq2</t>
         </is>
@@ -45126,7 +45130,7 @@
           <t>0194644084738</t>
         </is>
       </c>
-      <c r="B151" s="23" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>b093lnhzq2</t>
         </is>
@@ -45176,7 +45180,7 @@
           <t>0194644084721</t>
         </is>
       </c>
-      <c r="B152" s="23" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>b093lnhzq2</t>
         </is>
@@ -45226,7 +45230,7 @@
           <t>0194644084745</t>
         </is>
       </c>
-      <c r="B153" s="23" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>b093lnhzq2</t>
         </is>
@@ -45276,7 +45280,7 @@
           <t>0194644145316</t>
         </is>
       </c>
-      <c r="B154" s="23" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>b093lnhzq2-1</t>
         </is>
@@ -45326,7 +45330,7 @@
           <t>0194644145293</t>
         </is>
       </c>
-      <c r="B155" s="23" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>b093lnhzq2-1</t>
         </is>
@@ -45376,7 +45380,7 @@
           <t>0194644145279</t>
         </is>
       </c>
-      <c r="B156" s="23" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>b093lnhzq2-1</t>
         </is>
@@ -45426,7 +45430,7 @@
           <t>0194644145309</t>
         </is>
       </c>
-      <c r="B157" s="23" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>b093lnhzq2-1</t>
         </is>
@@ -45476,7 +45480,7 @@
           <t>0194644084738</t>
         </is>
       </c>
-      <c r="B158" s="23" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>b093lnhzq2-1</t>
         </is>
@@ -45526,7 +45530,7 @@
           <t>0194644084721</t>
         </is>
       </c>
-      <c r="B159" s="23" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>b093lnhzq2-1</t>
         </is>
@@ -45576,7 +45580,7 @@
           <t>0194644084745</t>
         </is>
       </c>
-      <c r="B160" s="23" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>b093lnhzq2-1</t>
         </is>
@@ -45626,7 +45630,7 @@
           <t>4580295033632</t>
         </is>
       </c>
-      <c r="B161" s="23" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>b09871bcr4</t>
         </is>
@@ -45666,7 +45670,7 @@
           <t>4580295033649</t>
         </is>
       </c>
-      <c r="B162" s="23" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>b09871bcr4</t>
         </is>
@@ -45706,7 +45710,7 @@
           <t>4902430644723</t>
         </is>
       </c>
-      <c r="B163" s="23" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>b098mh987h</t>
         </is>
@@ -45756,7 +45760,7 @@
           <t>4902430644723</t>
         </is>
       </c>
-      <c r="B164" s="23" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>b098mh987h-1</t>
         </is>
@@ -45806,7 +45810,7 @@
           <t>4902430645041</t>
         </is>
       </c>
-      <c r="B165" s="23" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>b098mjm99x</t>
         </is>
@@ -45856,7 +45860,7 @@
           <t>4902430645041</t>
         </is>
       </c>
-      <c r="B166" s="23" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>b098mjm99x-1</t>
         </is>
@@ -45906,7 +45910,7 @@
           <t>4902430645041</t>
         </is>
       </c>
-      <c r="B167" s="23" t="inlineStr">
+      <c r="B167" t="inlineStr">
         <is>
           <t>b098mjm99x-2</t>
         </is>
@@ -45956,7 +45960,7 @@
           <t>4902430645027</t>
         </is>
       </c>
-      <c r="B168" s="23" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>b098qfn95n</t>
         </is>
@@ -46006,7 +46010,7 @@
           <t>4902430644914</t>
         </is>
       </c>
-      <c r="B169" s="23" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>b098qhm24d</t>
         </is>
@@ -46056,7 +46060,7 @@
           <t>4902430644914</t>
         </is>
       </c>
-      <c r="B170" s="23" t="inlineStr">
+      <c r="B170" t="inlineStr">
         <is>
           <t>b098qhm24d-3</t>
         </is>
@@ -46106,7 +46110,7 @@
           <t>0840080535111</t>
         </is>
       </c>
-      <c r="B171" s="23" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>b09b2rlplv</t>
         </is>
@@ -46144,7 +46148,7 @@
           <t>0840080537337</t>
         </is>
       </c>
-      <c r="B172" s="23" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>b09b2rlplv</t>
         </is>
@@ -46182,7 +46186,7 @@
           <t>0840080525952</t>
         </is>
       </c>
-      <c r="B173" s="23" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>b09b2rlplv</t>
         </is>
@@ -46220,7 +46224,7 @@
           <t>4987176032454</t>
         </is>
       </c>
-      <c r="B174" s="23" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>b09dc7q6kl</t>
         </is>
@@ -46270,7 +46274,7 @@
           <t>4987176032454</t>
         </is>
       </c>
-      <c r="B175" s="23" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>b09dc7q6kl-1</t>
         </is>
@@ -46320,7 +46324,7 @@
           <t>4961310157685</t>
         </is>
       </c>
-      <c r="B176" s="23" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>b09dl6dc59</t>
         </is>
@@ -46370,7 +46374,7 @@
           <t>4571390307698</t>
         </is>
       </c>
-      <c r="B177" s="23" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>b09gvt2ls1</t>
         </is>
@@ -46410,7 +46414,7 @@
           <t>4550207690475</t>
         </is>
       </c>
-      <c r="B178" s="23" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>b09jbyt2cz</t>
         </is>
@@ -46460,7 +46464,7 @@
           <t>4901008314679</t>
         </is>
       </c>
-      <c r="B179" s="23" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>b09ltnc8bs</t>
         </is>
@@ -46510,7 +46514,7 @@
           <t>0078332582495</t>
         </is>
       </c>
-      <c r="B180" s="23" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>b09mj5g5z7</t>
         </is>
@@ -46550,7 +46554,7 @@
           <t>0783325824949</t>
         </is>
       </c>
-      <c r="B181" s="23" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>b09mj5g5z7</t>
         </is>
@@ -46590,7 +46594,7 @@
           <t>4987241173242</t>
         </is>
       </c>
-      <c r="B182" s="23" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>b09py4134y</t>
         </is>
@@ -46640,7 +46644,7 @@
           <t>4901070761005</t>
         </is>
       </c>
-      <c r="B183" s="23" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>b09qpnzlss</t>
         </is>
@@ -46690,7 +46694,7 @@
           <t>4902407024985</t>
         </is>
       </c>
-      <c r="B184" s="23" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>b09tdl4t6v</t>
         </is>
@@ -46740,7 +46744,7 @@
           <t>4573177597704</t>
         </is>
       </c>
-      <c r="B185" s="23" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>b09wxwcrp4</t>
         </is>
@@ -46790,7 +46794,7 @@
           <t>4582521683475</t>
         </is>
       </c>
-      <c r="B186" s="23" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>b09xglsws2</t>
         </is>
@@ -46840,7 +46844,7 @@
           <t>4582521683475</t>
         </is>
       </c>
-      <c r="B187" s="23" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>b09xglsws2-1</t>
         </is>
@@ -46890,7 +46894,7 @@
           <t>4970501032731</t>
         </is>
       </c>
-      <c r="B188" s="23" t="inlineStr">
+      <c r="B188" t="inlineStr">
         <is>
           <t>b09xxtb2xr</t>
         </is>
@@ -46940,7 +46944,7 @@
           <t>0840268981389</t>
         </is>
       </c>
-      <c r="B189" s="23" t="inlineStr">
+      <c r="B189" t="inlineStr">
         <is>
           <t>b09zx764zl</t>
         </is>
@@ -46980,7 +46984,7 @@
           <t>0840268966508</t>
         </is>
       </c>
-      <c r="B190" s="23" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>b09zx764zl</t>
         </is>
@@ -47030,7 +47034,7 @@
           <t>0840268982034</t>
         </is>
       </c>
-      <c r="B191" s="23" t="inlineStr">
+      <c r="B191" t="inlineStr">
         <is>
           <t>b09zx764zl</t>
         </is>
@@ -47070,7 +47074,7 @@
           <t>0840268997410</t>
         </is>
       </c>
-      <c r="B192" s="23" t="inlineStr">
+      <c r="B192" t="inlineStr">
         <is>
           <t>b09zx764zl</t>
         </is>
@@ -47110,7 +47114,7 @@
           <t>0194644104542</t>
         </is>
       </c>
-      <c r="B193" s="23" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>b0b4h3d98m</t>
         </is>
@@ -47160,7 +47164,7 @@
           <t>4902806121476</t>
         </is>
       </c>
-      <c r="B194" s="23" t="inlineStr">
+      <c r="B194" t="inlineStr">
         <is>
           <t>b0b7gz7p5h</t>
         </is>
@@ -47210,7 +47214,7 @@
           <t>0194644108953</t>
         </is>
       </c>
-      <c r="B195" s="23" t="inlineStr">
+      <c r="B195" t="inlineStr">
         <is>
           <t>b0bb1pfcs3</t>
         </is>
@@ -47250,7 +47254,7 @@
           <t>4976558003564</t>
         </is>
       </c>
-      <c r="B196" s="23" t="inlineStr">
+      <c r="B196" t="inlineStr">
         <is>
           <t>b0bd42lkyk</t>
         </is>
@@ -47298,7 +47302,7 @@
       <c r="A197" t="n">
         <v>4936201106424</v>
       </c>
-      <c r="B197" s="23" t="inlineStr">
+      <c r="B197" t="inlineStr">
         <is>
           <t>b0bgs64g46</t>
         </is>
@@ -47338,7 +47342,7 @@
           <t>4904710434345</t>
         </is>
       </c>
-      <c r="B198" s="23" t="inlineStr">
+      <c r="B198" t="inlineStr">
         <is>
           <t>b0bj93nj2k</t>
         </is>
@@ -47378,7 +47382,7 @@
           <t>0194644114398</t>
         </is>
       </c>
-      <c r="B199" s="23" t="inlineStr">
+      <c r="B199" t="inlineStr">
         <is>
           <t>b0bjcqcq7z</t>
         </is>
@@ -47428,7 +47432,7 @@
           <t>0194644114398</t>
         </is>
       </c>
-      <c r="B200" s="23" t="inlineStr">
+      <c r="B200" t="inlineStr">
         <is>
           <t>b0bjcqcq7z-1</t>
         </is>
@@ -47476,7 +47480,7 @@
       <c r="A201" t="n">
         <v>4901422361211</v>
       </c>
-      <c r="B201" s="23" t="inlineStr">
+      <c r="B201" t="inlineStr">
         <is>
           <t>b0bjvwq6lg</t>
         </is>
@@ -47516,7 +47520,7 @@
           <t>8806173478880</t>
         </is>
       </c>
-      <c r="B202" s="23" t="inlineStr">
+      <c r="B202" t="inlineStr">
         <is>
           <t>b0bl26m3s6</t>
         </is>
@@ -47556,7 +47560,7 @@
           <t>0840268902810</t>
         </is>
       </c>
-      <c r="B203" s="23" t="inlineStr">
+      <c r="B203" t="inlineStr">
         <is>
           <t>b0bl6fdw1f</t>
         </is>
@@ -47594,7 +47598,7 @@
           <t>0840268903183</t>
         </is>
       </c>
-      <c r="B204" s="23" t="inlineStr">
+      <c r="B204" t="inlineStr">
         <is>
           <t>b0bl6fdw1f</t>
         </is>
@@ -47632,7 +47636,7 @@
           <t>0840268936228</t>
         </is>
       </c>
-      <c r="B205" s="23" t="inlineStr">
+      <c r="B205" t="inlineStr">
         <is>
           <t>b0bl6fdw1f</t>
         </is>
@@ -47670,7 +47674,7 @@
           <t>0840268945213</t>
         </is>
       </c>
-      <c r="B206" s="23" t="inlineStr">
+      <c r="B206" t="inlineStr">
         <is>
           <t>b0bls11y97</t>
         </is>
@@ -47720,7 +47724,7 @@
           <t>0840268991722</t>
         </is>
       </c>
-      <c r="B207" s="23" t="inlineStr">
+      <c r="B207" t="inlineStr">
         <is>
           <t>b0bls11y97</t>
         </is>
@@ -47770,7 +47774,7 @@
           <t>4562201211877</t>
         </is>
       </c>
-      <c r="B208" s="23" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>b0bls3hvdz</t>
         </is>
@@ -47820,7 +47824,7 @@
           <t>4895252500868</t>
         </is>
       </c>
-      <c r="B209" s="23" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>b0bls9fnwh</t>
         </is>
@@ -47870,7 +47874,7 @@
           <t>9000326168003</t>
         </is>
       </c>
-      <c r="B210" s="23" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>b0bltqq367</t>
         </is>
@@ -47920,7 +47924,7 @@
           <t>4901133458033</t>
         </is>
       </c>
-      <c r="B211" s="23" t="inlineStr">
+      <c r="B211" t="inlineStr">
         <is>
           <t>b0blvdxqgy</t>
         </is>
@@ -47970,7 +47974,7 @@
           <t>4901792044578</t>
         </is>
       </c>
-      <c r="B212" s="23" t="inlineStr">
+      <c r="B212" t="inlineStr">
         <is>
           <t>b0bmz5whhh</t>
         </is>
@@ -48020,7 +48024,7 @@
           <t>4901792044585</t>
         </is>
       </c>
-      <c r="B213" s="23" t="inlineStr">
+      <c r="B213" t="inlineStr">
         <is>
           <t>b0bmz7ccxd</t>
         </is>
@@ -48060,7 +48064,7 @@
           <t>4901792044592</t>
         </is>
       </c>
-      <c r="B214" s="23" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>b0bmz8mk97</t>
         </is>
@@ -48100,7 +48104,7 @@
           <t>0194644121297</t>
         </is>
       </c>
-      <c r="B215" s="23" t="inlineStr">
+      <c r="B215" t="inlineStr">
         <is>
           <t>b0bqmsxfp7</t>
         </is>
@@ -48150,7 +48154,7 @@
           <t>4902111772523</t>
         </is>
       </c>
-      <c r="B216" s="23" t="inlineStr">
+      <c r="B216" t="inlineStr">
         <is>
           <t>b0bqt8pr1d</t>
         </is>
@@ -48190,7 +48194,7 @@
           <t>4902111772554</t>
         </is>
       </c>
-      <c r="B217" s="23" t="inlineStr">
+      <c r="B217" t="inlineStr">
         <is>
           <t>b0bqtg4wsq</t>
         </is>
@@ -48230,7 +48234,7 @@
           <t>4902111772479</t>
         </is>
       </c>
-      <c r="B218" s="23" t="inlineStr">
+      <c r="B218" t="inlineStr">
         <is>
           <t>b0bqtg8vt7</t>
         </is>
@@ -48280,7 +48284,7 @@
           <t>4902111772479</t>
         </is>
       </c>
-      <c r="B219" s="23" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>b0bqtg8vt7-1</t>
         </is>
@@ -48330,7 +48334,7 @@
           <t>4902111772509</t>
         </is>
       </c>
-      <c r="B220" s="23" t="inlineStr">
+      <c r="B220" t="inlineStr">
         <is>
           <t>b0bqth3gg9</t>
         </is>
@@ -48370,7 +48374,7 @@
           <t>4902111772431</t>
         </is>
       </c>
-      <c r="B221" s="23" t="inlineStr">
+      <c r="B221" t="inlineStr">
         <is>
           <t>b0bqtp6fl5</t>
         </is>
@@ -48410,7 +48414,7 @@
           <t>4902111772516</t>
         </is>
       </c>
-      <c r="B222" s="23" t="inlineStr">
+      <c r="B222" t="inlineStr">
         <is>
           <t>b0bqtsq4t8</t>
         </is>
@@ -48460,7 +48464,7 @@
           <t>4902111772448</t>
         </is>
       </c>
-      <c r="B223" s="23" t="inlineStr">
+      <c r="B223" t="inlineStr">
         <is>
           <t>b0bqtwtpp8</t>
         </is>
@@ -48500,7 +48504,7 @@
           <t>4902111772530</t>
         </is>
       </c>
-      <c r="B224" s="23" t="inlineStr">
+      <c r="B224" t="inlineStr">
         <is>
           <t>b0bqv2x83n</t>
         </is>
@@ -48540,7 +48544,7 @@
           <t>4550516474971</t>
         </is>
       </c>
-      <c r="B225" s="23" t="inlineStr">
+      <c r="B225" t="inlineStr">
         <is>
           <t>b0bsgb956y</t>
         </is>
@@ -48580,7 +48584,7 @@
           <t>4550516474988</t>
         </is>
       </c>
-      <c r="B226" s="23" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>b0bsgcdmp7</t>
         </is>
@@ -48620,7 +48624,7 @@
           <t>4901080080318</t>
         </is>
       </c>
-      <c r="B227" s="23" t="inlineStr">
+      <c r="B227" t="inlineStr">
         <is>
           <t>b0bsl8s15z</t>
         </is>
@@ -48670,7 +48674,7 @@
           <t>4909978145538</t>
         </is>
       </c>
-      <c r="B228" s="23" t="inlineStr">
+      <c r="B228" t="inlineStr">
         <is>
           <t>b0bthtbcrn</t>
         </is>
@@ -48718,7 +48722,7 @@
           <t>4901133458101.0</t>
         </is>
       </c>
-      <c r="B229" s="23" t="inlineStr">
+      <c r="B229" t="inlineStr">
         <is>
           <t>b0bw9bdd5k</t>
         </is>
@@ -48758,7 +48762,7 @@
           <t>4901080068712</t>
         </is>
       </c>
-      <c r="B230" s="23" t="inlineStr">
+      <c r="B230" t="inlineStr">
         <is>
           <t>b0bwdnysh3</t>
         </is>
@@ -48808,7 +48812,7 @@
           <t>4903301344223</t>
         </is>
       </c>
-      <c r="B231" s="23" t="inlineStr">
+      <c r="B231" t="inlineStr">
         <is>
           <t>b0bxbnhlfy-1</t>
         </is>
@@ -48858,7 +48862,7 @@
           <t>4901301429247</t>
         </is>
       </c>
-      <c r="B232" s="23" t="inlineStr">
+      <c r="B232" t="inlineStr">
         <is>
           <t>b0bxcstz4s</t>
         </is>
@@ -48898,7 +48902,7 @@
           <t>4901301422156</t>
         </is>
       </c>
-      <c r="B233" s="23" t="inlineStr">
+      <c r="B233" t="inlineStr">
         <is>
           <t>b0bxct4qnx</t>
         </is>
@@ -48948,7 +48952,7 @@
           <t>4901301416087</t>
         </is>
       </c>
-      <c r="B234" s="23" t="inlineStr">
+      <c r="B234" t="inlineStr">
         <is>
           <t>b0by2pjqg2</t>
         </is>
@@ -48998,7 +49002,7 @@
           <t>4901301413109</t>
         </is>
       </c>
-      <c r="B235" s="23" t="inlineStr">
+      <c r="B235" t="inlineStr">
         <is>
           <t>b0by2sypqr</t>
         </is>
@@ -49048,7 +49052,7 @@
           <t>4573164186454</t>
         </is>
       </c>
-      <c r="B236" s="23" t="inlineStr">
+      <c r="B236" t="inlineStr">
         <is>
           <t>b0by7gklq4</t>
         </is>
@@ -49088,7 +49092,7 @@
           <t>4573164186317</t>
         </is>
       </c>
-      <c r="B237" s="23" t="inlineStr">
+      <c r="B237" t="inlineStr">
         <is>
           <t>b0by8b2ghs</t>
         </is>
@@ -49128,7 +49132,7 @@
           <t>0194644131432</t>
         </is>
       </c>
-      <c r="B238" s="23" t="inlineStr">
+      <c r="B238" t="inlineStr">
         <is>
           <t>b0bz45nc3z</t>
         </is>
@@ -49178,7 +49182,7 @@
           <t>0840268981846</t>
         </is>
       </c>
-      <c r="B239" s="23" t="inlineStr">
+      <c r="B239" t="inlineStr">
         <is>
           <t>b0c2s4k41g</t>
         </is>
@@ -49216,7 +49220,7 @@
           <t>0840268912925</t>
         </is>
       </c>
-      <c r="B240" s="23" t="inlineStr">
+      <c r="B240" t="inlineStr">
         <is>
           <t>b0c2s4k41g</t>
         </is>
@@ -49254,7 +49258,7 @@
           <t>0840268931865</t>
         </is>
       </c>
-      <c r="B241" s="23" t="inlineStr">
+      <c r="B241" t="inlineStr">
         <is>
           <t>b0c2s4k41g</t>
         </is>
@@ -49292,7 +49296,7 @@
           <t>4969919300679</t>
         </is>
       </c>
-      <c r="B242" s="23" t="inlineStr">
+      <c r="B242" t="inlineStr">
         <is>
           <t>b0c2vsxhy9</t>
         </is>
@@ -49342,7 +49346,7 @@
           <t>0194644137311</t>
         </is>
       </c>
-      <c r="B243" s="23" t="inlineStr">
+      <c r="B243" t="inlineStr">
         <is>
           <t>b0c5cbv6l3</t>
         </is>
@@ -49382,7 +49386,7 @@
           <t>0194644137595</t>
         </is>
       </c>
-      <c r="B244" s="23" t="inlineStr">
+      <c r="B244" t="inlineStr">
         <is>
           <t>b0c5cbv6l3</t>
         </is>
@@ -49422,7 +49426,7 @@
           <t>0194644138080</t>
         </is>
       </c>
-      <c r="B245" s="23" t="inlineStr">
+      <c r="B245" t="inlineStr">
         <is>
           <t>b0c5jb3rjm</t>
         </is>
@@ -49462,7 +49466,7 @@
           <t>0194644138097</t>
         </is>
       </c>
-      <c r="B246" s="23" t="inlineStr">
+      <c r="B246" t="inlineStr">
         <is>
           <t>b0c5jb3rjm</t>
         </is>
@@ -49502,7 +49506,7 @@
           <t>4971902010526</t>
         </is>
       </c>
-      <c r="B247" s="23" t="inlineStr">
+      <c r="B247" t="inlineStr">
         <is>
           <t>b0c6dhfd9t</t>
         </is>
@@ -49550,7 +49554,7 @@
       <c r="A248" t="n">
         <v>4978951921735</v>
       </c>
-      <c r="B248" s="23" t="inlineStr">
+      <c r="B248" t="inlineStr">
         <is>
           <t>b0c96849wl</t>
         </is>
@@ -49590,7 +49594,7 @@
           <t>4547761490399</t>
         </is>
       </c>
-      <c r="B249" s="23" t="inlineStr">
+      <c r="B249" t="inlineStr">
         <is>
           <t>b0c9d3ftyv</t>
         </is>
@@ -49630,7 +49634,7 @@
           <t>4547761490382</t>
         </is>
       </c>
-      <c r="B250" s="23" t="inlineStr">
+      <c r="B250" t="inlineStr">
         <is>
           <t>b0c9d3ftyv</t>
         </is>
@@ -49670,7 +49674,7 @@
           <t>4547761490443</t>
         </is>
       </c>
-      <c r="B251" s="23" t="inlineStr">
+      <c r="B251" t="inlineStr">
         <is>
           <t>b0c9d3ftyv</t>
         </is>
@@ -49710,7 +49714,7 @@
           <t>4969655463041</t>
         </is>
       </c>
-      <c r="B252" s="23" t="inlineStr">
+      <c r="B252" t="inlineStr">
         <is>
           <t>b0chs4xy6d</t>
         </is>
@@ -49758,7 +49762,7 @@
           <t>0840268925536</t>
         </is>
       </c>
-      <c r="B253" s="23" t="inlineStr">
+      <c r="B253" t="inlineStr">
         <is>
           <t>b0cjlfprmh</t>
         </is>
@@ -49796,7 +49800,7 @@
           <t>4987176184580</t>
         </is>
       </c>
-      <c r="B254" s="23" t="inlineStr">
+      <c r="B254" t="inlineStr">
         <is>
           <t>b0ckhk5b77</t>
         </is>
@@ -49844,7 +49848,7 @@
           <t>4901422365264</t>
         </is>
       </c>
-      <c r="B255" s="23" t="inlineStr">
+      <c r="B255" t="inlineStr">
         <is>
           <t>b0ckv5gbnc</t>
         </is>
@@ -49894,7 +49898,7 @@
           <t>0194644179724</t>
         </is>
       </c>
-      <c r="B256" s="23" t="inlineStr">
+      <c r="B256" t="inlineStr">
         <is>
           <t>b0cm66ly5f</t>
         </is>
@@ -49944,7 +49948,7 @@
           <t>4901609016057</t>
         </is>
       </c>
-      <c r="B257" s="23" t="inlineStr">
+      <c r="B257" t="inlineStr">
         <is>
           <t>b0cnkfjw3j</t>
         </is>
@@ -49994,7 +49998,7 @@
           <t>0194644186241</t>
         </is>
       </c>
-      <c r="B258" s="23" t="inlineStr">
+      <c r="B258" t="inlineStr">
         <is>
           <t>b0cp4rhk7x</t>
         </is>
@@ -50034,7 +50038,7 @@
           <t>0194644186227</t>
         </is>
       </c>
-      <c r="B259" s="23" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>b0cp4rhk7x</t>
         </is>
@@ -50074,7 +50078,7 @@
           <t>0194644186258</t>
         </is>
       </c>
-      <c r="B260" s="23" t="inlineStr">
+      <c r="B260" t="inlineStr">
         <is>
           <t>b0cp4rhk7x</t>
         </is>
@@ -50114,7 +50118,7 @@
           <t>0194644186234</t>
         </is>
       </c>
-      <c r="B261" s="23" t="inlineStr">
+      <c r="B261" t="inlineStr">
         <is>
           <t>b0cp4rhk7x</t>
         </is>
@@ -50154,7 +50158,7 @@
           <t>4987241193899</t>
         </is>
       </c>
-      <c r="B262" s="23" t="inlineStr">
+      <c r="B262" t="inlineStr">
         <is>
           <t>b0ct52gvd8</t>
         </is>
@@ -50204,7 +50208,7 @@
           <t>4987241194377</t>
         </is>
       </c>
-      <c r="B263" s="23" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>b0ct5mt6vf</t>
         </is>
@@ -50254,7 +50258,7 @@
           <t>4902111776620</t>
         </is>
       </c>
-      <c r="B264" s="23" t="inlineStr">
+      <c r="B264" t="inlineStr">
         <is>
           <t>b0ct9kdbfs</t>
         </is>
@@ -50304,7 +50308,7 @@
           <t>4987176233288</t>
         </is>
       </c>
-      <c r="B265" s="23" t="inlineStr">
+      <c r="B265" t="inlineStr">
         <is>
           <t>b0cthfllth</t>
         </is>
@@ -50354,7 +50358,7 @@
           <t>5745000698271</t>
         </is>
       </c>
-      <c r="B266" s="23" t="inlineStr">
+      <c r="B266" t="inlineStr">
         <is>
           <t>b0ctt9m27s</t>
         </is>
@@ -50404,7 +50408,7 @@
           <t>4987176241153</t>
         </is>
       </c>
-      <c r="B267" s="23" t="inlineStr">
+      <c r="B267" t="inlineStr">
         <is>
           <t>b0cvxgygdw</t>
         </is>
@@ -50454,7 +50458,7 @@
           <t>4987176241153</t>
         </is>
       </c>
-      <c r="B268" s="23" t="inlineStr">
+      <c r="B268" t="inlineStr">
         <is>
           <t>b0cvxgygdw-1</t>
         </is>
@@ -50504,7 +50508,7 @@
           <t>4987241193943</t>
         </is>
       </c>
-      <c r="B269" s="23" t="inlineStr">
+      <c r="B269" t="inlineStr">
         <is>
           <t>b0cw3c9tyd</t>
         </is>
@@ -50554,7 +50558,7 @@
           <t>7290114048101</t>
         </is>
       </c>
-      <c r="B270" s="23" t="inlineStr">
+      <c r="B270" t="inlineStr">
         <is>
           <t>b0cxj4tsk8</t>
         </is>
@@ -50590,7 +50594,7 @@
       <c r="A271" t="n">
         <v>7290114045995</v>
       </c>
-      <c r="B271" s="23" t="inlineStr">
+      <c r="B271" t="inlineStr">
         <is>
           <t>b0cxj4tsk8</t>
         </is>
@@ -50630,7 +50634,7 @@
           <t>0194644043070</t>
         </is>
       </c>
-      <c r="B272" s="23" t="inlineStr">
+      <c r="B272" t="inlineStr">
         <is>
           <t>b0cxny69dc</t>
         </is>
@@ -50670,7 +50674,7 @@
           <t>0194644043094</t>
         </is>
       </c>
-      <c r="B273" s="23" t="inlineStr">
+      <c r="B273" t="inlineStr">
         <is>
           <t>b0cxny69dc</t>
         </is>
@@ -50708,7 +50712,7 @@
       <c r="A274" t="n">
         <v>4549777706761</v>
       </c>
-      <c r="B274" s="23" t="inlineStr">
+      <c r="B274" t="inlineStr">
         <is>
           <t>b0czpjdzv4</t>
         </is>
@@ -50746,7 +50750,7 @@
       <c r="A275" t="n">
         <v>4987176244215</v>
       </c>
-      <c r="B275" s="23" t="inlineStr">
+      <c r="B275" t="inlineStr">
         <is>
           <t>b0czxfsh7d</t>
         </is>
@@ -50784,7 +50788,7 @@
       <c r="A276" t="n">
         <v>4987176244215</v>
       </c>
-      <c r="B276" s="23" t="inlineStr">
+      <c r="B276" t="inlineStr">
         <is>
           <t>b0czxfsh7d-1</t>
         </is>
@@ -50822,7 +50826,7 @@
       <c r="A277" t="n">
         <v>4987176244215</v>
       </c>
-      <c r="B277" s="23" t="inlineStr">
+      <c r="B277" t="inlineStr">
         <is>
           <t>b0czxfsh7d-2</t>
         </is>
@@ -50860,7 +50864,7 @@
       <c r="A278" t="n">
         <v>4988755067768</v>
       </c>
-      <c r="B278" s="23" t="inlineStr">
+      <c r="B278" t="inlineStr">
         <is>
           <t>b0d1q8zb4d</t>
         </is>
@@ -50898,7 +50902,7 @@
       <c r="A279" t="n">
         <v>4562149053928</v>
       </c>
-      <c r="B279" s="23" t="inlineStr">
+      <c r="B279" t="inlineStr">
         <is>
           <t>b0d32pg6c1</t>
         </is>
@@ -50938,7 +50942,7 @@
           <t>4549995444964</t>
         </is>
       </c>
-      <c r="B280" s="23" t="inlineStr">
+      <c r="B280" t="inlineStr">
         <is>
           <t>b0d3kthmt4</t>
         </is>
@@ -50978,7 +50982,7 @@
           <t>4549995444988</t>
         </is>
       </c>
-      <c r="B281" s="23" t="inlineStr">
+      <c r="B281" t="inlineStr">
         <is>
           <t>b0d3kthmt4</t>
         </is>
@@ -51018,7 +51022,7 @@
           <t>4549995444957</t>
         </is>
       </c>
-      <c r="B282" s="23" t="inlineStr">
+      <c r="B282" t="inlineStr">
         <is>
           <t>b0d3kthmt4</t>
         </is>
@@ -51058,7 +51062,7 @@
           <t>4549995444971</t>
         </is>
       </c>
-      <c r="B283" s="23" t="inlineStr">
+      <c r="B283" t="inlineStr">
         <is>
           <t>b0d3kthmt4</t>
         </is>
@@ -51098,7 +51102,7 @@
           <t>0194644204709</t>
         </is>
       </c>
-      <c r="B284" s="23" t="inlineStr">
+      <c r="B284" t="inlineStr">
         <is>
           <t>b0d7zlpsjg</t>
         </is>
@@ -51138,7 +51142,7 @@
           <t>0194644204723</t>
         </is>
       </c>
-      <c r="B285" s="23" t="inlineStr">
+      <c r="B285" t="inlineStr">
         <is>
           <t>b0d7zlpsjg</t>
         </is>
@@ -51178,7 +51182,7 @@
           <t>0194644204624</t>
         </is>
       </c>
-      <c r="B286" s="23" t="inlineStr">
+      <c r="B286" t="inlineStr">
         <is>
           <t>b0d7zlpsjg</t>
         </is>
@@ -51218,7 +51222,7 @@
           <t>0194644204693</t>
         </is>
       </c>
-      <c r="B287" s="23" t="inlineStr">
+      <c r="B287" t="inlineStr">
         <is>
           <t>b0d7zlpsjg</t>
         </is>
@@ -51258,7 +51262,7 @@
           <t>0194644205706</t>
         </is>
       </c>
-      <c r="B288" s="23" t="inlineStr">
+      <c r="B288" t="inlineStr">
         <is>
           <t>b0d8q93vmg</t>
         </is>
@@ -51298,7 +51302,7 @@
           <t>4902806130607</t>
         </is>
       </c>
-      <c r="B289" s="23" t="inlineStr">
+      <c r="B289" t="inlineStr">
         <is>
           <t>b0d9w4dwf5</t>
         </is>
@@ -51348,7 +51352,7 @@
           <t>4901301437198</t>
         </is>
       </c>
-      <c r="B290" s="23" t="inlineStr">
+      <c r="B290" t="inlineStr">
         <is>
           <t>b0d9zg3zkm</t>
         </is>
@@ -51396,7 +51400,7 @@
       <c r="A291" t="n">
         <v>4901301441720</v>
       </c>
-      <c r="B291" s="23" t="inlineStr">
+      <c r="B291" t="inlineStr">
         <is>
           <t>b0d9znvl7q</t>
         </is>
@@ -51436,7 +51440,7 @@
           <t>0194644207540</t>
         </is>
       </c>
-      <c r="B292" s="23" t="inlineStr">
+      <c r="B292" t="inlineStr">
         <is>
           <t>b0db1hfzlk</t>
         </is>
@@ -51476,7 +51480,7 @@
           <t>0194644207557</t>
         </is>
       </c>
-      <c r="B293" s="23" t="inlineStr">
+      <c r="B293" t="inlineStr">
         <is>
           <t>b0db1hfzlk</t>
         </is>
@@ -51516,7 +51520,7 @@
           <t>0194644207571</t>
         </is>
       </c>
-      <c r="B294" s="23" t="inlineStr">
+      <c r="B294" t="inlineStr">
         <is>
           <t>b0db1hfzlk</t>
         </is>
@@ -51556,7 +51560,7 @@
           <t>0194644207588</t>
         </is>
       </c>
-      <c r="B295" s="23" t="inlineStr">
+      <c r="B295" t="inlineStr">
         <is>
           <t>b0db1hfzlk</t>
         </is>
@@ -51596,7 +51600,7 @@
           <t>4969929259561</t>
         </is>
       </c>
-      <c r="B296" s="23" t="inlineStr">
+      <c r="B296" t="inlineStr">
         <is>
           <t>b0dbqn8sl3</t>
         </is>
@@ -51636,7 +51640,7 @@
           <t>4969929260307</t>
         </is>
       </c>
-      <c r="B297" s="23" t="inlineStr">
+      <c r="B297" t="inlineStr">
         <is>
           <t>b0dbqn8sl3</t>
         </is>
@@ -51676,7 +51680,7 @@
           <t>4547410536317</t>
         </is>
       </c>
-      <c r="B298" s="23" t="inlineStr">
+      <c r="B298" t="inlineStr">
         <is>
           <t>b0ddsypbwx</t>
         </is>
@@ -51726,7 +51730,7 @@
           <t>4550533130829</t>
         </is>
       </c>
-      <c r="B299" s="23" t="inlineStr">
+      <c r="B299" t="inlineStr">
         <is>
           <t>b0dfbl4mqp</t>
         </is>
@@ -51776,7 +51780,7 @@
           <t>4549980880715</t>
         </is>
       </c>
-      <c r="B300" s="23" t="inlineStr">
+      <c r="B300" t="inlineStr">
         <is>
           <t>b0dffzzxqw</t>
         </is>
@@ -51826,7 +51830,7 @@
           <t>9000278745000</t>
         </is>
       </c>
-      <c r="B301" s="23" t="inlineStr">
+      <c r="B301" t="inlineStr">
         <is>
           <t>b0dfmgm2n9</t>
         </is>
@@ -51876,7 +51880,7 @@
           <t>4550451259138</t>
         </is>
       </c>
-      <c r="B302" s="23" t="inlineStr">
+      <c r="B302" t="inlineStr">
         <is>
           <t>b0dfpz82g5</t>
         </is>
@@ -51926,7 +51930,7 @@
           <t>4987176260635</t>
         </is>
       </c>
-      <c r="B303" s="23" t="inlineStr">
+      <c r="B303" t="inlineStr">
         <is>
           <t>b0dfyjnwjt</t>
         </is>
@@ -51976,7 +51980,7 @@
           <t>4710483949340</t>
         </is>
       </c>
-      <c r="B304" s="23" t="inlineStr">
+      <c r="B304" t="inlineStr">
         <is>
           <t>b0dg4fk9hp</t>
         </is>
@@ -52026,7 +52030,7 @@
           <t>4978951921391</t>
         </is>
       </c>
-      <c r="B305" s="23" t="inlineStr">
+      <c r="B305" t="inlineStr">
         <is>
           <t>b0dh2hl1mv</t>
         </is>
@@ -52074,7 +52078,7 @@
       <c r="A306" t="n">
         <v>4902135147505</v>
       </c>
-      <c r="B306" s="23" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>b0dhj8bx53</t>
         </is>
@@ -52114,7 +52118,7 @@
           <t>4902135147543</t>
         </is>
       </c>
-      <c r="B307" s="23" t="inlineStr">
+      <c r="B307" t="inlineStr">
         <is>
           <t>b0dhjcr7yq</t>
         </is>
@@ -52154,7 +52158,7 @@
           <t>4901133303845</t>
         </is>
       </c>
-      <c r="B308" s="23" t="inlineStr">
+      <c r="B308" t="inlineStr">
         <is>
           <t>b0dhjqr9vv</t>
         </is>
@@ -52204,7 +52208,7 @@
           <t>4987176260666</t>
         </is>
       </c>
-      <c r="B309" s="23" t="inlineStr">
+      <c r="B309" t="inlineStr">
         <is>
           <t>b0dkjk26lh</t>
         </is>
@@ -52244,7 +52248,7 @@
           <t>4987176261267</t>
         </is>
       </c>
-      <c r="B310" s="23" t="inlineStr">
+      <c r="B310" t="inlineStr">
         <is>
           <t>b0dkjk6hkh</t>
         </is>
@@ -52292,7 +52296,7 @@
       <c r="A311" t="n">
         <v>4987176260659</v>
       </c>
-      <c r="B311" s="23" t="inlineStr">
+      <c r="B311" t="inlineStr">
         <is>
           <t>b0dktchdgk</t>
         </is>
@@ -52342,7 +52346,7 @@
           <t>4901301438140</t>
         </is>
       </c>
-      <c r="B312" s="23" t="inlineStr">
+      <c r="B312" t="inlineStr">
         <is>
           <t>b0dmnwc48r</t>
         </is>
@@ -52392,7 +52396,7 @@
           <t>4901301439154</t>
         </is>
       </c>
-      <c r="B313" s="23" t="inlineStr">
+      <c r="B313" t="inlineStr">
         <is>
           <t>b0dmp16lqs</t>
         </is>
@@ -52440,7 +52444,7 @@
       <c r="A314" t="n">
         <v>4520699694367</v>
       </c>
-      <c r="B314" s="23" t="inlineStr">
+      <c r="B314" t="inlineStr">
         <is>
           <t>b0dmrwrwrd</t>
         </is>
@@ -52480,7 +52484,7 @@
           <t>4902111780566</t>
         </is>
       </c>
-      <c r="B315" s="23" t="inlineStr">
+      <c r="B315" t="inlineStr">
         <is>
           <t>b0dmz5q8r7</t>
         </is>
@@ -52520,7 +52524,7 @@
           <t>4908046850831</t>
         </is>
       </c>
-      <c r="B316" s="23" t="inlineStr">
+      <c r="B316" t="inlineStr">
         <is>
           <t>b0dnjrzdt9</t>
         </is>
@@ -52560,7 +52564,7 @@
           <t>4908046850848</t>
         </is>
       </c>
-      <c r="B317" s="23" t="inlineStr">
+      <c r="B317" t="inlineStr">
         <is>
           <t>b0dnjrzdt9</t>
         </is>
@@ -52600,7 +52604,7 @@
           <t>4582738117022</t>
         </is>
       </c>
-      <c r="B318" s="23" t="inlineStr">
+      <c r="B318" t="inlineStr">
         <is>
           <t>b0dnjrzdt9</t>
         </is>
@@ -52640,7 +52644,7 @@
           <t>4571657201189</t>
         </is>
       </c>
-      <c r="B319" s="23" t="inlineStr">
+      <c r="B319" t="inlineStr">
         <is>
           <t>b0dnjrzdt9</t>
         </is>
@@ -52680,7 +52684,7 @@
           <t>4560191497165</t>
         </is>
       </c>
-      <c r="B320" s="23" t="inlineStr">
+      <c r="B320" t="inlineStr">
         <is>
           <t>b0dnk11vxk</t>
         </is>
@@ -52713,7 +52717,7 @@
           <t>4560191497172</t>
         </is>
       </c>
-      <c r="B321" s="23" t="inlineStr">
+      <c r="B321" t="inlineStr">
         <is>
           <t>b0dnk11vxk</t>
         </is>
@@ -52746,7 +52750,7 @@
           <t>4560191497189</t>
         </is>
       </c>
-      <c r="B322" s="23" t="inlineStr">
+      <c r="B322" t="inlineStr">
         <is>
           <t>b0dnk11vxk</t>
         </is>
@@ -52779,7 +52783,7 @@
           <t>4560191497196</t>
         </is>
       </c>
-      <c r="B323" s="23" t="inlineStr">
+      <c r="B323" t="inlineStr">
         <is>
           <t>b0dnk11vxk</t>
         </is>
@@ -52812,7 +52816,7 @@
           <t>4560191498438</t>
         </is>
       </c>
-      <c r="B324" s="23" t="inlineStr">
+      <c r="B324" t="inlineStr">
         <is>
           <t>b0dnk11vxk</t>
         </is>
@@ -52845,7 +52849,7 @@
           <t>0194644226954</t>
         </is>
       </c>
-      <c r="B325" s="23" t="inlineStr">
+      <c r="B325" t="inlineStr">
         <is>
           <t>b0dnlr2nyn</t>
         </is>
@@ -52885,7 +52889,7 @@
           <t>0194644226947</t>
         </is>
       </c>
-      <c r="B326" s="23" t="inlineStr">
+      <c r="B326" t="inlineStr">
         <is>
           <t>b0dnlr2nyn</t>
         </is>
@@ -52923,7 +52927,7 @@
       <c r="A327" t="n">
         <v>4520699635674</v>
       </c>
-      <c r="B327" s="23" t="inlineStr">
+      <c r="B327" t="inlineStr">
         <is>
           <t>b0dpfkqck7</t>
         </is>
@@ -52963,7 +52967,7 @@
           <t>4903301366959</t>
         </is>
       </c>
-      <c r="B328" s="23" t="inlineStr">
+      <c r="B328" t="inlineStr">
         <is>
           <t>b0dq55rncd</t>
         </is>
@@ -53011,7 +53015,7 @@
       <c r="A329" t="n">
         <v>4970501033592</v>
       </c>
-      <c r="B329" s="23" t="inlineStr">
+      <c r="B329" t="inlineStr">
         <is>
           <t>b0dq7vk36r</t>
         </is>
@@ -53051,7 +53055,7 @@
           <t>4987176286260</t>
         </is>
       </c>
-      <c r="B330" s="23" t="inlineStr">
+      <c r="B330" t="inlineStr">
         <is>
           <t>b0dqxmpx2g</t>
         </is>
@@ -53101,7 +53105,7 @@
           <t>4987176286284</t>
         </is>
       </c>
-      <c r="B331" s="23" t="inlineStr">
+      <c r="B331" t="inlineStr">
         <is>
           <t>b0dqxnd1qs</t>
         </is>
@@ -53151,7 +53155,7 @@
           <t>4987176286307</t>
         </is>
       </c>
-      <c r="B332" s="23" t="inlineStr">
+      <c r="B332" t="inlineStr">
         <is>
           <t>b0dqxrwnzc</t>
         </is>
@@ -53201,7 +53205,7 @@
           <t>0190021133402</t>
         </is>
       </c>
-      <c r="B333" s="23" t="inlineStr">
+      <c r="B333" t="inlineStr">
         <is>
           <t>b0ds2b3p2b</t>
         </is>
@@ -53249,7 +53253,7 @@
           <t>4901301450173</t>
         </is>
       </c>
-      <c r="B334" s="23" t="inlineStr">
+      <c r="B334" t="inlineStr">
         <is>
           <t>b0ds7s7p82</t>
         </is>
@@ -53289,7 +53293,7 @@
           <t>4901301450180</t>
         </is>
       </c>
-      <c r="B335" s="23" t="inlineStr">
+      <c r="B335" t="inlineStr">
         <is>
           <t>b0ds7s7p82</t>
         </is>
@@ -53329,7 +53333,7 @@
           <t>4987241196432</t>
         </is>
       </c>
-      <c r="B336" s="23" t="inlineStr">
+      <c r="B336" t="inlineStr">
         <is>
           <t>b0dt4gr197</t>
         </is>
@@ -53379,7 +53383,7 @@
           <t>4901301447883</t>
         </is>
       </c>
-      <c r="B337" s="23" t="inlineStr">
+      <c r="B337" t="inlineStr">
         <is>
           <t>b0dtykkwgn</t>
         </is>
@@ -53429,7 +53433,7 @@
           <t>4571648684465</t>
         </is>
       </c>
-      <c r="B338" s="23" t="inlineStr">
+      <c r="B338" t="inlineStr">
         <is>
           <t>b0dv35n5cc</t>
         </is>
@@ -53479,7 +53483,7 @@
           <t>4902407025166</t>
         </is>
       </c>
-      <c r="B339" s="23" t="inlineStr">
+      <c r="B339" t="inlineStr">
         <is>
           <t>b0dwfmjjwh</t>
         </is>
@@ -53529,7 +53533,7 @@
           <t>0194644233532</t>
         </is>
       </c>
-      <c r="B340" s="23" t="inlineStr">
+      <c r="B340" t="inlineStr">
         <is>
           <t>b0dwmpnclc-1</t>
         </is>
@@ -53579,7 +53583,7 @@
           <t>0194644236243</t>
         </is>
       </c>
-      <c r="B341" s="23" t="inlineStr">
+      <c r="B341" t="inlineStr">
         <is>
           <t>b0f1mm3fm6</t>
         </is>
@@ -53629,7 +53633,7 @@
           <t>4582210598141</t>
         </is>
       </c>
-      <c r="B342" s="23" t="inlineStr">
+      <c r="B342" t="inlineStr">
         <is>
           <t>b0f1mv5vdx</t>
         </is>
@@ -53679,7 +53683,7 @@
           <t>4582210598110</t>
         </is>
       </c>
-      <c r="B343" s="23" t="inlineStr">
+      <c r="B343" t="inlineStr">
         <is>
           <t>b0f1mwdn83</t>
         </is>
@@ -53729,7 +53733,7 @@
           <t>4547410550955</t>
         </is>
       </c>
-      <c r="B344" s="23" t="inlineStr">
+      <c r="B344" t="inlineStr">
         <is>
           <t>b0f1slwhqg</t>
         </is>
@@ -53779,7 +53783,7 @@
           <t>0194644236601</t>
         </is>
       </c>
-      <c r="B345" s="23" t="inlineStr">
+      <c r="B345" t="inlineStr">
         <is>
           <t>b0f24ggf3z</t>
         </is>
@@ -53829,7 +53833,7 @@
           <t>4901133736230</t>
         </is>
       </c>
-      <c r="B346" s="23" t="inlineStr">
+      <c r="B346" t="inlineStr">
         <is>
           <t>b0f2fq6lp7</t>
         </is>
@@ -53879,7 +53883,7 @@
           <t>4987176301680</t>
         </is>
       </c>
-      <c r="B347" s="23" t="inlineStr">
+      <c r="B347" t="inlineStr">
         <is>
           <t>b0f3czw26m</t>
         </is>
@@ -53929,7 +53933,7 @@
           <t>4987176301598</t>
         </is>
       </c>
-      <c r="B348" s="23" t="inlineStr">
+      <c r="B348" t="inlineStr">
         <is>
           <t>b0f3d19j9q</t>
         </is>
@@ -53979,7 +53983,7 @@
           <t>4987176301604</t>
         </is>
       </c>
-      <c r="B349" s="23" t="inlineStr">
+      <c r="B349" t="inlineStr">
         <is>
           <t>b0f3d1nryv</t>
         </is>
@@ -54019,7 +54023,7 @@
           <t>4987176301499</t>
         </is>
       </c>
-      <c r="B350" s="23" t="inlineStr">
+      <c r="B350" t="inlineStr">
         <is>
           <t>b0f3d1y958</t>
         </is>
@@ -54069,7 +54073,7 @@
           <t>4987176305664</t>
         </is>
       </c>
-      <c r="B351" s="23" t="inlineStr">
+      <c r="B351" t="inlineStr">
         <is>
           <t>b0f3d1zsw8</t>
         </is>
@@ -54109,7 +54113,7 @@
           <t>4987176305732</t>
         </is>
       </c>
-      <c r="B352" s="23" t="inlineStr">
+      <c r="B352" t="inlineStr">
         <is>
           <t>b0f3d1zw85</t>
         </is>
@@ -54159,7 +54163,7 @@
           <t>4987176305701</t>
         </is>
       </c>
-      <c r="B353" s="23" t="inlineStr">
+      <c r="B353" t="inlineStr">
         <is>
           <t>b0f3d2l45v</t>
         </is>
@@ -54209,7 +54213,7 @@
           <t>4987176305701</t>
         </is>
       </c>
-      <c r="B354" s="23" t="inlineStr">
+      <c r="B354" t="inlineStr">
         <is>
           <t>b0f3d2l45v-1</t>
         </is>
@@ -54259,7 +54263,7 @@
           <t>4987176301543</t>
         </is>
       </c>
-      <c r="B355" s="23" t="inlineStr">
+      <c r="B355" t="inlineStr">
         <is>
           <t>b0f3d2psfp</t>
         </is>
@@ -54309,7 +54313,7 @@
           <t>4987176301505</t>
         </is>
       </c>
-      <c r="B356" s="23" t="inlineStr">
+      <c r="B356" t="inlineStr">
         <is>
           <t>b0f3d2q8sz</t>
         </is>
@@ -54349,7 +54353,7 @@
           <t>4902111781204</t>
         </is>
       </c>
-      <c r="B357" s="23" t="inlineStr">
+      <c r="B357" t="inlineStr">
         <is>
           <t>b0f3wyss1s</t>
         </is>
@@ -54397,7 +54401,7 @@
           <t>4987176309211</t>
         </is>
       </c>
-      <c r="B358" s="23" t="inlineStr">
+      <c r="B358" t="inlineStr">
         <is>
           <t>b0f4kkg4jh</t>
         </is>
@@ -54447,7 +54451,7 @@
           <t>4987072097878</t>
         </is>
       </c>
-      <c r="B359" s="23" t="inlineStr">
+      <c r="B359" t="inlineStr">
         <is>
           <t>b0f53l7j9k</t>
         </is>
@@ -54497,7 +54501,7 @@
           <t>4987176278081</t>
         </is>
       </c>
-      <c r="B360" s="23" t="inlineStr">
+      <c r="B360" t="inlineStr">
         <is>
           <t>b0f62pwtlz</t>
         </is>
@@ -54547,7 +54551,7 @@
           <t>4987176278388</t>
         </is>
       </c>
-      <c r="B361" s="23" t="inlineStr">
+      <c r="B361" t="inlineStr">
         <is>
           <t>b0f62x11z1</t>
         </is>
@@ -54597,7 +54601,7 @@
           <t>4987176278012</t>
         </is>
       </c>
-      <c r="B362" s="23" t="inlineStr">
+      <c r="B362" t="inlineStr">
         <is>
           <t>b0f62xplbf</t>
         </is>
@@ -54647,7 +54651,7 @@
           <t>4550432248892</t>
         </is>
       </c>
-      <c r="B363" s="23" t="inlineStr">
+      <c r="B363" t="inlineStr">
         <is>
           <t>b0f66p8fyc</t>
         </is>
@@ -54687,7 +54691,7 @@
           <t>0194644239664</t>
         </is>
       </c>
-      <c r="B364" s="23" t="inlineStr">
+      <c r="B364" t="inlineStr">
         <is>
           <t>b0f6lbdfc7</t>
         </is>
@@ -54727,7 +54731,7 @@
           <t>0194644239657</t>
         </is>
       </c>
-      <c r="B365" s="23" t="inlineStr">
+      <c r="B365" t="inlineStr">
         <is>
           <t>b0f6lbdfc7</t>
         </is>
@@ -54767,7 +54771,7 @@
           <t>4533141407514</t>
         </is>
       </c>
-      <c r="B366" s="23" t="inlineStr">
+      <c r="B366" t="inlineStr">
         <is>
           <t>b0f6xtgtgp</t>
         </is>
@@ -54817,7 +54821,7 @@
           <t>4533141407514</t>
         </is>
       </c>
-      <c r="B367" s="23" t="inlineStr">
+      <c r="B367" t="inlineStr">
         <is>
           <t>b0f6xtgtgp-1</t>
         </is>
@@ -54867,7 +54871,7 @@
           <t>4533141407514</t>
         </is>
       </c>
-      <c r="B368" s="23" t="inlineStr">
+      <c r="B368" t="inlineStr">
         <is>
           <t>b0f6xtgtgp-2</t>
         </is>
@@ -54912,7 +54916,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="B369" s="23" t="inlineStr">
+      <c r="B369" t="inlineStr">
         <is>
           <t>b0fdq59t55</t>
         </is>
@@ -54950,7 +54954,7 @@
       <c r="A370" t="n">
         <v>4987176304834</v>
       </c>
-      <c r="B370" s="23" t="inlineStr">
+      <c r="B370" t="inlineStr">
         <is>
           <t>b0fjg6x3h5</t>
         </is>
@@ -54985,7 +54989,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="B371" s="23" t="inlineStr">
+      <c r="B371" t="inlineStr">
         <is>
           <t>b0fl297cy2</t>
         </is>
@@ -55020,7 +55024,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="B372" s="23" t="inlineStr">
+      <c r="B372" t="inlineStr">
         <is>
           <t>b0fl297cy2</t>
         </is>
@@ -55060,7 +55064,7 @@
           <t>0194644251581</t>
         </is>
       </c>
-      <c r="B373" s="23" t="inlineStr">
+      <c r="B373" t="inlineStr">
         <is>
           <t>b0fnrs5wb2</t>
         </is>
@@ -55110,7 +55114,7 @@
           <t>0194644251574</t>
         </is>
       </c>
-      <c r="B374" s="23" t="inlineStr">
+      <c r="B374" t="inlineStr">
         <is>
           <t>b0fnrs5wb2</t>
         </is>
@@ -55160,7 +55164,7 @@
           <t>0194644251543</t>
         </is>
       </c>
-      <c r="B375" s="23" t="inlineStr">
+      <c r="B375" t="inlineStr">
         <is>
           <t>b0fnrs5wb2</t>
         </is>
@@ -55210,7 +55214,7 @@
           <t>4901770955247</t>
         </is>
       </c>
-      <c r="B376" s="23" t="inlineStr">
+      <c r="B376" t="inlineStr">
         <is>
           <t>b0fr92j75h</t>
         </is>
@@ -55260,7 +55264,7 @@
           <t>4550391912131</t>
         </is>
       </c>
-      <c r="B377" s="23" t="inlineStr">
+      <c r="B377" t="inlineStr">
         <is>
           <t>b0frs8pb58</t>
         </is>
@@ -55310,7 +55314,7 @@
           <t>4550391912094</t>
         </is>
       </c>
-      <c r="B378" s="23" t="inlineStr">
+      <c r="B378" t="inlineStr">
         <is>
           <t>b0frs8pb58</t>
         </is>
@@ -55360,7 +55364,7 @@
           <t>4550391011469</t>
         </is>
       </c>
-      <c r="B379" s="23" t="inlineStr">
+      <c r="B379" t="inlineStr">
         <is>
           <t>b0frs8pb58</t>
         </is>
@@ -55410,7 +55414,7 @@
           <t>4550391011360</t>
         </is>
       </c>
-      <c r="B380" s="23" t="inlineStr">
+      <c r="B380" t="inlineStr">
         <is>
           <t>b0frs8pb58</t>
         </is>
@@ -55460,7 +55464,7 @@
           <t>4550391011476</t>
         </is>
       </c>
-      <c r="B381" s="23" t="inlineStr">
+      <c r="B381" t="inlineStr">
         <is>
           <t>b0frs8pb58</t>
         </is>
@@ -55510,7 +55514,7 @@
           <t>4550391043903</t>
         </is>
       </c>
-      <c r="B382" s="23" t="inlineStr">
+      <c r="B382" t="inlineStr">
         <is>
           <t>b0frs8pb58</t>
         </is>
@@ -55560,7 +55564,7 @@
           <t>4550391912131</t>
         </is>
       </c>
-      <c r="B383" s="23" t="inlineStr">
+      <c r="B383" t="inlineStr">
         <is>
           <t>b0frs9w3ft</t>
         </is>
@@ -55610,7 +55614,7 @@
           <t>4550391912094</t>
         </is>
       </c>
-      <c r="B384" s="23" t="inlineStr">
+      <c r="B384" t="inlineStr">
         <is>
           <t>b0frs9w3ft</t>
         </is>
@@ -55660,7 +55664,7 @@
           <t>4550391011469</t>
         </is>
       </c>
-      <c r="B385" s="23" t="inlineStr">
+      <c r="B385" t="inlineStr">
         <is>
           <t>b0frs9w3ft</t>
         </is>
@@ -55710,7 +55714,7 @@
           <t>4550391011360</t>
         </is>
       </c>
-      <c r="B386" s="23" t="inlineStr">
+      <c r="B386" t="inlineStr">
         <is>
           <t>b0frs9w3ft</t>
         </is>
@@ -55760,7 +55764,7 @@
           <t>4550391011476</t>
         </is>
       </c>
-      <c r="B387" s="23" t="inlineStr">
+      <c r="B387" t="inlineStr">
         <is>
           <t>b0frs9w3ft</t>
         </is>
@@ -55810,7 +55814,7 @@
           <t>4550391043903</t>
         </is>
       </c>
-      <c r="B388" s="23" t="inlineStr">
+      <c r="B388" t="inlineStr">
         <is>
           <t>b0frs9w3ft</t>
         </is>
@@ -55860,7 +55864,7 @@
           <t>4901301436481</t>
         </is>
       </c>
-      <c r="B389" s="23" t="inlineStr">
+      <c r="B389" t="inlineStr">
         <is>
           <t>b0ftv1bb4j</t>
         </is>
@@ -55910,7 +55914,7 @@
           <t>4901301461001</t>
         </is>
       </c>
-      <c r="B390" s="23" t="inlineStr">
+      <c r="B390" t="inlineStr">
         <is>
           <t>b0ftv1fvnh</t>
         </is>
@@ -55958,7 +55962,7 @@
       <c r="A391" t="n">
         <v>4971710617214</v>
       </c>
-      <c r="B391" s="23" t="inlineStr">
+      <c r="B391" t="inlineStr">
         <is>
           <t>b0fyct4ql2</t>
         </is>
@@ -55998,7 +56002,7 @@
           <t>0194644309473</t>
         </is>
       </c>
-      <c r="B392" s="23" t="inlineStr">
+      <c r="B392" t="inlineStr">
         <is>
           <t>b0gf6zrvns</t>
         </is>
@@ -56048,7 +56052,7 @@
           <t>4580543942990</t>
         </is>
       </c>
-      <c r="B393" s="23" t="inlineStr">
+      <c r="B393" t="inlineStr">
         <is>
           <t>b0gmpz962k</t>
         </is>
@@ -56098,7 +56102,7 @@
           <t>4974824702067</t>
         </is>
       </c>
-      <c r="B394" s="23" t="inlineStr">
+      <c r="B394" t="inlineStr">
         <is>
           <t>b0gmw6x6kr</t>
         </is>
@@ -56148,7 +56152,7 @@
           <t>4550391012244</t>
         </is>
       </c>
-      <c r="B395" s="23" t="inlineStr">
+      <c r="B395" t="inlineStr">
         <is>
           <t>b0gsqcp1mx-a</t>
         </is>
@@ -56186,7 +56190,7 @@
           <t>4550391012251</t>
         </is>
       </c>
-      <c r="B396" s="23" t="inlineStr">
+      <c r="B396" t="inlineStr">
         <is>
           <t>b0gsqcp1mx-a</t>
         </is>
@@ -56224,7 +56228,7 @@
           <t>4550391012220</t>
         </is>
       </c>
-      <c r="B397" s="23" t="inlineStr">
+      <c r="B397" t="inlineStr">
         <is>
           <t>b0gsqcp1mx-a</t>
         </is>
@@ -56262,7 +56266,7 @@
           <t>4550391012237</t>
         </is>
       </c>
-      <c r="B398" s="23" t="inlineStr">
+      <c r="B398" t="inlineStr">
         <is>
           <t>b0gsqcp1mx-a</t>
         </is>
@@ -56302,7 +56306,7 @@
           <t>4550391012411</t>
         </is>
       </c>
-      <c r="B399" s="23" t="inlineStr">
+      <c r="B399" t="inlineStr">
         <is>
           <t>b0gsqjtck2</t>
         </is>
@@ -56352,7 +56356,7 @@
           <t>4550391012428</t>
         </is>
       </c>
-      <c r="B400" s="23" t="inlineStr">
+      <c r="B400" t="inlineStr">
         <is>
           <t>b0gsqjtck2</t>
         </is>
@@ -56402,7 +56406,7 @@
           <t>4550391012381</t>
         </is>
       </c>
-      <c r="B401" s="23" t="inlineStr">
+      <c r="B401" t="inlineStr">
         <is>
           <t>b0gsqjtck2</t>
         </is>
@@ -56452,7 +56456,7 @@
           <t>4550391012435</t>
         </is>
       </c>
-      <c r="B402" s="23" t="inlineStr">
+      <c r="B402" t="inlineStr">
         <is>
           <t>b0gsqjtck2</t>
         </is>
@@ -56497,7 +56501,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="B403" s="23" t="inlineStr">
+      <c r="B403" t="inlineStr">
         <is>
           <t>b0gsqjtck2</t>
         </is>
@@ -56537,7 +56541,7 @@
           <t>4550391012404</t>
         </is>
       </c>
-      <c r="B404" s="23" t="inlineStr">
+      <c r="B404" t="inlineStr">
         <is>
           <t>b0gsqjtck2</t>
         </is>
@@ -56587,7 +56591,7 @@
           <t>4550391012398</t>
         </is>
       </c>
-      <c r="B405" s="23" t="inlineStr">
+      <c r="B405" t="inlineStr">
         <is>
           <t>b0gsqjtck2</t>
         </is>
@@ -56637,7 +56641,7 @@
           <t>4550391012367</t>
         </is>
       </c>
-      <c r="B406" s="23" t="inlineStr">
+      <c r="B406" t="inlineStr">
         <is>
           <t>b0gsqjtck2</t>
         </is>
@@ -56687,7 +56691,7 @@
           <t>4982502082318</t>
         </is>
       </c>
-      <c r="B407" s="23" t="inlineStr">
+      <c r="B407" t="inlineStr">
         <is>
           <t>b0gzfws395</t>
         </is>
@@ -56722,7 +56726,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="B408" s="23" t="inlineStr">
+      <c r="B408" t="inlineStr">
         <is>
           <t>b0h143yckk</t>
         </is>
@@ -56762,7 +56766,7 @@
           <t>4550433077941</t>
         </is>
       </c>
-      <c r="B409" s="23" t="inlineStr">
+      <c r="B409" t="inlineStr">
         <is>
           <t>b0h1x7lkwn</t>
         </is>
@@ -56810,7 +56814,7 @@
       <c r="A410" t="n">
         <v>4582191688985</v>
       </c>
-      <c r="B410" s="23" t="inlineStr">
+      <c r="B410" t="inlineStr">
         <is>
           <t>compass1699347902</t>
         </is>
@@ -56845,7 +56849,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="B411" s="23" t="inlineStr">
+      <c r="B411" t="inlineStr">
         <is>
           <t>set-0001</t>
         </is>
@@ -56880,7 +56884,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="B412" s="23" t="inlineStr">
+      <c r="B412" t="inlineStr">
         <is>
           <t>0192333006122</t>
         </is>
@@ -56900,7 +56904,7 @@
           <t>クリニーク CLINIQUE アドベントカレンダー24 デイズ オブ クリニーク コスメ 化粧品</t>
         </is>
       </c>
-      <c r="G412" s="14" t="n">
+      <c r="G412" t="n">
         <v>0</v>
       </c>
       <c r="H412" t="n">
@@ -56917,7 +56921,7 @@
           <t>4562149054178</t>
         </is>
       </c>
-      <c r="B413" s="25" t="inlineStr">
+      <c r="B413" t="inlineStr">
         <is>
           <t>4562149054178-2</t>
         </is>
@@ -56944,7 +56948,7 @@
         <v>3</v>
       </c>
       <c r="I413">
-        <f>SUM(G412*H413)</f>
+        <f>SUM(G413*H413)</f>
         <v/>
       </c>
     </row>
@@ -56954,7 +56958,7 @@
           <t>4901301438683</t>
         </is>
       </c>
-      <c r="B414" s="25" t="inlineStr">
+      <c r="B414" t="inlineStr">
         <is>
           <t>4901301438683-2</t>
         </is>
@@ -56964,7 +56968,7 @@
           <t>4901301438683-2</t>
         </is>
       </c>
-      <c r="D414" s="11" t="inlineStr">
+      <c r="D414" t="inlineStr">
         <is>
           <t>4901301438683-2</t>
         </is>
@@ -56974,7 +56978,7 @@
           <t>【2個セット】めぐりズム 蒸気でホットアイマスク PoK?MoN企画品 小さめサイズ 5枚入×2個セット 花王 ポケモン ポケットモンスター ホットアイマスク アイマスク 温熱 蒸気 リラックス 目元ケア 休憩 就寝前 個包装 男女兼用</t>
         </is>
       </c>
-      <c r="G414" s="14" t="n">
+      <c r="G414" t="n">
         <v>696</v>
       </c>
       <c r="H414" t="n">
@@ -56991,7 +56995,7 @@
           <t>4902201213219</t>
         </is>
       </c>
-      <c r="B415" s="23" t="inlineStr">
+      <c r="B415" t="inlineStr">
         <is>
           <t>4902201213219-12</t>
         </is>
@@ -57001,7 +57005,7 @@
           <t>4902201213219-12</t>
         </is>
       </c>
-      <c r="D415" s="11" t="inlineStr">
+      <c r="D415" t="inlineStr">
         <is>
           <t>4902201213219-12</t>
         </is>
@@ -57011,7 +57015,7 @@
           <t>【12個セット】モンプチ プチリュクス ナチュラル 成猫用 まぐろのしらす添え 30g×12袋セット キャットフード ウェットフード パウチ 総合栄養食 猫用フード 成猫用 まぐろ しらす ごはん ペットフード 小分け 食べ切り 水分補給 愛猫 国産 まとめ買い ストック</t>
         </is>
       </c>
-      <c r="G415" s="14" t="n">
+      <c r="G415" t="n">
         <v>1116</v>
       </c>
       <c r="H415" t="n">
@@ -57028,7 +57032,7 @@
           <t>4903301186427</t>
         </is>
       </c>
-      <c r="B416" s="23" t="inlineStr">
+      <c r="B416" t="inlineStr">
         <is>
           <t>4903301186427-3</t>
         </is>
@@ -57048,7 +57052,7 @@
           <t>【3個セット】ライオン デンタークリアMAX ナチュラルミント 縦型 140g×3本セット 薬用ハミガキ 歯磨き粉 歯みがき粉 歯垢除去 虫歯予防 口臭予防 フッ素配合 クリーニングパウダー オーラルケア デンタルケア 家庭用 まとめ買い</t>
         </is>
       </c>
-      <c r="G416" s="14" t="n">
+      <c r="G416" t="n">
         <v>327</v>
       </c>
       <c r="H416" t="n">
@@ -57065,7 +57069,7 @@
           <t>4571411204838</t>
         </is>
       </c>
-      <c r="B417" s="23" t="inlineStr">
+      <c r="B417" t="inlineStr">
         <is>
           <t>4571411204838</t>
         </is>
@@ -57085,7 +57089,7 @@
           <t>Anker 523 Charger Nano 3 47W ブラック ホワイト A2039N11  A2039N21 USB-C 急速充電器 GaN PD対応 最大47W 2ポート USB充電器 Type-C 折りたたみ式 コンパクト 小型 MacBook iPad iPhone Android ノートPC タブレット対応 USB-C充電アダプター 高速充電 持ち運び Anker</t>
         </is>
       </c>
-      <c r="G417" s="14" t="n">
+      <c r="G417" t="n">
         <v>2990</v>
       </c>
       <c r="H417" t="n">
@@ -57097,7 +57101,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="B418" s="23" t="inlineStr">
+      <c r="B418" t="inlineStr">
         <is>
           <t>b08x11gd52</t>
         </is>
@@ -57117,7 +57121,7 @@
           <t>Anker Nano II 65W PD充電器 USB-C ブラック ホワイト GaN II USB-C充電器 急速充電器 Power Delivery PPS対応 Type-C ACアダプター MacBook Air Pro iPad iPhone Android Galaxy Pixel ノートPC 折りたたみプラグ 小型 軽量 コンパクト PSE認証</t>
         </is>
       </c>
-      <c r="G418" s="14" t="n">
+      <c r="G418" t="n">
         <v>2690</v>
       </c>
       <c r="H418" t="n">
@@ -57129,7 +57133,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="B419" s="23" t="inlineStr">
+      <c r="B419" t="inlineStr">
         <is>
           <t>b08x11gd52</t>
         </is>
@@ -57149,7 +57153,7 @@
           <t>Anker Nano II 65W PD充電器 USB-C ブラック ホワイト GaN II USB-C充電器 急速充電器 Power Delivery PPS対応 Type-C ACアダプター MacBook Air Pro iPad iPhone Android Galaxy Pixel ノートPC 折りたたみプラグ 小型 軽量 コンパクト PSE認証</t>
         </is>
       </c>
-      <c r="G419" s="14" t="n">
+      <c r="G419" t="n">
         <v>2690</v>
       </c>
       <c r="H419" t="n">
@@ -57161,7 +57165,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="B420" s="23" t="inlineStr">
+      <c r="B420" t="inlineStr">
         <is>
           <t>b0cx4c1tvk</t>
         </is>
@@ -57181,7 +57185,7 @@
           <t>Anker Power Bank (10000mAh, Fusion, Built-In USB-C ケーブル) ブラック ピンク ブルー ホワイト モバイルバッテリー USB-C ケーブル一体型 30W 急速充電 コンセント一体型 USB充電器 PD LEDディスプレイ 折りたたみプラグ iPhone Android iPad MacBook 小型 軽量 防災</t>
         </is>
       </c>
-      <c r="G420" s="14" t="n">
+      <c r="G420" t="n">
         <v>5890</v>
       </c>
       <c r="H420" t="n">
@@ -57193,7 +57197,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="B421" s="23" t="inlineStr">
+      <c r="B421" t="inlineStr">
         <is>
           <t>b0cx4c1tvk</t>
         </is>
@@ -57213,7 +57217,7 @@
           <t>Anker Power Bank (10000mAh, Fusion, Built-In USB-C ケーブル) ブラック ピンク ブルー ホワイト モバイルバッテリー USB-C ケーブル一体型 30W 急速充電 コンセント一体型 USB充電器 PD LEDディスプレイ 折りたたみプラグ iPhone Android iPad MacBook 小型 軽量 防災</t>
         </is>
       </c>
-      <c r="G421" s="14" t="n">
+      <c r="G421" t="n">
         <v>5990</v>
       </c>
       <c r="H421" t="n">
@@ -57225,7 +57229,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="B422" s="23" t="inlineStr">
+      <c r="B422" t="inlineStr">
         <is>
           <t>b0cx4c1tvk</t>
         </is>
@@ -57245,7 +57249,7 @@
           <t>Anker Power Bank (10000mAh, Fusion, Built-In USB-C ケーブル) ブラック ピンク ブルー ホワイト モバイルバッテリー USB-C ケーブル一体型 30W 急速充電 コンセント一体型 USB充電器 PD LEDディスプレイ 折りたたみプラグ iPhone Android iPad MacBook 小型 軽量 防災</t>
         </is>
       </c>
-      <c r="G422" s="14" t="n">
+      <c r="G422" t="n">
         <v>5990</v>
       </c>
       <c r="H422" t="n">
@@ -57257,7 +57261,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="B423" s="23" t="inlineStr">
+      <c r="B423" t="inlineStr">
         <is>
           <t>b0cx4c1tvk</t>
         </is>
@@ -57277,7 +57281,7 @@
           <t>Anker Power Bank (10000mAh, Fusion, Built-In USB-C ケーブル) ブラック ピンク ブルー ホワイト モバイルバッテリー USB-C ケーブル一体型 30W 急速充電 コンセント一体型 USB充電器 PD LEDディスプレイ 折りたたみプラグ iPhone Android iPad MacBook 小型 軽量 防災</t>
         </is>
       </c>
-      <c r="G423" s="14" t="n">
+      <c r="G423" t="n">
         <v>5990</v>
       </c>
       <c r="H423" t="n">
@@ -57294,7 +57298,7 @@
           <t>4987176354273</t>
         </is>
       </c>
-      <c r="B424" s="23" t="inlineStr">
+      <c r="B424" t="inlineStr">
         <is>
           <t>b0fy1j62w9-2</t>
         </is>
@@ -57314,7 +57318,7 @@
           <t>【2個セット】レノア リセット セラム 柔軟剤 さくらフローラルの香り 詰め替え 680mL×2 期間限定 SAKURA 詰替え 大容量 衣類ケア シワ防止 ヨレ防止 毛玉防止 静電気防止 ふんわり 香り長続き 洗濯 ランドリー 部屋干し 花粉対策 防臭 消臭 まとめ買い ストック P&amp;G</t>
         </is>
       </c>
-      <c r="G424" s="14" t="n">
+      <c r="G424" t="n">
         <v>874</v>
       </c>
       <c r="H424" t="n">
@@ -57326,7 +57330,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="B425" s="23" t="inlineStr">
+      <c r="B425" t="inlineStr">
         <is>
           <t>b0g1sql91q-2</t>
         </is>
@@ -57336,7 +57340,7 @@
           <t>0299/2086</t>
         </is>
       </c>
-      <c r="D425" s="11" t="inlineStr">
+      <c r="D425" t="inlineStr">
         <is>
           <t>B0G1SQL91Q-2</t>
         </is>
@@ -57346,7 +57350,7 @@
           <t>【2個セット】レノア アロマジュエル SAKURA 衣料用香り付けビーズ さくらフローラルの香り 詰め替え 990mL×2 期間限定 柔軟剤 香り付けビーズ 洗濯 ビーズ 大容量 特大 詰替え 香り長続き 部屋干し 縦型 ドラム式 P&amp;G</t>
         </is>
       </c>
-      <c r="G425" s="14" t="n">
+      <c r="G425" t="n">
         <v>2086</v>
       </c>
       <c r="H425" t="n">
@@ -57363,7 +57367,7 @@
           <t>4901301466426</t>
         </is>
       </c>
-      <c r="B426" s="23" t="inlineStr">
+      <c r="B426" t="inlineStr">
         <is>
           <t>b0gm6xjjst-2</t>
         </is>
@@ -57373,7 +57377,7 @@
           <t>4901301466426-2</t>
         </is>
       </c>
-      <c r="D426" s="11" t="inlineStr">
+      <c r="D426" t="inlineStr">
         <is>
           <t>B0GM6XJJST-2</t>
         </is>
@@ -57383,7 +57387,7 @@
           <t>【2個セット】アタックZERO 部屋干し 詰め替え 1460g×2個セット 花王 洗濯洗剤 液体洗剤 部屋干し専用 超特大 大容量 詰替え 24時間部屋干し臭防止 抗菌 洗濯槽防カビ 洗濯槽除菌 自動投入対応 生乾き臭 ニオイ対策 ランドリー 日用品 まとめ買い</t>
         </is>
       </c>
-      <c r="G426" s="14" t="n">
+      <c r="G426" t="n">
         <v>3460</v>
       </c>
       <c r="H426" t="n">
@@ -57400,7 +57404,7 @@
           <t>4901301466303</t>
         </is>
       </c>
-      <c r="B427" s="23" t="inlineStr">
+      <c r="B427" t="inlineStr">
         <is>
           <t>b0gm6y6yj4-2</t>
         </is>
@@ -57410,7 +57414,7 @@
           <t>4901301466303-2</t>
         </is>
       </c>
-      <c r="D427" s="11" t="inlineStr">
+      <c r="D427" t="inlineStr">
         <is>
           <t>B0GM6Y6YJ4-2</t>
         </is>
@@ -57420,7 +57424,7 @@
           <t>【2個セット】アタックZERO 詰め替え 1460g×2個セット 花王 洗濯洗剤 液体洗剤 超特大 大容量 詰替え 最高峰の消臭 自動投入対応 抗菌 洗濯槽除菌 洗濯槽防カビ バイオフィルム除去 糸くずフィルターヌメリ除去 すすぎ1回 濃縮 ランドリー 日用品 まとめ買い</t>
         </is>
       </c>
-      <c r="G427" s="14" t="n">
+      <c r="G427" t="n">
         <v>3460</v>
       </c>
       <c r="H427" t="n">
@@ -57432,12 +57436,12 @@
       </c>
     </row>
     <row r="428">
-      <c r="B428" s="23" t="inlineStr">
+      <c r="B428" t="inlineStr">
         <is>
           <t>set-0005</t>
         </is>
       </c>
-      <c r="C428" s="11" t="inlineStr">
+      <c r="C428" t="inlineStr">
         <is>
           <t>6260,6506/1736</t>
         </is>
@@ -57452,7 +57456,7 @@
           <t>【セット品】ファブリーズ W除菌+消臭スプレー 衣類・布製品用 ほのかな緑茶の香り 本体370mL＋詰め替え4回分1280mL P&amp;G 除菌 消臭 スプレー 布用 ソファ カーテン ベッド クッション 衣類 部屋干し タバコ 汗 ニオイ対策 大容量 詰替え まとめ買い</t>
         </is>
       </c>
-      <c r="G428" s="14" t="n">
+      <c r="G428" t="n">
         <v>1736</v>
       </c>
       <c r="H428" t="n">
@@ -57464,7 +57468,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="B429" s="23" t="inlineStr">
+      <c r="B429" t="inlineStr">
         <is>
           <t>set-0006</t>
         </is>
@@ -57484,7 +57488,7 @@
           <t>【セット品】ファブリーズ W除菌+消臭スプレー 衣類・布製品用 無香料 アルコール成分配合 本体370mL＋つめかえ4回分1280mL P&amp;G 布用 消臭スプレー 除菌スプレー 衣類 ソファ カーテン ベッド クッション 部屋干し タバコ 汗 ニオイ対策 大容量 詰替え まとめ買い</t>
         </is>
       </c>
-      <c r="G429" s="14" t="n">
+      <c r="G429" t="n">
         <v>1736</v>
       </c>
       <c r="H429" t="n">
@@ -57496,7 +57500,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="B430" s="23" t="inlineStr">
+      <c r="B430" t="inlineStr">
         <is>
           <t>set-0007</t>
         </is>
@@ -57516,7 +57520,7 @@
           <t>【セット品】ファブリーズ W除菌+消臭スプレー 衣類・布製品用 香りが残らない 本体370mL＋つめかえ4回分1280mL P&amp;G 布用 消臭スプレー 除菌スプレー 衣類 ソファ カーテン ベッド クッション 部屋干し タバコ 汗 ニオイ対策 大容量 詰替え まとめ買い</t>
         </is>
       </c>
-      <c r="G430" s="14" t="n">
+      <c r="G430" t="n">
         <v>1736</v>
       </c>
       <c r="H430" t="n">
@@ -57533,12 +57537,12 @@
           <t>4571104713265</t>
         </is>
       </c>
-      <c r="B431" s="23" t="inlineStr">
+      <c r="B431" t="inlineStr">
         <is>
           <t>b0179h2jvo-6</t>
         </is>
       </c>
-      <c r="C431" s="11" t="inlineStr">
+      <c r="C431" t="inlineStr">
         <is>
           <t>4571104713265-6</t>
         </is>
@@ -57553,7 +57557,7 @@
           <t>【6個セット】健康缶 15歳からの健康缶パウチ とろとろまぐろペースト 40g×6袋セット シニア猫用 キャットフード ウェットフード パウチ まぐろ ペースト 総合栄養食 高齢猫 老猫 水分補給 やわらか 食べやすい ごはん 愛猫 国産 猫用フード まとめ買い</t>
         </is>
       </c>
-      <c r="G431" s="14" t="n">
+      <c r="G431" t="n">
         <v>624</v>
       </c>
       <c r="H431" t="n">
@@ -57565,12 +57569,12 @@
       </c>
     </row>
     <row r="432">
-      <c r="B432" s="23" t="inlineStr">
+      <c r="B432" t="inlineStr">
         <is>
           <t>b01g81swcm</t>
         </is>
       </c>
-      <c r="C432" s="11" t="inlineStr">
+      <c r="C432" t="inlineStr">
         <is>
           <t>4901133863318-2-w</t>
         </is>
@@ -57585,7 +57589,7 @@
           <t>【訳あり】【12個入り】いなば 金のだしカップ まぐろ・かつお節入り 70g キャットフード ウェットフード 猫用 一般食 国産 ゼリータイプ まぐろ かつお節 猫 エサ ごはん 成猫 シニア 水分補給 食べ切り カップタイプ ペットフード いなばペットフード</t>
         </is>
       </c>
-      <c r="G432" s="14" t="n">
+      <c r="G432" t="n">
         <v>1396</v>
       </c>
       <c r="H432" t="n">
@@ -57602,12 +57606,12 @@
           <t>4589530701046</t>
         </is>
       </c>
-      <c r="B433" s="23" t="inlineStr">
+      <c r="B433" t="inlineStr">
         <is>
           <t>b01mtemme0</t>
         </is>
       </c>
-      <c r="C433" s="11" t="inlineStr">
+      <c r="C433" t="inlineStr">
         <is>
           <t>4589530701046-2</t>
         </is>
@@ -57622,7 +57626,7 @@
           <t>【2本セット】ビュクレール クレンジングローション 500mL メイク落とし クレンジングウォーター 拭き取りクレンジング W洗顔不要 オイルフリー まつエクOK 化粧水 保湿 ブライトニング 大容量 毛穴汚れ 角質ケア 日本製 BEAUCLAIR</t>
         </is>
       </c>
-      <c r="G433" s="14" t="n">
+      <c r="G433" t="n">
         <v>792</v>
       </c>
       <c r="H433" t="n">
@@ -57634,12 +57638,12 @@
       </c>
     </row>
     <row r="434">
-      <c r="B434" s="23" t="inlineStr">
+      <c r="B434" t="inlineStr">
         <is>
           <t>b075ssnk1l</t>
         </is>
       </c>
-      <c r="C434" s="11" t="inlineStr">
+      <c r="C434" t="inlineStr">
         <is>
           <t>3693/4780</t>
         </is>
@@ -57654,7 +57658,7 @@
           <t>【ブラウン】オーラルB 電動歯ブラシ D6015253P 回転式 電動歯ブラシ 歯垢除去 ホワイトニング 歯ぐきケア 充電式 防水設計 デンタルケア 口腔ケア Oral-B オーラルケア 歯ブラシ 電動ブラシ 替えブラシ対応 旅行 出張 身だしなみ ケア</t>
         </is>
       </c>
-      <c r="G434" s="14" t="n">
+      <c r="G434" t="n">
         <v>4780</v>
       </c>
       <c r="H434" t="n">
@@ -57671,13 +57675,15 @@
           <t>5060144645562</t>
         </is>
       </c>
-      <c r="B435" s="23" t="inlineStr">
+      <c r="B435" t="inlineStr">
         <is>
           <t>b07vl5tf8z</t>
         </is>
       </c>
-      <c r="C435" t="n">
-        <v>5060144645562</v>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>5060144645562</t>
+        </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -57689,7 +57695,7 @@
           <t>Bulldog ブルドッグ オリジナル 5枚刃 バンブーホルダー カミソリ 本体 替刃2個付き メンズ 髭剃り シェーバー 竹製ハンドル 首振り式 アロエスムーザー トリマー付き 男性用 シェービング スキンケア</t>
         </is>
       </c>
-      <c r="G435" s="14" t="n">
+      <c r="G435" t="n">
         <v>1192</v>
       </c>
       <c r="H435" t="n">
@@ -57706,7 +57712,7 @@
           <t>4902430898706</t>
         </is>
       </c>
-      <c r="B436" s="23" t="inlineStr">
+      <c r="B436" t="inlineStr">
         <is>
           <t>b08gpdl9ky</t>
         </is>
@@ -57726,7 +57732,7 @@
           <t>ブラウン 替刃 F/C70S-3Z-b シルバー 旧シリーズ7対応 純正 シェーバー替刃 網刃 内刃一体型 ブラシ付 70S メンズシェーバー 交換用 約18か月分 深剃り 髭剃り 電気シェーバー用 720s 750cc 760cc 790cc 7720s 7840s 7898cc</t>
         </is>
       </c>
-      <c r="G436" s="14" t="n">
+      <c r="G436" t="n">
         <v>4676</v>
       </c>
       <c r="H436" t="n">
@@ -57743,12 +57749,12 @@
           <t>4901301397355</t>
         </is>
       </c>
-      <c r="B437" s="23" t="inlineStr">
+      <c r="B437" t="inlineStr">
         <is>
           <t>b0915ngd2j-6</t>
         </is>
       </c>
-      <c r="C437" s="11" t="inlineStr">
+      <c r="C437" t="inlineStr">
         <is>
           <t>4901301397355-6</t>
         </is>
@@ -57763,7 +57769,7 @@
           <t>【6個セット】IROKA イロカ フレアフレグランス ネイキッドリリーの香り 詰め替え 1200mL×6個セット 花王 柔軟剤 大容量 液体 詰替え 超特大 香水のような香り 上質 透明感 消臭 抗菌 防臭 衣類ケア ふんわり 静電気防止 シワ防止 ランドリー 日用品 まとめ買い ストック</t>
         </is>
       </c>
-      <c r="G437" s="14" t="n">
+      <c r="G437" t="n">
         <v>7164</v>
       </c>
       <c r="H437" t="n">
@@ -57775,12 +57781,12 @@
       </c>
     </row>
     <row r="438">
-      <c r="B438" s="23" t="inlineStr">
+      <c r="B438" t="inlineStr">
         <is>
           <t>b09dc4r8qq-3</t>
         </is>
       </c>
-      <c r="C438" s="11" t="inlineStr">
+      <c r="C438" t="inlineStr">
         <is>
           <t>2546/13196</t>
         </is>
@@ -57795,7 +57801,7 @@
           <t>【3個セット】ジレット プロシールド 電動タイプ 本体＋替刃6個付（うち1個装着済） カミソリ 髭剃り メンズシェーバー 電動振動 深剃り 肌にやさしい 剃刀 シェービング 替刃式 Gillette 男性用 旅行 出張 身だしなみ ケア まとめ買い 大容量</t>
         </is>
       </c>
-      <c r="G438" s="14" t="n">
+      <c r="G438" t="n">
         <v>13196</v>
       </c>
       <c r="H438" t="n">
@@ -57807,12 +57813,12 @@
       </c>
     </row>
     <row r="439">
-      <c r="B439" s="23" t="inlineStr">
+      <c r="B439" t="inlineStr">
         <is>
           <t>b0b4nfdgn7</t>
         </is>
       </c>
-      <c r="C439" s="11" t="inlineStr">
+      <c r="C439" t="inlineStr">
         <is>
           <t>4901301347541-5-h</t>
         </is>
@@ -57827,7 +57833,7 @@
           <t>【5個セット】ビオレ さらさらパウダーシート さわやかせっけんの香り 携帯用 10枚 制汗シート ボディシート 汗拭きシート デオドラントシート ボディペーパー 汗ふきシート さらさら ベタつき ニオイ対策 外出 通勤 通学 スポーツ 花王</t>
         </is>
       </c>
-      <c r="G439" s="14" t="n">
+      <c r="G439" t="n">
         <v>1070</v>
       </c>
       <c r="H439" t="n">
@@ -57839,7 +57845,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="B440" s="23" t="inlineStr">
+      <c r="B440" t="inlineStr">
         <is>
           <t>b0c3l32wkr-2</t>
         </is>
@@ -57859,7 +57865,7 @@
           <t>【2個セット】友和 Tipo's 超撥水コーティング剤 弾き！ つめかえ用 500ml 撥水 コーティング剤 詰め替え 掃除 水回り シンク 洗面台 浴室 鏡 キッチン 蛇口 窓ガラス 車 ガラス 防汚 水アカ対策 汚れ防止 お手入れ 日本製 ティポス</t>
         </is>
       </c>
-      <c r="G440" s="14" t="n">
+      <c r="G440" t="n">
         <v>1116</v>
       </c>
       <c r="H440" t="n">
@@ -57876,12 +57882,12 @@
           <t>4582228251861</t>
         </is>
       </c>
-      <c r="B441" s="23" t="inlineStr">
+      <c r="B441" t="inlineStr">
         <is>
           <t>b0cp51ckvd</t>
         </is>
       </c>
-      <c r="C441" s="11" t="inlineStr">
+      <c r="C441" t="inlineStr">
         <is>
           <t>4582228251861-2</t>
         </is>
@@ -57896,7 +57902,7 @@
           <t>【20枚セット】アイリスオーヤマ 激熱家族 使い捨てカイロ 貼れない レギュラー 屋外専用 高温 約79℃ 寒さ対策 防寒 通勤 通学 スポーツ観戦 キャンプ アウトドア レジャー 作業 防災 10枚×2個セット</t>
         </is>
       </c>
-      <c r="G441" s="14" t="n">
+      <c r="G441" t="n">
         <v>505</v>
       </c>
       <c r="H441" t="n">
@@ -57913,12 +57919,12 @@
           <t>4987176228697</t>
         </is>
       </c>
-      <c r="B442" s="23" t="inlineStr">
+      <c r="B442" t="inlineStr">
         <is>
           <t>b0csctf87w-2</t>
         </is>
       </c>
-      <c r="C442" s="11" t="inlineStr">
+      <c r="C442" t="inlineStr">
         <is>
           <t>4987176228697-2</t>
         </is>
@@ -57933,7 +57939,7 @@
           <t>レノア アロマジュエル HOTEL ホワイトティーの香り 詰め替え 1410mL×2個セット 香り付けビーズ 衣類用香りづけ剤 大容量 洗濯ビーズ アロマビーズ 消臭 部屋干し 洗濯 香り 長続き 柔軟剤と一緒に使える 詰替え 衣類 ケア ランドリー 洗濯用品 日用品 まとめ買い ストック</t>
         </is>
       </c>
-      <c r="G442" s="14" t="n">
+      <c r="G442" t="n">
         <v>3376</v>
       </c>
       <c r="H442" t="n">
@@ -57950,7 +57956,7 @@
           <t>4902111776996</t>
         </is>
       </c>
-      <c r="B443" s="23" t="inlineStr">
+      <c r="B443" t="inlineStr">
         <is>
           <t>b0ctbg4l1x</t>
         </is>
@@ -57965,12 +57971,12 @@
           <t>b0ctbg4l1x</t>
         </is>
       </c>
-      <c r="E443" s="11" t="inlineStr">
+      <c r="E443" t="inlineStr">
         <is>
           <t>NEXXUS(ネクサス) リペアアンドカラープロテクト ヘアマスク トリートメント 本体 220g 日本製 色落ち防止 ケア ヘアケア</t>
         </is>
       </c>
-      <c r="G443" s="14" t="n">
+      <c r="G443" t="n">
         <v>1043</v>
       </c>
       <c r="H443" t="n">
@@ -57982,7 +57988,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="B444" s="23" t="inlineStr">
+      <c r="B444" t="inlineStr">
         <is>
           <t>b0cw1d1cmg-2</t>
         </is>
@@ -58002,7 +58008,7 @@
           <t>【2本セット】レブロン カラーステイ マルチプレイヤー アイ ペンシル 405 フォートレス 0.9g メタリックカーキ アイライナー アイシャドウ ウォータープルーフ ブレンディングブラシ シャープナー付き 高発色 落ちにくい にじみにくい 密着 アイメイク コスメ 化粧品</t>
         </is>
       </c>
-      <c r="G444" s="14" t="n">
+      <c r="G444" t="n">
         <v>998</v>
       </c>
       <c r="H444" t="n">
@@ -58019,12 +58025,12 @@
           <t>4901301432391</t>
         </is>
       </c>
-      <c r="B445" s="23" t="inlineStr">
+      <c r="B445" t="inlineStr">
         <is>
           <t>b0czhr33rf-3</t>
         </is>
       </c>
-      <c r="C445" s="11" t="inlineStr">
+      <c r="C445" t="inlineStr">
         <is>
           <t>4901301432391-3</t>
         </is>
@@ -58039,7 +58045,7 @@
           <t>花王 ビオレZero シート 無香性 20枚×3個セット 汗拭きシート ボディシート 顔・からだ用 超さらさらタイプ 制汗シート デオドラントシート 大判シート ベタつき 汗対策 全身 さらさら パウダーヴェール 持続型 詰め合わせ ボディケア 日用品 まとめ買い</t>
         </is>
       </c>
-      <c r="G445" s="14" t="n">
+      <c r="G445" t="n">
         <v>1083</v>
       </c>
       <c r="H445" t="n">
@@ -58056,12 +58062,12 @@
           <t>4987176243928</t>
         </is>
       </c>
-      <c r="B446" s="23" t="inlineStr">
+      <c r="B446" t="inlineStr">
         <is>
           <t>b0d6g9rw9y-2</t>
         </is>
       </c>
-      <c r="C446" s="11" t="inlineStr">
+      <c r="C446" t="inlineStr">
         <is>
           <t>4987176243928-2</t>
         </is>
@@ -58071,12 +58077,12 @@
           <t>b0d6g9rw9y-2</t>
         </is>
       </c>
-      <c r="E446" s="12" t="inlineStr">
+      <c r="E446" t="inlineStr">
         <is>
           <t>レノア 超消臭 煮沸レベル 抗菌ビーズ スポーツ クールリフレッシュ＆シトラス 詰め替え 超特大 1410mL×2個セット 香り付けビーズ 衣類用 消臭ビーズ 抗菌ビーズ 洗濯ビーズ ニオイ対策 部屋干し スポーツウェア 汗臭 大容量 詰替え 洗濯用品 日用品 まとめ買い ストック</t>
         </is>
       </c>
-      <c r="G446" s="14" t="n">
+      <c r="G446" t="n">
         <v>3376</v>
       </c>
       <c r="H446" t="n">
@@ -58093,7 +58099,7 @@
           <t>4979750819926</t>
         </is>
       </c>
-      <c r="B447" s="23" t="inlineStr">
+      <c r="B447" t="inlineStr">
         <is>
           <t>b0d8pmzsgc</t>
         </is>
@@ -58113,7 +58119,7 @@
           <t>セガフェイブ meスマホ+ サンリオキャラクターズ スマホトイ 充電式 カメラ ゲーム 音楽 アラーム 音声メッセージ 写真撮影 知育玩具 子ども用スマホ キッズトイ ハローキティ マイメロディ クロミ シナモロール ポムポムプリン</t>
         </is>
       </c>
-      <c r="G447" s="14" t="n">
+      <c r="G447" t="n">
         <v>5580</v>
       </c>
       <c r="H447" t="n">
@@ -58130,12 +58136,12 @@
           <t>0194644233532</t>
         </is>
       </c>
-      <c r="B448" s="23" t="inlineStr">
+      <c r="B448" t="inlineStr">
         <is>
           <t>b0dwmpnclc</t>
         </is>
       </c>
-      <c r="C448" s="11" t="inlineStr">
+      <c r="C448" t="inlineStr">
         <is>
           <t>0194644233532-2</t>
         </is>
@@ -58150,7 +58156,7 @@
           <t>Anker Eufy ユーフィ SmartTrack Card E30×2個セット 充電式紛失防止トラッカー スマートタグ 盗難防止タグ スマホが見つかる スマホ鳴らす 充電対応</t>
         </is>
       </c>
-      <c r="G448" s="14" t="n">
+      <c r="G448" t="n">
         <v>5980</v>
       </c>
       <c r="H448" t="n">
@@ -58167,12 +58173,12 @@
           <t>4901301450135</t>
         </is>
       </c>
-      <c r="B449" s="23" t="inlineStr">
+      <c r="B449" t="inlineStr">
         <is>
           <t>b0dxnblx52-3</t>
         </is>
       </c>
-      <c r="C449" s="11" t="inlineStr">
+      <c r="C449" t="inlineStr">
         <is>
           <t>4901301450135-3</t>
         </is>
@@ -58187,7 +58193,7 @@
           <t>【3個セット】メリットキッズ 泡で出てくるシャンプー つめかえ用 270mL×3個セット 花王 キッズシャンプー 子供用 泡タイプ 詰替え用 弱酸性 ノンシリコーン パラベンフリー 合成着色料フリー 汗対策 ニオイケア 地肌ケア 毎日のお風呂 ヘアケア</t>
         </is>
       </c>
-      <c r="G449" s="14" t="n">
+      <c r="G449" t="n">
         <v>1011</v>
       </c>
       <c r="H449" t="n">
@@ -58204,7 +58210,7 @@
           <t>4987176305657</t>
         </is>
       </c>
-      <c r="B450" s="23" t="inlineStr">
+      <c r="B450" t="inlineStr">
         <is>
           <t>b0f3d1ls31</t>
         </is>
@@ -58224,7 +58230,7 @@
           <t>ファブリーズ プレミアム 消臭スプレー パステルフローラル＆ブロッサムの香り 詰め替え 4倍 1240mL P&amp;G 布用消臭剤 除菌 消臭 衣類 カーペット ソファ 布製品用 大容量 超特大 詰替用 まとめ買い 日用品</t>
         </is>
       </c>
-      <c r="G450" s="14" t="n">
+      <c r="G450" t="n">
         <v>1039</v>
       </c>
       <c r="H450" t="n">
@@ -58241,7 +58247,7 @@
           <t>0840414620421</t>
         </is>
       </c>
-      <c r="B451" s="23" t="inlineStr">
+      <c r="B451" t="inlineStr">
         <is>
           <t>b0f7zf7w9p</t>
         </is>
@@ -58261,7 +58267,7 @@
           <t>Amazon Fire TV Stick 4K Plus ストリーミングメディアプレーヤー 4K対応 Wi-Fi 6 映画 動画配信 Alexa対応 音声認識リモコン付属 Prime Video Netflix YouTube TV Disney+ ABEMA U-NEXT 映像配信 高画質 Dolby Vision Dolby Atmos</t>
         </is>
       </c>
-      <c r="G451" s="14" t="n">
+      <c r="G451" t="n">
         <v>5980</v>
       </c>
       <c r="H451" t="n">
@@ -58278,12 +58284,12 @@
           <t>4987176309099</t>
         </is>
       </c>
-      <c r="B452" s="23" t="inlineStr">
+      <c r="B452" t="inlineStr">
         <is>
           <t>b0fcfk55zk-4</t>
         </is>
       </c>
-      <c r="C452" s="11" t="inlineStr">
+      <c r="C452" t="inlineStr">
         <is>
           <t>4987176309099-4</t>
         </is>
@@ -58298,7 +58304,7 @@
           <t>【4個セット】アリエール 液体洗剤 漂白剤レベル洗浄 エリそで&amp;くすみ 詰め替え 超ウルトラジャンボ 1720g×4個セット 洗濯洗剤 液体 詰替え 大容量 黄ばみ くすみ エリ汚れ 皮脂汚れ 消臭 部屋干し 抗菌 衣類用洗剤 洗濯 ランドリー 日用品 まとめ買い ストック</t>
         </is>
       </c>
-      <c r="G452" s="14" t="n">
+      <c r="G452" t="n">
         <v>3940</v>
       </c>
       <c r="H452" t="n">
@@ -58315,12 +58321,12 @@
           <t>4903301375173</t>
         </is>
       </c>
-      <c r="B453" s="23" t="inlineStr">
+      <c r="B453" t="inlineStr">
         <is>
           <t>b0fpvbqv49-2</t>
         </is>
       </c>
-      <c r="C453" s="11" t="inlineStr">
+      <c r="C453" t="inlineStr">
         <is>
           <t>4903301375173-2</t>
         </is>
@@ -58335,7 +58341,7 @@
           <t>【2個セット】ソフラン アロマリッチ リラクシー ホワイトフラワーの香り 詰替用 1300mL 2個セット 柔軟剤 大容量 特大 つめかえ用 フローラル 部屋干し 抗菌 防臭 静電気防止 衣類ケア まとめ買い ライオン LION</t>
         </is>
       </c>
-      <c r="G453" s="14" t="n">
+      <c r="G453" t="n">
         <v>1668</v>
       </c>
       <c r="H453" t="n">
@@ -58347,7 +58353,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="B454" s="23" t="inlineStr">
+      <c r="B454" t="inlineStr">
         <is>
           <t>b0fzk6z13j-2</t>
         </is>
@@ -58367,7 +58373,7 @@
           <t>【2個セット】ファブリーズ レノアハピネスミスト 衣類・布製品用 消臭スプレー さくらフローラル＆ブロッサムの香り 詰め替え 610mL×2 期間限定 消臭 除菌 布用スプレー ファブリックスプレー 衣類 ソファ カーテン 寝具 クッション 部屋干し ニオイ対策 まとめ買い 大容量</t>
         </is>
       </c>
-      <c r="G454" s="14" t="n">
+      <c r="G454" t="n">
         <v>1204</v>
       </c>
       <c r="H454" t="n">
@@ -58379,7 +58385,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="B455" s="23" t="inlineStr">
+      <c r="B455" t="inlineStr">
         <is>
           <t>b0g2ktk6wy-2</t>
         </is>
@@ -58399,7 +58405,7 @@
           <t>【2個セット】ランドリン 柔軟剤 サクラチェリーブロッサムの香り 2026 600mL×2 本体 期間限定 桜 柔軟剤 大容量 フレグランス オーガニック植物エキス配合 部屋干しOK 静電気防止 花粉対策 赤ちゃん衣類OK 衣類ケア なめらか ふんわり ランドリー 洗濯 まとめ買い ストック</t>
         </is>
       </c>
-      <c r="G455" s="14" t="n">
+      <c r="G455" t="n">
         <v>1532</v>
       </c>
       <c r="H455" t="n">
@@ -58416,7 +58422,7 @@
           <t>0840414684973</t>
         </is>
       </c>
-      <c r="B456" s="23" t="inlineStr">
+      <c r="B456" t="inlineStr">
         <is>
           <t>b0g2tqzmy1</t>
         </is>
@@ -58436,7 +58442,7 @@
           <t>Amazon Fire TV Stick 4K Plus Alexa対応音声認識リモコン付 ストリーミングメディアプレーヤー Wi-Fi 6 4K Ultra HD Dolby Vision HDR10+ Dolby Atmos HDMI テレビ 動画配信 Netflix Prime Video YouTube TVer ABEMA U-NEXT Disney+ 音声操作</t>
         </is>
       </c>
-      <c r="G456" s="14" t="n">
+      <c r="G456" t="n">
         <v>5980</v>
       </c>
       <c r="H456" t="n">
@@ -58453,7 +58459,7 @@
           <t>0840414639447</t>
         </is>
       </c>
-      <c r="B457" s="23" t="inlineStr">
+      <c r="B457" t="inlineStr">
         <is>
           <t>b0g3ycrjkx</t>
         </is>
@@ -58473,7 +58479,7 @@
           <t>Amazon Fire TV Stick HD Alexa対応音声認識リモコン付 ストリーミングメディアプレーヤー Wi-Fi 6対応 フルHD HDMI 動画配信 Netflix Prime Video YouTube TVer ABEMA U-NEXT Disney+ 音声操作 コンパクト テレビ 接続</t>
         </is>
       </c>
-      <c r="G457" s="14" t="n">
+      <c r="G457" t="n">
         <v>3780</v>
       </c>
       <c r="H457" t="n">
@@ -58490,12 +58496,12 @@
           <t>4987176364166</t>
         </is>
       </c>
-      <c r="B458" s="23" t="inlineStr">
+      <c r="B458" t="inlineStr">
         <is>
           <t>b0g4mfq7cw-2</t>
         </is>
       </c>
-      <c r="C458" s="11" t="inlineStr">
+      <c r="C458" t="inlineStr">
         <is>
           <t>4987176364166-2</t>
         </is>
@@ -58510,7 +58516,7 @@
           <t>【2個セット】レノア アロマジュエル Perfume ブルーミングブロッサムの香り 詰め替え 1410mL×2個セット 香り付けビーズ 衣類用香りづけ剤 大容量 洗濯ビーズ アロマビーズ 消臭 防臭 洗濯 香り 長続き 詰替え ランドリー 衣類ケア 洗濯用品 日用品 まとめ買い ストック</t>
         </is>
       </c>
-      <c r="G458" s="14" t="n">
+      <c r="G458" t="n">
         <v>3376</v>
       </c>
       <c r="H458" t="n">
@@ -58527,7 +58533,7 @@
           <t>4987176364289</t>
         </is>
       </c>
-      <c r="B459" s="23" t="inlineStr">
+      <c r="B459" t="inlineStr">
         <is>
           <t>b0g4mhkqp8-2</t>
         </is>
@@ -58542,12 +58548,12 @@
           <t>b0g4mhkqp8-2</t>
         </is>
       </c>
-      <c r="E459" s="12" t="inlineStr">
+      <c r="E459" t="inlineStr">
         <is>
           <t>レノア アロマジュエル Perfume アンティークローズ&amp;フローラルの香り 詰め替え 1410mL×2個セット 香り付けビーズ 衣類用香りづけ剤 大容量 洗濯ビーズ アロマビーズ 消臭 防臭 洗濯 香り 長続き 詰替え ランドリー 衣類ケア 洗濯用品 日用品 まとめ買い ストック</t>
         </is>
       </c>
-      <c r="G459" s="14" t="n">
+      <c r="G459" t="n">
         <v>3376</v>
       </c>
       <c r="H459" t="n">
@@ -58564,12 +58570,12 @@
           <t>4901301466280</t>
         </is>
       </c>
-      <c r="B460" s="23" t="inlineStr">
+      <c r="B460" t="inlineStr">
         <is>
           <t>b0gm6xmjmn-2</t>
         </is>
       </c>
-      <c r="C460" s="11" t="inlineStr">
+      <c r="C460" t="inlineStr">
         <is>
           <t>4901301466280-2</t>
         </is>
@@ -58584,7 +58590,7 @@
           <t>【2個セット】アタックZERO ドラム式専用 詰め替え 1460g×2個セット 花王 洗濯洗剤 液体洗剤 部屋干し 消臭 抗菌 ドラム式洗濯機専用 超特大 大容量 詰替え 衣類から洗濯槽まで 最高峰の消臭 エリ汚れ 皮脂汚れ ニオイ対策 洗濯 ランドリー 日用品 まとめ買い ストック</t>
         </is>
       </c>
-      <c r="G460" s="14" t="n">
+      <c r="G460" t="n">
         <v>3460</v>
       </c>
       <c r="H460" t="n">
@@ -58596,7 +58602,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="B461" s="23" t="inlineStr">
+      <c r="B461" t="inlineStr">
         <is>
           <t>set-0008</t>
         </is>
@@ -58616,7 +58622,7 @@
           <t>【2種セット】しずくちゃん ウォーターシール しずくパーク しずくの森のなかまたち デコシール ぷっくりシール 立体シール キャラクターシール キラキラ シール 文具 手帳 ノート アルバム デコレーション 子ども キッズ 女の子 プレゼント ギフト アソート まとめ買い</t>
         </is>
       </c>
-      <c r="G461" s="14" t="n">
+      <c r="G461" t="n">
         <v>580</v>
       </c>
       <c r="H461" t="n">
@@ -58628,7 +58634,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="B462" s="23" t="inlineStr">
+      <c r="B462" t="inlineStr">
         <is>
           <t>set-0009</t>
         </is>
@@ -58648,7 +58654,7 @@
           <t>【2種セット】しずくちゃん おはじきシール しずくちゃん みるみるちゃん キャラクターシール デコシール ぷっくりシール 立体シール キラキラ シール 文具 ステーショナリー 手帳 ノート アルバム デコレーション キッズ 子ども 女の子 プレゼント ギフト まとめ買い</t>
         </is>
       </c>
-      <c r="G462" s="14" t="n">
+      <c r="G462" t="n">
         <v>522</v>
       </c>
       <c r="H462" t="n">
@@ -58660,12 +58666,12 @@
       </c>
     </row>
     <row r="463">
-      <c r="B463" s="23" t="inlineStr">
+      <c r="B463" t="inlineStr">
         <is>
           <t>set-0010</t>
         </is>
       </c>
-      <c r="C463" s="11" t="inlineStr">
+      <c r="C463" t="inlineStr">
         <is>
           <t>0561,0578,0585,0592/928</t>
         </is>
@@ -58680,7 +58686,7 @@
           <t>【4種セット】エターナルジュエリークラウンシール フェアリーブルーコア トゥインクルクラウン ダークムーンエンジェル マジカルドリーミー デコシール ジュエリーシール 立体シール キラキラ シール 手帳 ノート アルバム デコレーション プレゼント ギフト まとめ買い</t>
         </is>
       </c>
-      <c r="G463" s="14" t="n">
+      <c r="G463" t="n">
         <v>928</v>
       </c>
       <c r="H463" t="n">
@@ -58692,13 +58698,15 @@
       </c>
     </row>
     <row r="464">
-      <c r="B464" s="23" t="inlineStr">
+      <c r="B464" t="inlineStr">
         <is>
           <t>set-0011</t>
         </is>
       </c>
-      <c r="C464" s="18" t="n">
-        <v>1486149315091510</v>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>1486,1493,1509,1516</t>
+        </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -58710,7 +58718,7 @@
           <t>【4種セット】プレミアムオーロラスポンジシール おやすみバニー エアリーチュチュ スイートハニークラウド マジカルウィッシュ デコシール スポンジシール オーロラシール 立体シール 手帳 ノート アルバム 文具 デコレーション プレゼント ギフト</t>
         </is>
       </c>
-      <c r="G464" s="14" t="n">
+      <c r="G464" t="n">
         <v>814</v>
       </c>
       <c r="H464" t="n">
@@ -58722,7 +58730,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="B465" s="23" t="inlineStr">
+      <c r="B465" t="inlineStr">
         <is>
           <t>set-0012</t>
         </is>
@@ -58742,7 +58750,7 @@
           <t>【3種セット】ハピピチョアチョアポップシール 3種セット うさうさ わんわん ねこねこ キャラクターシール デコシール ステッカー ポップシール 手帳シール ノートデコ スマホデコ 韓国風文具 かわいいシール 女の子向け 雑貨 コレクションシール まとめ買い ギフト</t>
         </is>
       </c>
-      <c r="G465" s="14" t="n">
+      <c r="G465" t="n">
         <v>558</v>
       </c>
       <c r="H465" t="n">
@@ -58754,7 +58762,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="B466" s="23" t="inlineStr">
+      <c r="B466" t="inlineStr">
         <is>
           <t>set-0013</t>
         </is>
@@ -58774,7 +58782,7 @@
           <t>【2種セット】おはじきシール スイートカフェ おやすみバニー デコシール ぷっくりシール 透明シール きらきらシール 立体風シール ステッカー 手帳 ノート アルバム デコレーション 文房具 小物デコ コレクション ギフト まとめ買い 女の子雑貨</t>
         </is>
       </c>
-      <c r="G466" s="14" t="n">
+      <c r="G466" t="n">
         <v>372</v>
       </c>
       <c r="H466" t="n">
@@ -58786,7 +58794,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="B467" s="23" t="inlineStr">
+      <c r="B467" t="inlineStr">
         <is>
           <t>set-0014</t>
         </is>
@@ -58806,7 +58814,7 @@
           <t>【セット品】NEXXUS ネクサス リペアアンドカラープロテクト トリートメント セット ポンプ440g+詰め替え350g カラーケア ダメージケア 色落ち防止 サロン品質 保湿 補修 ヘアケア 日本製 ユニリーバ</t>
         </is>
       </c>
-      <c r="G467" s="14" t="n">
+      <c r="G467" t="n">
         <v>1432</v>
       </c>
       <c r="H467" t="n">
@@ -58818,22 +58826,21 @@
       </c>
     </row>
     <row r="468">
-      <c r="E468" s="13" t="inlineStr">
+      <c r="E468" s="26" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="H468" s="13">
+      <c r="H468" s="26">
         <f>SUM(H2:H467)</f>
         <v/>
       </c>
-      <c r="I468" s="13">
+      <c r="I468" s="26">
         <f>SUM(I2:I467)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>